--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -785,25 +785,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8431300</v>
+        <v>28154100</v>
       </c>
       <c r="E8" s="3">
-        <v>8232000</v>
+        <v>8918000</v>
       </c>
       <c r="F8" s="3">
-        <v>9324900</v>
+        <v>10101900</v>
       </c>
       <c r="G8" s="3">
-        <v>9522700</v>
+        <v>10316300</v>
       </c>
       <c r="H8" s="3">
-        <v>10425200</v>
+        <v>11294000</v>
       </c>
       <c r="I8" s="3">
-        <v>10532400</v>
+        <v>11410100</v>
       </c>
       <c r="J8" s="3">
-        <v>7793500</v>
+        <v>8442900</v>
       </c>
       <c r="K8" s="3">
         <v>7622700</v>
@@ -877,25 +877,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4945400</v>
+        <v>18899000</v>
       </c>
       <c r="E9" s="3">
-        <v>5156900</v>
+        <v>5586600</v>
       </c>
       <c r="F9" s="3">
-        <v>5466800</v>
+        <v>5922300</v>
       </c>
       <c r="G9" s="3">
-        <v>5761800</v>
+        <v>6241900</v>
       </c>
       <c r="H9" s="3">
-        <v>5864500</v>
+        <v>6353200</v>
       </c>
       <c r="I9" s="3">
-        <v>5538600</v>
+        <v>6000200</v>
       </c>
       <c r="J9" s="3">
-        <v>4305100</v>
+        <v>4663800</v>
       </c>
       <c r="K9" s="3">
         <v>4591800</v>
@@ -969,25 +969,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3485900</v>
+        <v>9255100</v>
       </c>
       <c r="E10" s="3">
-        <v>3075100</v>
+        <v>3331400</v>
       </c>
       <c r="F10" s="3">
-        <v>3858100</v>
+        <v>4179600</v>
       </c>
       <c r="G10" s="3">
-        <v>3760900</v>
+        <v>4074300</v>
       </c>
       <c r="H10" s="3">
-        <v>4560700</v>
+        <v>4940800</v>
       </c>
       <c r="I10" s="3">
-        <v>4993700</v>
+        <v>5409900</v>
       </c>
       <c r="J10" s="3">
-        <v>3488400</v>
+        <v>3779100</v>
       </c>
       <c r="K10" s="3">
         <v>3030900</v>
@@ -1095,25 +1095,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>193100</v>
+        <v>209200</v>
       </c>
       <c r="E12" s="3">
-        <v>59900</v>
+        <v>64900</v>
       </c>
       <c r="F12" s="3">
-        <v>59800</v>
+        <v>64800</v>
       </c>
       <c r="G12" s="3">
-        <v>209900</v>
+        <v>227400</v>
       </c>
       <c r="H12" s="3">
-        <v>23900</v>
+        <v>25900</v>
       </c>
       <c r="I12" s="3">
-        <v>106800</v>
+        <v>115700</v>
       </c>
       <c r="J12" s="3">
-        <v>22300</v>
+        <v>24200</v>
       </c>
       <c r="K12" s="3">
         <v>101600</v>
@@ -1279,25 +1279,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="E14" s="3">
-        <v>8800</v>
+        <v>9500</v>
       </c>
       <c r="F14" s="3">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="G14" s="3">
-        <v>81100</v>
+        <v>87900</v>
       </c>
       <c r="H14" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="I14" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="J14" s="3">
-        <v>6300</v>
+        <v>6800</v>
       </c>
       <c r="K14" s="3">
         <v>24000</v>
@@ -1371,25 +1371,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>29200</v>
+        <v>31600</v>
       </c>
       <c r="E15" s="3">
-        <v>29500</v>
+        <v>32000</v>
       </c>
       <c r="F15" s="3">
-        <v>36800</v>
+        <v>39900</v>
       </c>
       <c r="G15" s="3">
-        <v>79300</v>
+        <v>85900</v>
       </c>
       <c r="H15" s="3">
-        <v>30600</v>
+        <v>33200</v>
       </c>
       <c r="I15" s="3">
-        <v>31400</v>
+        <v>34000</v>
       </c>
       <c r="J15" s="3">
-        <v>31200</v>
+        <v>33800</v>
       </c>
       <c r="K15" s="3">
         <v>89200</v>
@@ -1494,25 +1494,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5595500</v>
+        <v>18782100</v>
       </c>
       <c r="E17" s="3">
-        <v>5712400</v>
+        <v>6188400</v>
       </c>
       <c r="F17" s="3">
-        <v>6031900</v>
+        <v>6534500</v>
       </c>
       <c r="G17" s="3">
-        <v>6706600</v>
+        <v>7265500</v>
       </c>
       <c r="H17" s="3">
-        <v>6292000</v>
+        <v>6816300</v>
       </c>
       <c r="I17" s="3">
-        <v>6066500</v>
+        <v>6572100</v>
       </c>
       <c r="J17" s="3">
-        <v>4786300</v>
+        <v>5185200</v>
       </c>
       <c r="K17" s="3">
         <v>5129400</v>
@@ -1586,25 +1586,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2835900</v>
+        <v>9372000</v>
       </c>
       <c r="E18" s="3">
-        <v>2519600</v>
+        <v>2729600</v>
       </c>
       <c r="F18" s="3">
-        <v>3293000</v>
+        <v>3567400</v>
       </c>
       <c r="G18" s="3">
-        <v>2816100</v>
+        <v>3050800</v>
       </c>
       <c r="H18" s="3">
-        <v>4133200</v>
+        <v>4477600</v>
       </c>
       <c r="I18" s="3">
-        <v>4465800</v>
+        <v>4838000</v>
       </c>
       <c r="J18" s="3">
-        <v>3007100</v>
+        <v>3257700</v>
       </c>
       <c r="K18" s="3">
         <v>2493200</v>
@@ -1712,25 +1712,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>288500</v>
+        <v>499900</v>
       </c>
       <c r="E20" s="3">
-        <v>-47700</v>
+        <v>-51700</v>
       </c>
       <c r="F20" s="3">
-        <v>137900</v>
+        <v>149400</v>
       </c>
       <c r="G20" s="3">
-        <v>65800</v>
+        <v>71200</v>
       </c>
       <c r="H20" s="3">
-        <v>-42900</v>
+        <v>-46500</v>
       </c>
       <c r="I20" s="3">
-        <v>-101000</v>
+        <v>-109400</v>
       </c>
       <c r="J20" s="3">
-        <v>-53600</v>
+        <v>-58100</v>
       </c>
       <c r="K20" s="3">
         <v>-21600</v>
@@ -1804,25 +1804,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3973700</v>
+        <v>12488300</v>
       </c>
       <c r="E21" s="3">
-        <v>3278700</v>
+        <v>3552000</v>
       </c>
       <c r="F21" s="3">
-        <v>4190000</v>
+        <v>4539100</v>
       </c>
       <c r="G21" s="3">
-        <v>3693000</v>
+        <v>4000700</v>
       </c>
       <c r="H21" s="3">
-        <v>4854500</v>
+        <v>5259000</v>
       </c>
       <c r="I21" s="3">
-        <v>5050200</v>
+        <v>5471100</v>
       </c>
       <c r="J21" s="3">
-        <v>3603800</v>
+        <v>3904100</v>
       </c>
       <c r="K21" s="3">
         <v>3137800</v>
@@ -1896,25 +1896,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>413500</v>
+        <v>1428900</v>
       </c>
       <c r="E22" s="3">
-        <v>405500</v>
+        <v>439300</v>
       </c>
       <c r="F22" s="3">
-        <v>417200</v>
+        <v>452000</v>
       </c>
       <c r="G22" s="3">
-        <v>391500</v>
+        <v>424100</v>
       </c>
       <c r="H22" s="3">
-        <v>349400</v>
+        <v>378500</v>
       </c>
       <c r="I22" s="3">
-        <v>319700</v>
+        <v>346400</v>
       </c>
       <c r="J22" s="3">
-        <v>263600</v>
+        <v>285600</v>
       </c>
       <c r="K22" s="3">
         <v>294600</v>
@@ -1988,25 +1988,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>2710900</v>
+        <v>8443000</v>
       </c>
       <c r="E23" s="3">
-        <v>2066400</v>
+        <v>2238600</v>
       </c>
       <c r="F23" s="3">
-        <v>3013700</v>
+        <v>3264800</v>
       </c>
       <c r="G23" s="3">
-        <v>2490400</v>
+        <v>2697900</v>
       </c>
       <c r="H23" s="3">
-        <v>3741000</v>
+        <v>4052700</v>
       </c>
       <c r="I23" s="3">
-        <v>4045100</v>
+        <v>4382200</v>
       </c>
       <c r="J23" s="3">
-        <v>2689900</v>
+        <v>2914000</v>
       </c>
       <c r="K23" s="3">
         <v>2177000</v>
@@ -2080,25 +2080,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>1273700</v>
+        <v>3701900</v>
       </c>
       <c r="E24" s="3">
-        <v>800600</v>
+        <v>867300</v>
       </c>
       <c r="F24" s="3">
-        <v>1342300</v>
+        <v>1454200</v>
       </c>
       <c r="G24" s="3">
-        <v>643600</v>
+        <v>697200</v>
       </c>
       <c r="H24" s="3">
-        <v>1227700</v>
+        <v>1330000</v>
       </c>
       <c r="I24" s="3">
-        <v>1274300</v>
+        <v>1380500</v>
       </c>
       <c r="J24" s="3">
-        <v>932100</v>
+        <v>1009800</v>
       </c>
       <c r="K24" s="3">
         <v>495300</v>
@@ -2264,25 +2264,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1437100</v>
+        <v>4741100</v>
       </c>
       <c r="E26" s="3">
-        <v>1265800</v>
+        <v>1371300</v>
       </c>
       <c r="F26" s="3">
-        <v>1671400</v>
+        <v>1810600</v>
       </c>
       <c r="G26" s="3">
-        <v>1846800</v>
+        <v>2000800</v>
       </c>
       <c r="H26" s="3">
-        <v>2513200</v>
+        <v>2722700</v>
       </c>
       <c r="I26" s="3">
-        <v>2770800</v>
+        <v>3001700</v>
       </c>
       <c r="J26" s="3">
-        <v>1757700</v>
+        <v>1904200</v>
       </c>
       <c r="K26" s="3">
         <v>1681700</v>
@@ -2356,25 +2356,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1220600</v>
+        <v>3859200</v>
       </c>
       <c r="E27" s="3">
-        <v>981000</v>
+        <v>1062700</v>
       </c>
       <c r="F27" s="3">
-        <v>1358500</v>
+        <v>1471700</v>
       </c>
       <c r="G27" s="3">
-        <v>1644200</v>
+        <v>1781200</v>
       </c>
       <c r="H27" s="3">
-        <v>2283100</v>
+        <v>2473300</v>
       </c>
       <c r="I27" s="3">
-        <v>2512800</v>
+        <v>2722200</v>
       </c>
       <c r="J27" s="3">
-        <v>1577400</v>
+        <v>1708900</v>
       </c>
       <c r="K27" s="3">
         <v>1458500</v>
@@ -2816,25 +2816,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-288500</v>
+        <v>-499900</v>
       </c>
       <c r="E32" s="3">
-        <v>47700</v>
+        <v>51700</v>
       </c>
       <c r="F32" s="3">
-        <v>-137900</v>
+        <v>-149400</v>
       </c>
       <c r="G32" s="3">
-        <v>-65800</v>
+        <v>-71200</v>
       </c>
       <c r="H32" s="3">
-        <v>42900</v>
+        <v>46500</v>
       </c>
       <c r="I32" s="3">
-        <v>101000</v>
+        <v>109400</v>
       </c>
       <c r="J32" s="3">
-        <v>53600</v>
+        <v>58100</v>
       </c>
       <c r="K32" s="3">
         <v>21600</v>
@@ -2908,25 +2908,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1220600</v>
+        <v>3859200</v>
       </c>
       <c r="E33" s="3">
-        <v>981000</v>
+        <v>1062700</v>
       </c>
       <c r="F33" s="3">
-        <v>1358500</v>
+        <v>1471700</v>
       </c>
       <c r="G33" s="3">
-        <v>1644200</v>
+        <v>1781200</v>
       </c>
       <c r="H33" s="3">
-        <v>2283100</v>
+        <v>2473300</v>
       </c>
       <c r="I33" s="3">
-        <v>2512800</v>
+        <v>2722200</v>
       </c>
       <c r="J33" s="3">
-        <v>1577400</v>
+        <v>1708900</v>
       </c>
       <c r="K33" s="3">
         <v>1458500</v>
@@ -3092,25 +3092,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1220600</v>
+        <v>3859200</v>
       </c>
       <c r="E35" s="3">
-        <v>981000</v>
+        <v>1062700</v>
       </c>
       <c r="F35" s="3">
-        <v>1358500</v>
+        <v>1471700</v>
       </c>
       <c r="G35" s="3">
-        <v>1644200</v>
+        <v>1781200</v>
       </c>
       <c r="H35" s="3">
-        <v>2283100</v>
+        <v>2473300</v>
       </c>
       <c r="I35" s="3">
-        <v>2512800</v>
+        <v>2722200</v>
       </c>
       <c r="J35" s="3">
-        <v>1577400</v>
+        <v>1708900</v>
       </c>
       <c r="K35" s="3">
         <v>1458500</v>
@@ -3349,25 +3349,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>2897000</v>
+        <v>3138400</v>
       </c>
       <c r="E41" s="3">
-        <v>2718000</v>
+        <v>2944500</v>
       </c>
       <c r="F41" s="3">
-        <v>3719400</v>
+        <v>4029300</v>
       </c>
       <c r="G41" s="3">
-        <v>3696300</v>
+        <v>4004300</v>
       </c>
       <c r="H41" s="3">
-        <v>3100300</v>
+        <v>3358600</v>
       </c>
       <c r="I41" s="3">
-        <v>2424900</v>
+        <v>2626900</v>
       </c>
       <c r="J41" s="3">
-        <v>3359800</v>
+        <v>3639800</v>
       </c>
       <c r="K41" s="3">
         <v>3492000</v>
@@ -3441,25 +3441,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>529100</v>
+        <v>573200</v>
       </c>
       <c r="E42" s="3">
-        <v>328600</v>
+        <v>356000</v>
       </c>
       <c r="F42" s="3">
-        <v>525500</v>
+        <v>569300</v>
       </c>
       <c r="G42" s="3">
-        <v>400600</v>
+        <v>434000</v>
       </c>
       <c r="H42" s="3">
-        <v>645800</v>
+        <v>699600</v>
       </c>
       <c r="I42" s="3">
-        <v>398000</v>
+        <v>431200</v>
       </c>
       <c r="J42" s="3">
-        <v>517000</v>
+        <v>560000</v>
       </c>
       <c r="K42" s="3">
         <v>517100</v>
@@ -3533,25 +3533,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>11166900</v>
+        <v>12097500</v>
       </c>
       <c r="E43" s="3">
-        <v>12482700</v>
+        <v>13522900</v>
       </c>
       <c r="F43" s="3">
-        <v>13381200</v>
+        <v>14496300</v>
       </c>
       <c r="G43" s="3">
-        <v>11251700</v>
+        <v>12189300</v>
       </c>
       <c r="H43" s="3">
-        <v>9599900</v>
+        <v>10399900</v>
       </c>
       <c r="I43" s="3">
-        <v>8614400</v>
+        <v>9332300</v>
       </c>
       <c r="J43" s="3">
-        <v>7370700</v>
+        <v>7984900</v>
       </c>
       <c r="K43" s="3">
         <v>6087200</v>
@@ -3625,25 +3625,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>2725600</v>
+        <v>2952700</v>
       </c>
       <c r="E44" s="3">
-        <v>2470900</v>
+        <v>2676800</v>
       </c>
       <c r="F44" s="3">
-        <v>2669500</v>
+        <v>2892000</v>
       </c>
       <c r="G44" s="3">
-        <v>2851200</v>
+        <v>3088800</v>
       </c>
       <c r="H44" s="3">
-        <v>2588000</v>
+        <v>2803700</v>
       </c>
       <c r="I44" s="3">
-        <v>2922400</v>
+        <v>3165900</v>
       </c>
       <c r="J44" s="3">
-        <v>2633200</v>
+        <v>2852700</v>
       </c>
       <c r="K44" s="3">
         <v>2015600</v>
@@ -3717,25 +3717,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>425700</v>
+        <v>461100</v>
       </c>
       <c r="E45" s="3">
-        <v>392800</v>
+        <v>425600</v>
       </c>
       <c r="F45" s="3">
-        <v>425700</v>
+        <v>461100</v>
       </c>
       <c r="G45" s="3">
-        <v>346700</v>
+        <v>375600</v>
       </c>
       <c r="H45" s="3">
-        <v>389000</v>
+        <v>421400</v>
       </c>
       <c r="I45" s="3">
-        <v>282800</v>
+        <v>306400</v>
       </c>
       <c r="J45" s="3">
-        <v>315200</v>
+        <v>341400</v>
       </c>
       <c r="K45" s="3">
         <v>295100</v>
@@ -3809,25 +3809,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>17744200</v>
+        <v>19222900</v>
       </c>
       <c r="E46" s="3">
-        <v>18393000</v>
+        <v>19925800</v>
       </c>
       <c r="F46" s="3">
-        <v>20721300</v>
+        <v>22448100</v>
       </c>
       <c r="G46" s="3">
-        <v>18546400</v>
+        <v>20092000</v>
       </c>
       <c r="H46" s="3">
-        <v>16322900</v>
+        <v>17683200</v>
       </c>
       <c r="I46" s="3">
-        <v>14642500</v>
+        <v>15862700</v>
       </c>
       <c r="J46" s="3">
-        <v>14195800</v>
+        <v>15378800</v>
       </c>
       <c r="K46" s="3">
         <v>12407000</v>
@@ -3901,25 +3901,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>9391800</v>
+        <v>10174500</v>
       </c>
       <c r="E47" s="3">
-        <v>10036300</v>
+        <v>10872700</v>
       </c>
       <c r="F47" s="3">
-        <v>10281200</v>
+        <v>11137900</v>
       </c>
       <c r="G47" s="3">
-        <v>10371700</v>
+        <v>11236000</v>
       </c>
       <c r="H47" s="3">
-        <v>9213700</v>
+        <v>9981500</v>
       </c>
       <c r="I47" s="3">
-        <v>8690900</v>
+        <v>9415100</v>
       </c>
       <c r="J47" s="3">
-        <v>8664700</v>
+        <v>9386800</v>
       </c>
       <c r="K47" s="3">
         <v>8117900</v>
@@ -3993,25 +3993,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>33603000</v>
+        <v>36403200</v>
       </c>
       <c r="E48" s="3">
-        <v>33590900</v>
+        <v>36390100</v>
       </c>
       <c r="F48" s="3">
-        <v>34514900</v>
+        <v>37391200</v>
       </c>
       <c r="G48" s="3">
-        <v>34547700</v>
+        <v>37426700</v>
       </c>
       <c r="H48" s="3">
-        <v>33150500</v>
+        <v>35913000</v>
       </c>
       <c r="I48" s="3">
-        <v>31348500</v>
+        <v>33960900</v>
       </c>
       <c r="J48" s="3">
-        <v>29836600</v>
+        <v>32323000</v>
       </c>
       <c r="K48" s="3">
         <v>30365200</v>
@@ -4085,25 +4085,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>4868300</v>
+        <v>5273900</v>
       </c>
       <c r="E49" s="3">
-        <v>5020500</v>
+        <v>5438800</v>
       </c>
       <c r="F49" s="3">
-        <v>5416500</v>
+        <v>5867900</v>
       </c>
       <c r="G49" s="3">
-        <v>5581500</v>
+        <v>6046600</v>
       </c>
       <c r="H49" s="3">
-        <v>5342800</v>
+        <v>5788000</v>
       </c>
       <c r="I49" s="3">
-        <v>4921600</v>
+        <v>5331700</v>
       </c>
       <c r="J49" s="3">
-        <v>4599200</v>
+        <v>4982500</v>
       </c>
       <c r="K49" s="3">
         <v>4626800</v>
@@ -4361,25 +4361,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2847400</v>
+        <v>3084700</v>
       </c>
       <c r="E52" s="3">
-        <v>3290200</v>
+        <v>3564400</v>
       </c>
       <c r="F52" s="3">
-        <v>4032900</v>
+        <v>4368900</v>
       </c>
       <c r="G52" s="3">
-        <v>4481300</v>
+        <v>4854700</v>
       </c>
       <c r="H52" s="3">
-        <v>3921700</v>
+        <v>4248500</v>
       </c>
       <c r="I52" s="3">
-        <v>3487100</v>
+        <v>3777700</v>
       </c>
       <c r="J52" s="3">
-        <v>2902900</v>
+        <v>3144900</v>
       </c>
       <c r="K52" s="3">
         <v>3103100</v>
@@ -4545,25 +4545,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>68454700</v>
+        <v>74159200</v>
       </c>
       <c r="E54" s="3">
-        <v>70330900</v>
+        <v>76191800</v>
       </c>
       <c r="F54" s="3">
-        <v>74966800</v>
+        <v>81214000</v>
       </c>
       <c r="G54" s="3">
-        <v>73528700</v>
+        <v>79656100</v>
       </c>
       <c r="H54" s="3">
-        <v>67951600</v>
+        <v>73614300</v>
       </c>
       <c r="I54" s="3">
-        <v>63090500</v>
+        <v>68348000</v>
       </c>
       <c r="J54" s="3">
-        <v>60199300</v>
+        <v>65215900</v>
       </c>
       <c r="K54" s="3">
         <v>58620000</v>
@@ -4705,25 +4705,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2887200</v>
+        <v>3127800</v>
       </c>
       <c r="E57" s="3">
-        <v>2773400</v>
+        <v>3004600</v>
       </c>
       <c r="F57" s="3">
-        <v>3102600</v>
+        <v>3361200</v>
       </c>
       <c r="G57" s="3">
-        <v>3608300</v>
+        <v>3909000</v>
       </c>
       <c r="H57" s="3">
-        <v>2827300</v>
+        <v>3062900</v>
       </c>
       <c r="I57" s="3">
-        <v>2936600</v>
+        <v>3181400</v>
       </c>
       <c r="J57" s="3">
-        <v>2644200</v>
+        <v>2864600</v>
       </c>
       <c r="K57" s="3">
         <v>2512900</v>
@@ -4797,25 +4797,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>4228000</v>
+        <v>4580300</v>
       </c>
       <c r="E58" s="3">
-        <v>4104300</v>
+        <v>4446300</v>
       </c>
       <c r="F58" s="3">
-        <v>3901800</v>
+        <v>4226900</v>
       </c>
       <c r="G58" s="3">
-        <v>5327700</v>
+        <v>5771600</v>
       </c>
       <c r="H58" s="3">
-        <v>5427500</v>
+        <v>5879800</v>
       </c>
       <c r="I58" s="3">
-        <v>2343100</v>
+        <v>2538400</v>
       </c>
       <c r="J58" s="3">
-        <v>2097300</v>
+        <v>2272100</v>
       </c>
       <c r="K58" s="3">
         <v>2209500</v>
@@ -4889,25 +4889,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>5298000</v>
+        <v>5739500</v>
       </c>
       <c r="E59" s="3">
-        <v>8282900</v>
+        <v>8973100</v>
       </c>
       <c r="F59" s="3">
-        <v>11119600</v>
+        <v>12046200</v>
       </c>
       <c r="G59" s="3">
-        <v>4691800</v>
+        <v>5082800</v>
       </c>
       <c r="H59" s="3">
-        <v>4078600</v>
+        <v>4418500</v>
       </c>
       <c r="I59" s="3">
-        <v>4740700</v>
+        <v>5135800</v>
       </c>
       <c r="J59" s="3">
-        <v>5524200</v>
+        <v>5984500</v>
       </c>
       <c r="K59" s="3">
         <v>2537300</v>
@@ -4981,25 +4981,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>12413200</v>
+        <v>13447600</v>
       </c>
       <c r="E60" s="3">
-        <v>15160600</v>
+        <v>16424000</v>
       </c>
       <c r="F60" s="3">
-        <v>18124000</v>
+        <v>19634300</v>
       </c>
       <c r="G60" s="3">
-        <v>13627800</v>
+        <v>14763400</v>
       </c>
       <c r="H60" s="3">
-        <v>12333300</v>
+        <v>13361100</v>
       </c>
       <c r="I60" s="3">
-        <v>10020500</v>
+        <v>10855500</v>
       </c>
       <c r="J60" s="3">
-        <v>10265700</v>
+        <v>11121200</v>
       </c>
       <c r="K60" s="3">
         <v>7259700</v>
@@ -5073,25 +5073,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>22106900</v>
+        <v>23949200</v>
       </c>
       <c r="E61" s="3">
-        <v>21830200</v>
+        <v>23649400</v>
       </c>
       <c r="F61" s="3">
-        <v>24025200</v>
+        <v>26027300</v>
       </c>
       <c r="G61" s="3">
-        <v>22304700</v>
+        <v>24163400</v>
       </c>
       <c r="H61" s="3">
-        <v>20430100</v>
+        <v>22132600</v>
       </c>
       <c r="I61" s="3">
-        <v>21356000</v>
+        <v>23135700</v>
       </c>
       <c r="J61" s="3">
-        <v>19891100</v>
+        <v>21548700</v>
       </c>
       <c r="K61" s="3">
         <v>20605100</v>
@@ -5165,25 +5165,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>8972000</v>
+        <v>9719600</v>
       </c>
       <c r="E62" s="3">
-        <v>8981800</v>
+        <v>9730300</v>
       </c>
       <c r="F62" s="3">
-        <v>8895400</v>
+        <v>9636600</v>
       </c>
       <c r="G62" s="3">
-        <v>9015300</v>
+        <v>9766600</v>
       </c>
       <c r="H62" s="3">
-        <v>9306900</v>
+        <v>10082500</v>
       </c>
       <c r="I62" s="3">
-        <v>8991500</v>
+        <v>9740800</v>
       </c>
       <c r="J62" s="3">
-        <v>8647900</v>
+        <v>9368600</v>
       </c>
       <c r="K62" s="3">
         <v>8254700</v>
@@ -5533,25 +5533,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>49705900</v>
+        <v>53848100</v>
       </c>
       <c r="E66" s="3">
-        <v>52371200</v>
+        <v>56735500</v>
       </c>
       <c r="F66" s="3">
-        <v>57540800</v>
+        <v>62335800</v>
       </c>
       <c r="G66" s="3">
-        <v>51680400</v>
+        <v>55987000</v>
       </c>
       <c r="H66" s="3">
-        <v>48304000</v>
+        <v>52329300</v>
       </c>
       <c r="I66" s="3">
-        <v>46144700</v>
+        <v>49990000</v>
       </c>
       <c r="J66" s="3">
-        <v>44250100</v>
+        <v>47937600</v>
       </c>
       <c r="K66" s="3">
         <v>41404100</v>
@@ -6027,25 +6027,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>8229900</v>
+        <v>8915800</v>
       </c>
       <c r="E72" s="3">
-        <v>7009400</v>
+        <v>7593500</v>
       </c>
       <c r="F72" s="3">
-        <v>6028400</v>
+        <v>6530700</v>
       </c>
       <c r="G72" s="3">
-        <v>10521600</v>
+        <v>11398400</v>
       </c>
       <c r="H72" s="3">
-        <v>8877400</v>
+        <v>9617200</v>
       </c>
       <c r="I72" s="3">
-        <v>6594300</v>
+        <v>7143800</v>
       </c>
       <c r="J72" s="3">
-        <v>5739300</v>
+        <v>6217600</v>
       </c>
       <c r="K72" s="3">
         <v>6914900</v>
@@ -6395,25 +6395,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>18748700</v>
+        <v>20311100</v>
       </c>
       <c r="E76" s="3">
-        <v>17959700</v>
+        <v>19456300</v>
       </c>
       <c r="F76" s="3">
-        <v>17426000</v>
+        <v>18878200</v>
       </c>
       <c r="G76" s="3">
-        <v>21848300</v>
+        <v>23669000</v>
       </c>
       <c r="H76" s="3">
-        <v>19647700</v>
+        <v>21285000</v>
       </c>
       <c r="I76" s="3">
-        <v>16945800</v>
+        <v>18358000</v>
       </c>
       <c r="J76" s="3">
-        <v>15949300</v>
+        <v>17278400</v>
       </c>
       <c r="K76" s="3">
         <v>17215900</v>
@@ -6676,25 +6676,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1220600</v>
+        <v>3859200</v>
       </c>
       <c r="E81" s="3">
-        <v>981000</v>
+        <v>1062700</v>
       </c>
       <c r="F81" s="3">
-        <v>1358500</v>
+        <v>1471700</v>
       </c>
       <c r="G81" s="3">
-        <v>1644200</v>
+        <v>1781200</v>
       </c>
       <c r="H81" s="3">
-        <v>2283100</v>
+        <v>2473300</v>
       </c>
       <c r="I81" s="3">
-        <v>2512800</v>
+        <v>2722200</v>
       </c>
       <c r="J81" s="3">
-        <v>1577400</v>
+        <v>1708900</v>
       </c>
       <c r="K81" s="3">
         <v>1458500</v>
@@ -6802,25 +6802,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>849300</v>
+        <v>2616400</v>
       </c>
       <c r="E83" s="3">
-        <v>806800</v>
+        <v>874000</v>
       </c>
       <c r="F83" s="3">
-        <v>759100</v>
+        <v>822300</v>
       </c>
       <c r="G83" s="3">
-        <v>811100</v>
+        <v>878700</v>
       </c>
       <c r="H83" s="3">
-        <v>764100</v>
+        <v>827800</v>
       </c>
       <c r="I83" s="3">
-        <v>685400</v>
+        <v>742600</v>
       </c>
       <c r="J83" s="3">
-        <v>650300</v>
+        <v>704500</v>
       </c>
       <c r="K83" s="3">
         <v>666200</v>
@@ -7354,25 +7354,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1005600</v>
+        <v>2443700</v>
       </c>
       <c r="E89" s="3">
-        <v>753100</v>
+        <v>815900</v>
       </c>
       <c r="F89" s="3">
-        <v>497000</v>
+        <v>538500</v>
       </c>
       <c r="G89" s="3">
-        <v>2726200</v>
+        <v>2953400</v>
       </c>
       <c r="H89" s="3">
-        <v>3584400</v>
+        <v>3883100</v>
       </c>
       <c r="I89" s="3">
-        <v>1476900</v>
+        <v>1600000</v>
       </c>
       <c r="J89" s="3">
-        <v>908700</v>
+        <v>984400</v>
       </c>
       <c r="K89" s="3">
         <v>2642300</v>
@@ -7756,25 +7756,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-1251700</v>
+        <v>-3499000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1081100</v>
+        <v>-1171200</v>
       </c>
       <c r="F94" s="3">
-        <v>-897000</v>
+        <v>-971800</v>
       </c>
       <c r="G94" s="3">
-        <v>-1689300</v>
+        <v>-1830000</v>
       </c>
       <c r="H94" s="3">
-        <v>-1155700</v>
+        <v>-1252000</v>
       </c>
       <c r="I94" s="3">
-        <v>-831000</v>
+        <v>-900300</v>
       </c>
       <c r="J94" s="3">
-        <v>-666800</v>
+        <v>-722400</v>
       </c>
       <c r="K94" s="3">
         <v>-916800</v>
@@ -7882,25 +7882,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-311800</v>
+        <v>-1003500</v>
       </c>
       <c r="E96" s="3">
-        <v>-560100</v>
+        <v>-606700</v>
       </c>
       <c r="F96" s="3">
-        <v>-54500</v>
+        <v>-59000</v>
       </c>
       <c r="G96" s="3">
-        <v>-520800</v>
+        <v>-564200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1253200</v>
+        <v>-1357600</v>
       </c>
       <c r="I96" s="3">
-        <v>-1366000</v>
+        <v>-1479900</v>
       </c>
       <c r="J96" s="3">
-        <v>-65700</v>
+        <v>-71100</v>
       </c>
       <c r="K96" s="3">
         <v>-323200</v>
@@ -8250,25 +8250,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>486000</v>
+        <v>435100</v>
       </c>
       <c r="E100" s="3">
-        <v>-537200</v>
+        <v>-582000</v>
       </c>
       <c r="F100" s="3">
-        <v>452800</v>
+        <v>490500</v>
       </c>
       <c r="G100" s="3">
-        <v>-627800</v>
+        <v>-680100</v>
       </c>
       <c r="H100" s="3">
-        <v>-1769100</v>
+        <v>-1916600</v>
       </c>
       <c r="I100" s="3">
-        <v>-1776100</v>
+        <v>-1924100</v>
       </c>
       <c r="J100" s="3">
-        <v>-371100</v>
+        <v>-402100</v>
       </c>
       <c r="K100" s="3">
         <v>-734000</v>
@@ -8342,25 +8342,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-60900</v>
+        <v>-245600</v>
       </c>
       <c r="E101" s="3">
-        <v>-136200</v>
+        <v>-147500</v>
       </c>
       <c r="F101" s="3">
-        <v>-29700</v>
+        <v>-32200</v>
       </c>
       <c r="G101" s="3">
-        <v>186800</v>
+        <v>202400</v>
       </c>
       <c r="H101" s="3">
-        <v>15800</v>
+        <v>17100</v>
       </c>
       <c r="I101" s="3">
-        <v>195300</v>
+        <v>211600</v>
       </c>
       <c r="J101" s="3">
-        <v>-3000</v>
+        <v>-3200</v>
       </c>
       <c r="K101" s="3">
         <v>79700</v>
@@ -8434,25 +8434,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>179000</v>
+        <v>-865900</v>
       </c>
       <c r="E102" s="3">
-        <v>-1001400</v>
+        <v>-1084900</v>
       </c>
       <c r="F102" s="3">
-        <v>23100</v>
+        <v>25000</v>
       </c>
       <c r="G102" s="3">
-        <v>596000</v>
+        <v>645700</v>
       </c>
       <c r="H102" s="3">
-        <v>675400</v>
+        <v>731700</v>
       </c>
       <c r="I102" s="3">
-        <v>-934900</v>
+        <v>-1012800</v>
       </c>
       <c r="J102" s="3">
-        <v>-132200</v>
+        <v>-143200</v>
       </c>
       <c r="K102" s="3">
         <v>1071100</v>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -653,410 +653,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>28154100</v>
+        <v>7825400</v>
       </c>
       <c r="E8" s="3">
-        <v>8918000</v>
+        <v>8698600</v>
       </c>
       <c r="F8" s="3">
-        <v>10101900</v>
+        <v>8782600</v>
       </c>
       <c r="G8" s="3">
-        <v>10316300</v>
+        <v>8575000</v>
       </c>
       <c r="H8" s="3">
-        <v>11294000</v>
+        <v>9713400</v>
       </c>
       <c r="I8" s="3">
+        <v>9919500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>10859600</v>
+      </c>
+      <c r="K8" s="3">
         <v>11410100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8442900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7622700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5133200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4083300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3613300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2979900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2957500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2026000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3918700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4831100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4863900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4943300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4304500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>4761700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4826500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>9488900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>18899000</v>
+        <v>4765700</v>
       </c>
       <c r="E9" s="3">
-        <v>5586600</v>
+        <v>5826800</v>
       </c>
       <c r="F9" s="3">
-        <v>5922300</v>
+        <v>5151500</v>
       </c>
       <c r="G9" s="3">
-        <v>6241900</v>
+        <v>5371800</v>
       </c>
       <c r="H9" s="3">
-        <v>6353200</v>
+        <v>5694500</v>
       </c>
       <c r="I9" s="3">
+        <v>6001900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6108800</v>
+      </c>
+      <c r="K9" s="3">
         <v>6000200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4663800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4591800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3191300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2400600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2207500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2164400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2002500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1827700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2934600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3190200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3034900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3027600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2763200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3105100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2868100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>5581200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9255100</v>
+        <v>3059700</v>
       </c>
       <c r="E10" s="3">
-        <v>3331400</v>
+        <v>2871900</v>
       </c>
       <c r="F10" s="3">
-        <v>4179600</v>
+        <v>3631100</v>
       </c>
       <c r="G10" s="3">
-        <v>4074300</v>
+        <v>3203300</v>
       </c>
       <c r="H10" s="3">
-        <v>4940800</v>
+        <v>4018900</v>
       </c>
       <c r="I10" s="3">
+        <v>3917600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4750800</v>
+      </c>
+      <c r="K10" s="3">
         <v>5409900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3779100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3030900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1941900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1682700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1405700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>815500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>955000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>198300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>984100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1641000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1829000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1915700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1541300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1656600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1958400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>3907700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,100 +1113,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>209200</v>
+        <v>89200</v>
       </c>
       <c r="E12" s="3">
-        <v>64900</v>
+        <v>196400</v>
       </c>
       <c r="F12" s="3">
-        <v>64800</v>
+        <v>201200</v>
       </c>
       <c r="G12" s="3">
-        <v>227400</v>
+        <v>62400</v>
       </c>
       <c r="H12" s="3">
-        <v>25900</v>
+        <v>62300</v>
       </c>
       <c r="I12" s="3">
+        <v>218700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K12" s="3">
         <v>115700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>24200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>101600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>66200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>14100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>35300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>86600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>23800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>33600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>9800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>103000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>15700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>66900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>16600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>50300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>271600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>56400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>21200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>292200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>103900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>24700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>8600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>96800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,192 +1305,210 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2900</v>
+        <v>7000</v>
       </c>
       <c r="E14" s="3">
-        <v>9500</v>
+        <v>530900</v>
       </c>
       <c r="F14" s="3">
-        <v>6000</v>
+        <v>2700</v>
       </c>
       <c r="G14" s="3">
-        <v>87900</v>
+        <v>9100</v>
       </c>
       <c r="H14" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>84500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L14" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>400</v>
+      </c>
+      <c r="O14" s="3">
+        <v>500</v>
+      </c>
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="I14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J14" s="3">
-        <v>6800</v>
-      </c>
-      <c r="K14" s="3">
-        <v>24000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>400</v>
-      </c>
-      <c r="M14" s="3">
-        <v>500</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-116500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-328800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>314200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>187600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>10400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>5700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>4100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>149000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-14700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>7900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>244000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>31600</v>
+        <v>30300</v>
       </c>
       <c r="E15" s="3">
-        <v>32000</v>
+        <v>52300</v>
       </c>
       <c r="F15" s="3">
-        <v>39900</v>
+        <v>30400</v>
       </c>
       <c r="G15" s="3">
-        <v>85900</v>
+        <v>30800</v>
       </c>
       <c r="H15" s="3">
-        <v>33200</v>
+        <v>38300</v>
       </c>
       <c r="I15" s="3">
+        <v>82600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>31900</v>
+      </c>
+      <c r="K15" s="3">
         <v>34000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>33800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>89200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>12600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>14100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>13600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>40200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>3100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>12900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>20000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>46000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>10700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>11200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>5400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>7800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>4500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>11500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>6100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>8700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>15000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>10900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>13300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>16400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1488,192 +1538,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>18782100</v>
+        <v>5374800</v>
       </c>
       <c r="E17" s="3">
-        <v>6188400</v>
+        <v>7295400</v>
       </c>
       <c r="F17" s="3">
-        <v>6534500</v>
+        <v>5828600</v>
       </c>
       <c r="G17" s="3">
-        <v>7265500</v>
+        <v>5950400</v>
       </c>
       <c r="H17" s="3">
-        <v>6816300</v>
+        <v>6283200</v>
       </c>
       <c r="I17" s="3">
+        <v>6986100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6554200</v>
+      </c>
+      <c r="K17" s="3">
         <v>6572100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5185200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5129400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3570700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2706400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2455500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2553800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2319800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1827300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3529200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3845900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3321700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3334800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2966200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3593200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3300300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6019600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>9372000</v>
+        <v>2450600</v>
       </c>
       <c r="E18" s="3">
-        <v>2729600</v>
+        <v>1403200</v>
       </c>
       <c r="F18" s="3">
-        <v>3567400</v>
+        <v>2954000</v>
       </c>
       <c r="G18" s="3">
-        <v>3050800</v>
+        <v>2624600</v>
       </c>
       <c r="H18" s="3">
-        <v>4477600</v>
+        <v>3430200</v>
       </c>
       <c r="I18" s="3">
+        <v>2933400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>4305400</v>
+      </c>
+      <c r="K18" s="3">
         <v>4838000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3257700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2493200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1562500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1376900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1157800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>426100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>637700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>198700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>389600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>985200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1542100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1608600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1338300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1168600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1526200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>3469300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>538900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1706,468 +1770,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>499900</v>
+        <v>-21800</v>
       </c>
       <c r="E20" s="3">
-        <v>-51700</v>
+        <v>121500</v>
       </c>
       <c r="F20" s="3">
-        <v>149400</v>
+        <v>300500</v>
       </c>
       <c r="G20" s="3">
-        <v>71200</v>
+        <v>-49700</v>
       </c>
       <c r="H20" s="3">
-        <v>-46500</v>
+        <v>143700</v>
       </c>
       <c r="I20" s="3">
+        <v>68500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-109400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-58100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-21600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>25500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-34100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-8400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>70200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-70500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>31500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-47000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>80100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-31700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>43400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>61300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>83200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>19300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>45700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>26900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>18100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>117200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>291700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>12488300</v>
+        <v>3322000</v>
       </c>
       <c r="E21" s="3">
-        <v>3552000</v>
+        <v>2461900</v>
       </c>
       <c r="F21" s="3">
-        <v>4539100</v>
+        <v>4139200</v>
       </c>
       <c r="G21" s="3">
-        <v>4000700</v>
+        <v>3415300</v>
       </c>
       <c r="H21" s="3">
-        <v>5259000</v>
+        <v>4364500</v>
       </c>
       <c r="I21" s="3">
+        <v>3846900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>5056700</v>
+      </c>
+      <c r="K21" s="3">
         <v>5471100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>3904100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3137800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2179000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1845800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1632900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1019600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1118900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>779700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>922300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1657500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2106000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2217200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1937100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1748700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2104600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>4627400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>1428900</v>
+        <v>429500</v>
       </c>
       <c r="E22" s="3">
-        <v>439300</v>
+        <v>443200</v>
       </c>
       <c r="F22" s="3">
-        <v>452000</v>
+        <v>430700</v>
       </c>
       <c r="G22" s="3">
-        <v>424100</v>
+        <v>422400</v>
       </c>
       <c r="H22" s="3">
-        <v>378500</v>
+        <v>434600</v>
       </c>
       <c r="I22" s="3">
+        <v>407800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>363900</v>
+      </c>
+      <c r="K22" s="3">
         <v>346400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>285600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>294600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>154300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>127500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>117300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>125700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>155400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>156700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>126200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>127000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>128100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>129500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>122000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>183100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>144600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>347900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>171800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>206800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>198200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>153300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>205200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>226800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>8443000</v>
+        <v>1999300</v>
       </c>
       <c r="E23" s="3">
-        <v>2238600</v>
+        <v>1081500</v>
       </c>
       <c r="F23" s="3">
-        <v>3264800</v>
+        <v>2823800</v>
       </c>
       <c r="G23" s="3">
-        <v>2697900</v>
+        <v>2152500</v>
       </c>
       <c r="H23" s="3">
-        <v>4052700</v>
+        <v>3139200</v>
       </c>
       <c r="I23" s="3">
+        <v>2594200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3896800</v>
+      </c>
+      <c r="K23" s="3">
         <v>4382200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2914000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2177000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1433600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1215200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1032100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>370700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>411700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>73500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>216300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>938200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1382300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1522500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1277600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1068600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1401000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>3167100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>806300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>739400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>603800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>3701900</v>
+        <v>730200</v>
       </c>
       <c r="E24" s="3">
-        <v>867300</v>
+        <v>-188200</v>
       </c>
       <c r="F24" s="3">
-        <v>1454200</v>
+        <v>1326800</v>
       </c>
       <c r="G24" s="3">
-        <v>697200</v>
+        <v>834000</v>
       </c>
       <c r="H24" s="3">
-        <v>1330000</v>
+        <v>1398200</v>
       </c>
       <c r="I24" s="3">
+        <v>670400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1278900</v>
+      </c>
+      <c r="K24" s="3">
         <v>1380500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1009800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>495300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>482700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>371200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>322700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>178300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>137100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>91500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-186900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>477900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>505400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>451800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>303400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>589000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1192000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>564000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>457200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>414600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>535100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>396300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>485600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2258,192 +2354,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>4741100</v>
+        <v>1269100</v>
       </c>
       <c r="E26" s="3">
-        <v>1371300</v>
+        <v>1269700</v>
       </c>
       <c r="F26" s="3">
-        <v>1810600</v>
+        <v>1497000</v>
       </c>
       <c r="G26" s="3">
-        <v>2000800</v>
+        <v>1318500</v>
       </c>
       <c r="H26" s="3">
-        <v>2722700</v>
+        <v>1741000</v>
       </c>
       <c r="I26" s="3">
+        <v>1923800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2617900</v>
+      </c>
+      <c r="K26" s="3">
         <v>3001700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1904200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1681700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>951000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>844000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>709400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>192400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>274600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>72400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>124800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1125100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>904500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1017100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>825800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>765200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>811900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1975100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>845100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>391700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>474500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>343200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>118200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>3859200</v>
+        <v>1002900</v>
       </c>
       <c r="E27" s="3">
-        <v>1062700</v>
+        <v>1057100</v>
       </c>
       <c r="F27" s="3">
-        <v>1471700</v>
+        <v>1271500</v>
       </c>
       <c r="G27" s="3">
-        <v>1781200</v>
+        <v>1021900</v>
       </c>
       <c r="H27" s="3">
-        <v>2473300</v>
+        <v>1415100</v>
       </c>
       <c r="I27" s="3">
+        <v>1712700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2378200</v>
+      </c>
+      <c r="K27" s="3">
         <v>2722200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1708900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1458500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>837600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>782100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>648000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>141800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>205200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>6000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>34600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1042300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>813000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>941500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>741000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>688300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>749200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1840300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>784400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>321100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>417500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>283500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>61400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2534,8 +2648,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2626,8 +2746,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2718,8 +2844,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2810,192 +2942,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-499900</v>
+        <v>21800</v>
       </c>
       <c r="E32" s="3">
-        <v>51700</v>
+        <v>-121500</v>
       </c>
       <c r="F32" s="3">
-        <v>-149400</v>
+        <v>-300500</v>
       </c>
       <c r="G32" s="3">
-        <v>-71200</v>
+        <v>49700</v>
       </c>
       <c r="H32" s="3">
-        <v>46500</v>
+        <v>-143700</v>
       </c>
       <c r="I32" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>44700</v>
+      </c>
+      <c r="K32" s="3">
         <v>109400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>58100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>21600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-25500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>34100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>8400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-70200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>70500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-31500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>47000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-80100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>31700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-43400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-61300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-83200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-45700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>58800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>111000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>3859200</v>
+        <v>1002900</v>
       </c>
       <c r="E33" s="3">
-        <v>1062700</v>
+        <v>1057100</v>
       </c>
       <c r="F33" s="3">
-        <v>1471700</v>
+        <v>1271500</v>
       </c>
       <c r="G33" s="3">
-        <v>1781200</v>
+        <v>1021900</v>
       </c>
       <c r="H33" s="3">
-        <v>2473300</v>
+        <v>1415100</v>
       </c>
       <c r="I33" s="3">
+        <v>1712700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2378200</v>
+      </c>
+      <c r="K33" s="3">
         <v>2722200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1708900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1458500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>837600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>782100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>648000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>141800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>205200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>34600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1042300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>813000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>941500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>741000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>688300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>749200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1840300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>784400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>321100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>417500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>283500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>61400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3086,197 +3236,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>3859200</v>
+        <v>1002900</v>
       </c>
       <c r="E35" s="3">
-        <v>1062700</v>
+        <v>1057100</v>
       </c>
       <c r="F35" s="3">
-        <v>1471700</v>
+        <v>1271500</v>
       </c>
       <c r="G35" s="3">
-        <v>1781200</v>
+        <v>1021900</v>
       </c>
       <c r="H35" s="3">
-        <v>2473300</v>
+        <v>1415100</v>
       </c>
       <c r="I35" s="3">
+        <v>1712700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>2378200</v>
+      </c>
+      <c r="K35" s="3">
         <v>2722200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1708900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1458500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>837600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>782100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>648000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>141800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>205200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>34600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1042300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>813000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>941500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>741000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>688300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>749200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1840300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>784400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>321100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>417500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>283500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>61400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3309,8 +3477,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3343,836 +3513,892 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3138400</v>
+        <v>3791700</v>
       </c>
       <c r="E41" s="3">
-        <v>2944500</v>
+        <v>3084000</v>
       </c>
       <c r="F41" s="3">
-        <v>4029300</v>
+        <v>3017700</v>
       </c>
       <c r="G41" s="3">
-        <v>4004300</v>
+        <v>2831200</v>
       </c>
       <c r="H41" s="3">
-        <v>3358600</v>
+        <v>3874300</v>
       </c>
       <c r="I41" s="3">
+        <v>3850300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3229400</v>
+      </c>
+      <c r="K41" s="3">
         <v>2626900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3639800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3492000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2219100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1054500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1404400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1067300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1878900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2219500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2287300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1839700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2446500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1491500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2413200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1641100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1922600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1901200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>573200</v>
+        <v>573700</v>
       </c>
       <c r="E42" s="3">
-        <v>356000</v>
+        <v>602100</v>
       </c>
       <c r="F42" s="3">
-        <v>569300</v>
+        <v>551200</v>
       </c>
       <c r="G42" s="3">
-        <v>434000</v>
+        <v>342300</v>
       </c>
       <c r="H42" s="3">
-        <v>699600</v>
+        <v>547400</v>
       </c>
       <c r="I42" s="3">
+        <v>417300</v>
+      </c>
+      <c r="J42" s="3">
+        <v>672700</v>
+      </c>
+      <c r="K42" s="3">
         <v>431200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>560000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>517100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>467300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>102400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>156800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>506700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>839200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>999800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>247600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>459900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>662000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>906600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1349100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1383500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>2042100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1878800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>12097500</v>
+        <v>11108100</v>
       </c>
       <c r="E43" s="3">
-        <v>13522900</v>
+        <v>10566800</v>
       </c>
       <c r="F43" s="3">
-        <v>14496300</v>
+        <v>11632200</v>
       </c>
       <c r="G43" s="3">
-        <v>12189300</v>
+        <v>13002800</v>
       </c>
       <c r="H43" s="3">
-        <v>10399900</v>
+        <v>13938700</v>
       </c>
       <c r="I43" s="3">
+        <v>11720500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>9999900</v>
+      </c>
+      <c r="K43" s="3">
         <v>9332300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7984900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6087200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5301400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3306500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2555100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1960700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2097900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2059500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1806900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2131500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2049800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2634900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2725700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2538700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2350500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2628100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>2952700</v>
+        <v>2703400</v>
       </c>
       <c r="E44" s="3">
-        <v>2676800</v>
+        <v>2550600</v>
       </c>
       <c r="F44" s="3">
-        <v>2892000</v>
+        <v>2839100</v>
       </c>
       <c r="G44" s="3">
-        <v>3088800</v>
+        <v>2573900</v>
       </c>
       <c r="H44" s="3">
-        <v>2803700</v>
+        <v>2780800</v>
       </c>
       <c r="I44" s="3">
+        <v>2970000</v>
+      </c>
+      <c r="J44" s="3">
+        <v>2695900</v>
+      </c>
+      <c r="K44" s="3">
         <v>3165900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2852700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2015600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1997200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1507200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1345600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1061300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1322500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1208400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1511100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1471100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1594800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1580600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1479100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1326100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1461500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1641500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>461100</v>
+        <v>350900</v>
       </c>
       <c r="E45" s="3">
-        <v>425600</v>
+        <v>350200</v>
       </c>
       <c r="F45" s="3">
-        <v>461100</v>
+        <v>443400</v>
       </c>
       <c r="G45" s="3">
-        <v>375600</v>
+        <v>409200</v>
       </c>
       <c r="H45" s="3">
-        <v>421400</v>
+        <v>443400</v>
       </c>
       <c r="I45" s="3">
+        <v>361100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>405200</v>
+      </c>
+      <c r="K45" s="3">
         <v>306400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>341400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>295100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>358600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>175900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>224100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>199200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>282900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>216900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>304500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>172500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>196300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>144400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>146700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>138600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>131000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>125000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>131300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>125800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>180600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>191400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>169900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>140500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>19222900</v>
+        <v>18527800</v>
       </c>
       <c r="E46" s="3">
-        <v>19925800</v>
+        <v>17153800</v>
       </c>
       <c r="F46" s="3">
-        <v>22448100</v>
+        <v>18483600</v>
       </c>
       <c r="G46" s="3">
-        <v>20092000</v>
+        <v>19159400</v>
       </c>
       <c r="H46" s="3">
-        <v>17683200</v>
+        <v>21584700</v>
       </c>
       <c r="I46" s="3">
+        <v>19319200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>17003100</v>
+      </c>
+      <c r="K46" s="3">
         <v>15862700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>15378800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12407000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10343600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6146600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5686000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4795200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6421200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6704100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6157500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>6074800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>6949500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>6758000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>8113900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>7028000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>7907800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>8174700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>10174500</v>
+        <v>9582400</v>
       </c>
       <c r="E47" s="3">
-        <v>10872700</v>
+        <v>9642900</v>
       </c>
       <c r="F47" s="3">
-        <v>11137900</v>
+        <v>9783200</v>
       </c>
       <c r="G47" s="3">
-        <v>11236000</v>
+        <v>10454500</v>
       </c>
       <c r="H47" s="3">
-        <v>9981500</v>
+        <v>10709500</v>
       </c>
       <c r="I47" s="3">
+        <v>10803900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>9597600</v>
+      </c>
+      <c r="K47" s="3">
         <v>9415100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>9386800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>8117900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>7244100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1100900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1015100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>992900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1208900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1451100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1642600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1920700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1956400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1743300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1335500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1410900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1531900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1627300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>36403200</v>
+        <v>35477300</v>
       </c>
       <c r="E48" s="3">
-        <v>36390100</v>
+        <v>35307300</v>
       </c>
       <c r="F48" s="3">
-        <v>37391200</v>
+        <v>35003100</v>
       </c>
       <c r="G48" s="3">
-        <v>37426700</v>
+        <v>34990500</v>
       </c>
       <c r="H48" s="3">
-        <v>35913000</v>
+        <v>35953100</v>
       </c>
       <c r="I48" s="3">
+        <v>35987200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>34531700</v>
+      </c>
+      <c r="K48" s="3">
         <v>33960900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>32323000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>30365200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25704900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>21623400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21324800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>20752300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>24092400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>23977800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>26598600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>24369500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>24227100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>23212000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>23085100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>22319900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>22118800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>24635700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>5273900</v>
+        <v>4836200</v>
       </c>
       <c r="E49" s="3">
-        <v>5438800</v>
+        <v>4830300</v>
       </c>
       <c r="F49" s="3">
-        <v>5867900</v>
+        <v>5071100</v>
       </c>
       <c r="G49" s="3">
-        <v>6046600</v>
+        <v>5229600</v>
       </c>
       <c r="H49" s="3">
-        <v>5788000</v>
+        <v>5642200</v>
       </c>
       <c r="I49" s="3">
+        <v>5814100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>5565400</v>
+      </c>
+      <c r="K49" s="3">
         <v>5331700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4982500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4626800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>6636400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>407900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>402700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>400900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>460900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>357200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>397400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>364700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>355300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>354900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>361500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>345800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>354300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>383600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>384100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>415900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>404900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>375200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>380300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>393200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4263,8 +4489,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4355,100 +4587,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>3084700</v>
+        <v>3747400</v>
       </c>
       <c r="E52" s="3">
-        <v>3564400</v>
+        <v>3636000</v>
       </c>
       <c r="F52" s="3">
-        <v>4368900</v>
+        <v>2966000</v>
       </c>
       <c r="G52" s="3">
-        <v>4854700</v>
+        <v>3427300</v>
       </c>
       <c r="H52" s="3">
-        <v>4248500</v>
+        <v>4200900</v>
       </c>
       <c r="I52" s="3">
+        <v>4668000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4085100</v>
+      </c>
+      <c r="K52" s="3">
         <v>3777700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3144900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3103100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3142400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2484600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2427200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2336300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2923900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2825800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3302800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2486900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1880600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1713700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1711100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1717900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1535300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1653700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4539,100 +4783,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>74159200</v>
+        <v>72171100</v>
       </c>
       <c r="E54" s="3">
-        <v>76191800</v>
+        <v>70570100</v>
       </c>
       <c r="F54" s="3">
-        <v>81214000</v>
+        <v>71307000</v>
       </c>
       <c r="G54" s="3">
-        <v>79656100</v>
+        <v>73261300</v>
       </c>
       <c r="H54" s="3">
-        <v>73614300</v>
+        <v>78090400</v>
       </c>
       <c r="I54" s="3">
+        <v>76592400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>70783000</v>
+      </c>
+      <c r="K54" s="3">
         <v>68348000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>65215900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>58620000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>53071400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>31763400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>30855800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>29277600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35107300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35316000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>38098900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>35216500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>35368900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>33781800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>34607100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>32822600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>33448100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>36475000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4665,8 +4921,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4699,560 +4957,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>3127800</v>
+        <v>2925200</v>
       </c>
       <c r="E57" s="3">
-        <v>3004600</v>
+        <v>3426200</v>
       </c>
       <c r="F57" s="3">
-        <v>3361200</v>
+        <v>3007500</v>
       </c>
       <c r="G57" s="3">
-        <v>3909000</v>
+        <v>2889000</v>
       </c>
       <c r="H57" s="3">
-        <v>3062900</v>
+        <v>3231900</v>
       </c>
       <c r="I57" s="3">
+        <v>3758700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2945100</v>
+      </c>
+      <c r="K57" s="3">
         <v>3181400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2864600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2512900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1848600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1513700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1410300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1363300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1292100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1131100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1753800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2109900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1923100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1823000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1658600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1788400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1669000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1569200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>4580300</v>
+        <v>3838300</v>
       </c>
       <c r="E58" s="3">
-        <v>4446300</v>
+        <v>3887500</v>
       </c>
       <c r="F58" s="3">
-        <v>4226900</v>
+        <v>4404100</v>
       </c>
       <c r="G58" s="3">
-        <v>5771600</v>
+        <v>4275300</v>
       </c>
       <c r="H58" s="3">
-        <v>5879800</v>
+        <v>4064300</v>
       </c>
       <c r="I58" s="3">
+        <v>5549600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5653600</v>
+      </c>
+      <c r="K58" s="3">
         <v>2538400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2272100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2209500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1903900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1117900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1093400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1033900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1497800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2281900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1593000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1303200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1221700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1103800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1091500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1045200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>2169300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1703100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>5739500</v>
+        <v>7389400</v>
       </c>
       <c r="E59" s="3">
-        <v>8973100</v>
+        <v>3577100</v>
       </c>
       <c r="F59" s="3">
-        <v>12046200</v>
+        <v>5518800</v>
       </c>
       <c r="G59" s="3">
-        <v>5082800</v>
+        <v>8628000</v>
       </c>
       <c r="H59" s="3">
-        <v>4418500</v>
+        <v>11582900</v>
       </c>
       <c r="I59" s="3">
+        <v>4887300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4248500</v>
+      </c>
+      <c r="K59" s="3">
         <v>5135800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5984500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2537300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2381300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1427600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1688500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1442100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2328000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2975500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4170100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2239900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1948300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2444200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>4481500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1800800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2086300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2384800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>13447600</v>
+        <v>14152900</v>
       </c>
       <c r="E60" s="3">
-        <v>16424000</v>
+        <v>10890800</v>
       </c>
       <c r="F60" s="3">
-        <v>19634300</v>
+        <v>12930400</v>
       </c>
       <c r="G60" s="3">
-        <v>14763400</v>
+        <v>15792300</v>
       </c>
       <c r="H60" s="3">
-        <v>13361100</v>
+        <v>18879200</v>
       </c>
       <c r="I60" s="3">
+        <v>14195600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>12847200</v>
+      </c>
+      <c r="K60" s="3">
         <v>10855500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11121200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7259700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6133800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4059200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4192300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3839300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5117900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6388500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7517000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5653000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5093100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5371000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>7231700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4634400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5924600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>5657100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>23949200</v>
+        <v>23340400</v>
       </c>
       <c r="E61" s="3">
-        <v>23649400</v>
+        <v>22566400</v>
       </c>
       <c r="F61" s="3">
-        <v>26027300</v>
+        <v>23028000</v>
       </c>
       <c r="G61" s="3">
-        <v>24163400</v>
+        <v>22739800</v>
       </c>
       <c r="H61" s="3">
-        <v>22132600</v>
+        <v>25026200</v>
       </c>
       <c r="I61" s="3">
+        <v>23234100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>21281400</v>
+      </c>
+      <c r="K61" s="3">
         <v>23135700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>21548700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>20605100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>18309500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9394800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9384300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8779800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11336200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10598900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>10485200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>8639000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>9688200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>9012400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>9095000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>8851100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>8601200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>10695600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>9719600</v>
+        <v>11385100</v>
       </c>
       <c r="E62" s="3">
-        <v>9730300</v>
+        <v>11338200</v>
       </c>
       <c r="F62" s="3">
-        <v>9636600</v>
+        <v>9345800</v>
       </c>
       <c r="G62" s="3">
-        <v>9766600</v>
+        <v>9356000</v>
       </c>
       <c r="H62" s="3">
-        <v>10082500</v>
+        <v>9266000</v>
       </c>
       <c r="I62" s="3">
+        <v>9391000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>9694700</v>
+      </c>
+      <c r="K62" s="3">
         <v>9740800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9368600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>8254700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>7994800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5164400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5067400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4936500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4931700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4975800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5437900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5235000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4019500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4026100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4060300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3917900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>4026500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>4451000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5343,8 +5639,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5435,8 +5737,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5527,100 +5835,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>53848100</v>
+        <v>54861400</v>
       </c>
       <c r="E66" s="3">
-        <v>56735500</v>
+        <v>50972100</v>
       </c>
       <c r="F66" s="3">
-        <v>62335800</v>
+        <v>51777000</v>
       </c>
       <c r="G66" s="3">
-        <v>55987000</v>
+        <v>54553300</v>
       </c>
       <c r="H66" s="3">
-        <v>52329300</v>
+        <v>59938300</v>
       </c>
       <c r="I66" s="3">
+        <v>53833700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>50316600</v>
+      </c>
+      <c r="K66" s="3">
         <v>49990000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>47937600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>41404100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>39212600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19406800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>19405700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>18337600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>22287100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>22919800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>24429400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>20549300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19382000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>19002400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>20923200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>17947000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>19039000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>21376300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5653,8 +5973,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5745,8 +6067,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5837,8 +6165,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5929,8 +6263,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6021,100 +6361,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>8915800</v>
+        <v>7425700</v>
       </c>
       <c r="E72" s="3">
-        <v>7593500</v>
+        <v>9630000</v>
       </c>
       <c r="F72" s="3">
-        <v>6530700</v>
+        <v>8572900</v>
       </c>
       <c r="G72" s="3">
-        <v>11398400</v>
+        <v>7301400</v>
       </c>
       <c r="H72" s="3">
-        <v>9617200</v>
+        <v>6279500</v>
       </c>
       <c r="I72" s="3">
+        <v>10960000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>9247300</v>
+      </c>
+      <c r="K72" s="3">
         <v>7143800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>6217600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6914900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4951900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3927300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3144800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2643400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2859000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2653800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2868400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>4758100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>4799200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3986200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3044700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>4623800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>4086800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3708300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6205,8 +6557,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6297,8 +6655,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6389,100 +6753,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>20311100</v>
+        <v>17309800</v>
       </c>
       <c r="E76" s="3">
-        <v>19456300</v>
+        <v>19598000</v>
       </c>
       <c r="F76" s="3">
-        <v>18878200</v>
+        <v>19529900</v>
       </c>
       <c r="G76" s="3">
-        <v>23669000</v>
+        <v>18708000</v>
       </c>
       <c r="H76" s="3">
-        <v>21285000</v>
+        <v>18152100</v>
       </c>
       <c r="I76" s="3">
+        <v>22758700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>20466300</v>
+      </c>
+      <c r="K76" s="3">
         <v>18358000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>17278400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>17215900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13858900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12356600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11450100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10940000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>12820300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12396200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>13669400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>14667200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>15986900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14779400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>13683900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14875500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>14409100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>15098700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6573,197 +6949,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>3859200</v>
+        <v>1002900</v>
       </c>
       <c r="E81" s="3">
-        <v>1062700</v>
+        <v>1057100</v>
       </c>
       <c r="F81" s="3">
-        <v>1471700</v>
+        <v>1271500</v>
       </c>
       <c r="G81" s="3">
-        <v>1781200</v>
+        <v>1021900</v>
       </c>
       <c r="H81" s="3">
-        <v>2473300</v>
+        <v>1415100</v>
       </c>
       <c r="I81" s="3">
+        <v>1712700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>2378200</v>
+      </c>
+      <c r="K81" s="3">
         <v>2722200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1708900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1458500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>837600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>782100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>648000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>141800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>205200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>34600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1042300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>813000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>941500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>741000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>688300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>749200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1840300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>784400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>321100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>417500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>283500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>61400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6796,100 +7190,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>2616400</v>
+        <v>893200</v>
       </c>
       <c r="E83" s="3">
-        <v>874000</v>
+        <v>937300</v>
       </c>
       <c r="F83" s="3">
-        <v>822300</v>
+        <v>884700</v>
       </c>
       <c r="G83" s="3">
-        <v>878700</v>
+        <v>840400</v>
       </c>
       <c r="H83" s="3">
-        <v>827800</v>
+        <v>790700</v>
       </c>
       <c r="I83" s="3">
+        <v>844900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>796000</v>
+      </c>
+      <c r="K83" s="3">
         <v>742600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>704500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>666200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>591000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>503100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>483400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>523300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>551700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>549500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>579700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>592200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>595600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>565200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>537500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>497000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>559000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1112400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>537300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>588000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>713800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>683300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>660300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>634300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6980,8 +7382,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7072,8 +7480,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7164,8 +7578,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7256,8 +7676,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7348,100 +7774,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>2443700</v>
+        <v>1503600</v>
       </c>
       <c r="E89" s="3">
-        <v>815900</v>
+        <v>2600400</v>
       </c>
       <c r="F89" s="3">
-        <v>538500</v>
+        <v>1047500</v>
       </c>
       <c r="G89" s="3">
-        <v>2953400</v>
+        <v>784500</v>
       </c>
       <c r="H89" s="3">
-        <v>3883100</v>
+        <v>517800</v>
       </c>
       <c r="I89" s="3">
+        <v>2839800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>3733800</v>
+      </c>
+      <c r="K89" s="3">
         <v>1600000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>984400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2642300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1161500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>695900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>616000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1120400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>846400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-539500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>668800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1966900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2513500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1620900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1305300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1176500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2309500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2794100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>478900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7474,100 +7912,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-4273868000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-7224436000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6158165000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-5554360000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-5153955000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-295700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-178500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-359700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-320800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-278300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-214000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-385700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-324300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-196700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-161900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-358000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-220300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-333000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7658,8 +8104,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7750,100 +8202,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-3499000</v>
+        <v>-1002400</v>
       </c>
       <c r="E94" s="3">
-        <v>-1171200</v>
+        <v>-1640500</v>
       </c>
       <c r="F94" s="3">
-        <v>-971800</v>
+        <v>-1303800</v>
       </c>
       <c r="G94" s="3">
-        <v>-1830000</v>
+        <v>-1126200</v>
       </c>
       <c r="H94" s="3">
-        <v>-1252000</v>
+        <v>-934400</v>
       </c>
       <c r="I94" s="3">
+        <v>-1759700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1203900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-900300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-722400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-916800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-552000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-145300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-462600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-224600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-712600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-475200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-293400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>130100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-973300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -7876,100 +8340,108 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-1003500</v>
+        <v>-67700</v>
       </c>
       <c r="E96" s="3">
-        <v>-606700</v>
+        <v>-427800</v>
       </c>
       <c r="F96" s="3">
-        <v>-59000</v>
+        <v>-324800</v>
       </c>
       <c r="G96" s="3">
-        <v>-564200</v>
+        <v>-583400</v>
       </c>
       <c r="H96" s="3">
-        <v>-1357600</v>
+        <v>-56700</v>
       </c>
       <c r="I96" s="3">
+        <v>-542500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-1305400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-71100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-323200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-60300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-206300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-35300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-732400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-698500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-458600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-110700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-990600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-832000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-89800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-36500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-494600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-736600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8060,8 +8532,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8152,8 +8630,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8244,280 +8728,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>435100</v>
+        <v>151200</v>
       </c>
       <c r="E100" s="3">
-        <v>-582000</v>
+        <v>-507000</v>
       </c>
       <c r="F100" s="3">
-        <v>490500</v>
+        <v>506200</v>
       </c>
       <c r="G100" s="3">
-        <v>-680100</v>
+        <v>-559600</v>
       </c>
       <c r="H100" s="3">
-        <v>-1916600</v>
+        <v>471700</v>
       </c>
       <c r="I100" s="3">
+        <v>-653900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1842900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-402100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-734000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2906600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-507400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-163600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>2061800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-266700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-954100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-274300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-245600</v>
+        <v>55200</v>
       </c>
       <c r="E101" s="3">
-        <v>-147500</v>
+        <v>-386600</v>
       </c>
       <c r="F101" s="3">
-        <v>-32200</v>
+        <v>-63400</v>
       </c>
       <c r="G101" s="3">
-        <v>202400</v>
+        <v>-141800</v>
       </c>
       <c r="H101" s="3">
-        <v>17100</v>
+        <v>-31000</v>
       </c>
       <c r="I101" s="3">
+        <v>194600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>16500</v>
+      </c>
+      <c r="K101" s="3">
         <v>211600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>79700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-10700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>13700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>30000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-99000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-144100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>270100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-38800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>108200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>30500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-28500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>107900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>51800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-60100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>9800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>69600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>51000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-865900</v>
+        <v>707700</v>
       </c>
       <c r="E102" s="3">
-        <v>-1084900</v>
+        <v>66300</v>
       </c>
       <c r="F102" s="3">
-        <v>25000</v>
+        <v>186500</v>
       </c>
       <c r="G102" s="3">
-        <v>645700</v>
+        <v>-1043100</v>
       </c>
       <c r="H102" s="3">
-        <v>731700</v>
+        <v>24100</v>
       </c>
       <c r="I102" s="3">
+        <v>620800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>703500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-143200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1071100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1114400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-349900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>337100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-576700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-340600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>108200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>447600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-516200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>955000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-921700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>709100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-210300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>211400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-482500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>30000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>513900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>230300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -653,434 +653,446 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7825400</v>
+        <v>7830500</v>
       </c>
       <c r="E8" s="3">
-        <v>8698600</v>
+        <v>7512400</v>
       </c>
       <c r="F8" s="3">
-        <v>8782600</v>
+        <v>8350700</v>
       </c>
       <c r="G8" s="3">
-        <v>8575000</v>
+        <v>8431300</v>
       </c>
       <c r="H8" s="3">
-        <v>9713400</v>
+        <v>8232000</v>
       </c>
       <c r="I8" s="3">
-        <v>9919500</v>
+        <v>9324900</v>
       </c>
       <c r="J8" s="3">
+        <v>9522700</v>
+      </c>
+      <c r="K8" s="3">
         <v>10859600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11410100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8442900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7622700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5133200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4083300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3613300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2979900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2957500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2026000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3918700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4831100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4863900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4943300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4304500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4761700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4765700</v>
+        <v>4939400</v>
       </c>
       <c r="E9" s="3">
-        <v>5826800</v>
+        <v>4575100</v>
       </c>
       <c r="F9" s="3">
-        <v>5151500</v>
+        <v>5593700</v>
       </c>
       <c r="G9" s="3">
-        <v>5371800</v>
+        <v>4945400</v>
       </c>
       <c r="H9" s="3">
-        <v>5694500</v>
+        <v>5156900</v>
       </c>
       <c r="I9" s="3">
-        <v>6001900</v>
+        <v>5466800</v>
       </c>
       <c r="J9" s="3">
+        <v>5761800</v>
+      </c>
+      <c r="K9" s="3">
         <v>6108800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6000200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4663800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4591800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3191300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2400600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2207500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2164400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2002500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1827700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2934600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3190200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3034900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3027600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2763200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3105100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3059700</v>
+        <v>2891200</v>
       </c>
       <c r="E10" s="3">
-        <v>2871900</v>
+        <v>2937300</v>
       </c>
       <c r="F10" s="3">
-        <v>3631100</v>
+        <v>2757000</v>
       </c>
       <c r="G10" s="3">
-        <v>3203300</v>
+        <v>3485900</v>
       </c>
       <c r="H10" s="3">
-        <v>4018900</v>
+        <v>3075100</v>
       </c>
       <c r="I10" s="3">
-        <v>3917600</v>
+        <v>3858100</v>
       </c>
       <c r="J10" s="3">
+        <v>3760900</v>
+      </c>
+      <c r="K10" s="3">
         <v>4750800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5409900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3779100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3030900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1941900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1682700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1405700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>815500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>955000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>198300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>984100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1641000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1829000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1915700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1541300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1656600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,106 +1127,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>89200</v>
+        <v>112300</v>
       </c>
       <c r="E12" s="3">
-        <v>196400</v>
+        <v>85700</v>
       </c>
       <c r="F12" s="3">
-        <v>201200</v>
+        <v>188500</v>
       </c>
       <c r="G12" s="3">
-        <v>62400</v>
+        <v>193100</v>
       </c>
       <c r="H12" s="3">
-        <v>62300</v>
+        <v>59900</v>
       </c>
       <c r="I12" s="3">
-        <v>218700</v>
+        <v>59800</v>
       </c>
       <c r="J12" s="3">
+        <v>209900</v>
+      </c>
+      <c r="K12" s="3">
         <v>24900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>115700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>101600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>66200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>35300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>86600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>33600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>103000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>15700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>66900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>50300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>271600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>56400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>21200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>292200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>103900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>24700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>96800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1311,204 +1327,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>7000</v>
+        <v>4900</v>
       </c>
       <c r="E14" s="3">
-        <v>530900</v>
+        <v>6800</v>
       </c>
       <c r="F14" s="3">
+        <v>509700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J14" s="3">
+        <v>81100</v>
+      </c>
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="G14" s="3">
-        <v>9100</v>
-      </c>
-      <c r="H14" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I14" s="3">
-        <v>84500</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>24000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-116500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-328800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>314200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>187600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>149000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>244000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>30300</v>
+        <v>28700</v>
       </c>
       <c r="E15" s="3">
-        <v>52300</v>
+        <v>29100</v>
       </c>
       <c r="F15" s="3">
-        <v>30400</v>
+        <v>50200</v>
       </c>
       <c r="G15" s="3">
-        <v>30800</v>
+        <v>29200</v>
       </c>
       <c r="H15" s="3">
-        <v>38300</v>
+        <v>29500</v>
       </c>
       <c r="I15" s="3">
-        <v>82600</v>
+        <v>36800</v>
       </c>
       <c r="J15" s="3">
+        <v>79300</v>
+      </c>
+      <c r="K15" s="3">
         <v>31900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>89200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>40200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>20000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>46000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>10700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>11200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>7800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>6100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>15000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>10900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>13300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>16400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1540,204 +1565,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5374800</v>
+        <v>5542200</v>
       </c>
       <c r="E17" s="3">
-        <v>7295400</v>
+        <v>5159800</v>
       </c>
       <c r="F17" s="3">
-        <v>5828600</v>
+        <v>7003600</v>
       </c>
       <c r="G17" s="3">
-        <v>5950400</v>
+        <v>5595500</v>
       </c>
       <c r="H17" s="3">
-        <v>6283200</v>
+        <v>5712400</v>
       </c>
       <c r="I17" s="3">
-        <v>6986100</v>
+        <v>6031900</v>
       </c>
       <c r="J17" s="3">
+        <v>6706600</v>
+      </c>
+      <c r="K17" s="3">
         <v>6554200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6572100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5185200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5129400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3570700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2706400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2455500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2553800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2319800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1827300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3529200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3845900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3321700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3334800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2966200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3593200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2450600</v>
+        <v>2288300</v>
       </c>
       <c r="E18" s="3">
-        <v>1403200</v>
+        <v>2352600</v>
       </c>
       <c r="F18" s="3">
-        <v>2954000</v>
+        <v>1347100</v>
       </c>
       <c r="G18" s="3">
-        <v>2624600</v>
+        <v>2835900</v>
       </c>
       <c r="H18" s="3">
-        <v>3430200</v>
+        <v>2519600</v>
       </c>
       <c r="I18" s="3">
-        <v>2933400</v>
+        <v>3293000</v>
       </c>
       <c r="J18" s="3">
+        <v>2816100</v>
+      </c>
+      <c r="K18" s="3">
         <v>4305400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4838000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3257700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2493200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1562500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1376900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1157800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>426100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>637700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>198700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>389600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>985200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1542100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1608600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1338300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1168600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>538900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1772,498 +1804,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-21800</v>
+        <v>-29300</v>
       </c>
       <c r="E20" s="3">
-        <v>121500</v>
+        <v>-20900</v>
       </c>
       <c r="F20" s="3">
-        <v>300500</v>
+        <v>116600</v>
       </c>
       <c r="G20" s="3">
-        <v>-49700</v>
+        <v>288500</v>
       </c>
       <c r="H20" s="3">
-        <v>143700</v>
+        <v>-47700</v>
       </c>
       <c r="I20" s="3">
-        <v>68500</v>
+        <v>137900</v>
       </c>
       <c r="J20" s="3">
+        <v>65800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-44700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-109400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-58100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-34100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>70200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-70500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>31500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-47000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>80100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-31700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>43400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>61300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>83200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>45700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>26900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>18100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>117200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>291700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3322000</v>
+        <v>3150300</v>
       </c>
       <c r="E21" s="3">
-        <v>2461900</v>
+        <v>3189200</v>
       </c>
       <c r="F21" s="3">
-        <v>4139200</v>
+        <v>2363500</v>
       </c>
       <c r="G21" s="3">
-        <v>3415300</v>
+        <v>3973700</v>
       </c>
       <c r="H21" s="3">
-        <v>4364500</v>
+        <v>3278700</v>
       </c>
       <c r="I21" s="3">
-        <v>3846900</v>
+        <v>4190000</v>
       </c>
       <c r="J21" s="3">
+        <v>3693000</v>
+      </c>
+      <c r="K21" s="3">
         <v>5056700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5471100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3904100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3137800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2179000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1845800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1632900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1019600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1118900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>779700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>922300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1657500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2106000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2217200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1937100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1748700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>429500</v>
+        <v>426800</v>
       </c>
       <c r="E22" s="3">
-        <v>443200</v>
+        <v>412400</v>
       </c>
       <c r="F22" s="3">
-        <v>430700</v>
+        <v>425500</v>
       </c>
       <c r="G22" s="3">
-        <v>422400</v>
+        <v>413500</v>
       </c>
       <c r="H22" s="3">
-        <v>434600</v>
+        <v>405500</v>
       </c>
       <c r="I22" s="3">
-        <v>407800</v>
+        <v>417200</v>
       </c>
       <c r="J22" s="3">
+        <v>391500</v>
+      </c>
+      <c r="K22" s="3">
         <v>363900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>346400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>285600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>294600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>154300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>127500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>117300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>125700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>155400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>156700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>126200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>127000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>128100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>129500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>122000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>183100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>144600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>347900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>171800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>206800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>198200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>153300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>205200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>226800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1999300</v>
+        <v>1832200</v>
       </c>
       <c r="E23" s="3">
-        <v>1081500</v>
+        <v>1919300</v>
       </c>
       <c r="F23" s="3">
-        <v>2823800</v>
+        <v>1038200</v>
       </c>
       <c r="G23" s="3">
-        <v>2152500</v>
+        <v>2710900</v>
       </c>
       <c r="H23" s="3">
-        <v>3139200</v>
+        <v>2066400</v>
       </c>
       <c r="I23" s="3">
-        <v>2594200</v>
+        <v>3013700</v>
       </c>
       <c r="J23" s="3">
+        <v>2490400</v>
+      </c>
+      <c r="K23" s="3">
         <v>3896800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4382200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2914000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2177000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1433600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1215200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1032100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>370700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>411700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>216300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>938200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1382300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1522500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1277600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1068600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>806300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>739400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>603800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>730200</v>
+        <v>776100</v>
       </c>
       <c r="E24" s="3">
-        <v>-188200</v>
+        <v>701000</v>
       </c>
       <c r="F24" s="3">
-        <v>1326800</v>
+        <v>-180700</v>
       </c>
       <c r="G24" s="3">
-        <v>834000</v>
+        <v>1273700</v>
       </c>
       <c r="H24" s="3">
-        <v>1398200</v>
+        <v>800600</v>
       </c>
       <c r="I24" s="3">
-        <v>670400</v>
+        <v>1342300</v>
       </c>
       <c r="J24" s="3">
+        <v>643600</v>
+      </c>
+      <c r="K24" s="3">
         <v>1278900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1380500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1009800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>495300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>482700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>371200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>322700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>178300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>137100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>91500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-186900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>477900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>505400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>451800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>303400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>589000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>564000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>457200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>414600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>535100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>396300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>485600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2360,204 +2408,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1269100</v>
+        <v>1056100</v>
       </c>
       <c r="E26" s="3">
-        <v>1269700</v>
+        <v>1218300</v>
       </c>
       <c r="F26" s="3">
-        <v>1497000</v>
+        <v>1218900</v>
       </c>
       <c r="G26" s="3">
-        <v>1318500</v>
+        <v>1437100</v>
       </c>
       <c r="H26" s="3">
-        <v>1741000</v>
+        <v>1265800</v>
       </c>
       <c r="I26" s="3">
-        <v>1923800</v>
+        <v>1671400</v>
       </c>
       <c r="J26" s="3">
+        <v>1846800</v>
+      </c>
+      <c r="K26" s="3">
         <v>2617900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3001700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1904200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1681700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>951000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>844000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>709400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>192400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>274600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>72400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>124800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1125100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>904500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1017100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>825800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>765200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>811900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>845100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>391700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>474500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>343200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>118200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1002900</v>
+        <v>810200</v>
       </c>
       <c r="E27" s="3">
-        <v>1057100</v>
+        <v>962800</v>
       </c>
       <c r="F27" s="3">
-        <v>1271500</v>
+        <v>1014800</v>
       </c>
       <c r="G27" s="3">
-        <v>1021900</v>
+        <v>1220600</v>
       </c>
       <c r="H27" s="3">
-        <v>1415100</v>
+        <v>981000</v>
       </c>
       <c r="I27" s="3">
-        <v>1712700</v>
+        <v>1358500</v>
       </c>
       <c r="J27" s="3">
+        <v>1644200</v>
+      </c>
+      <c r="K27" s="3">
         <v>2378200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2722200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1708900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1458500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>837600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>782100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>648000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>141800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>205200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>34600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1042300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>813000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>941500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>741000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>688300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>749200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>784400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>321100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>417500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>283500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>61400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2654,8 +2711,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2752,8 +2812,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2850,8 +2913,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2948,204 +3014,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>21800</v>
+        <v>29300</v>
       </c>
       <c r="E32" s="3">
-        <v>-121500</v>
+        <v>20900</v>
       </c>
       <c r="F32" s="3">
-        <v>-300500</v>
+        <v>-116600</v>
       </c>
       <c r="G32" s="3">
-        <v>49700</v>
+        <v>-288500</v>
       </c>
       <c r="H32" s="3">
-        <v>-143700</v>
+        <v>47700</v>
       </c>
       <c r="I32" s="3">
-        <v>-68500</v>
+        <v>-137900</v>
       </c>
       <c r="J32" s="3">
+        <v>-65800</v>
+      </c>
+      <c r="K32" s="3">
         <v>44700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>109400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>58100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>34100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-70200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>70500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-31500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>47000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-80100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>31700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-43400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-61300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-83200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>58800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>111000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1002900</v>
+        <v>810200</v>
       </c>
       <c r="E33" s="3">
-        <v>1057100</v>
+        <v>962800</v>
       </c>
       <c r="F33" s="3">
-        <v>1271500</v>
+        <v>1014800</v>
       </c>
       <c r="G33" s="3">
-        <v>1021900</v>
+        <v>1220600</v>
       </c>
       <c r="H33" s="3">
-        <v>1415100</v>
+        <v>981000</v>
       </c>
       <c r="I33" s="3">
-        <v>1712700</v>
+        <v>1358500</v>
       </c>
       <c r="J33" s="3">
+        <v>1644200</v>
+      </c>
+      <c r="K33" s="3">
         <v>2378200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2722200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1708900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1458500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>837600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>782100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>648000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>141800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>34600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1042300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>813000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>941500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>741000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>688300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>749200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>784400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>321100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>417500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>283500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>61400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3242,209 +3317,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1002900</v>
+        <v>810200</v>
       </c>
       <c r="E35" s="3">
-        <v>1057100</v>
+        <v>962800</v>
       </c>
       <c r="F35" s="3">
-        <v>1271500</v>
+        <v>1014800</v>
       </c>
       <c r="G35" s="3">
-        <v>1021900</v>
+        <v>1220600</v>
       </c>
       <c r="H35" s="3">
-        <v>1415100</v>
+        <v>981000</v>
       </c>
       <c r="I35" s="3">
-        <v>1712700</v>
+        <v>1358500</v>
       </c>
       <c r="J35" s="3">
+        <v>1644200</v>
+      </c>
+      <c r="K35" s="3">
         <v>2378200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2722200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1708900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1458500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>837600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>782100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>648000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>141800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>34600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1042300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>813000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>941500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>741000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>688300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>749200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>784400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>321100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>417500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>283500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>61400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3479,8 +3563,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3515,890 +3600,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3791700</v>
+        <v>3176900</v>
       </c>
       <c r="E41" s="3">
-        <v>3084000</v>
+        <v>3640100</v>
       </c>
       <c r="F41" s="3">
-        <v>3017700</v>
+        <v>2960700</v>
       </c>
       <c r="G41" s="3">
-        <v>2831200</v>
+        <v>2897000</v>
       </c>
       <c r="H41" s="3">
-        <v>3874300</v>
+        <v>2718000</v>
       </c>
       <c r="I41" s="3">
-        <v>3850300</v>
+        <v>3719400</v>
       </c>
       <c r="J41" s="3">
+        <v>3696300</v>
+      </c>
+      <c r="K41" s="3">
         <v>3229400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2626900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3639800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3492000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2219100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1054500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1404400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1067300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1878900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2219500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2287300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1839700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2446500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1491500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2413200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1641100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>573700</v>
+        <v>647400</v>
       </c>
       <c r="E42" s="3">
-        <v>602100</v>
+        <v>550700</v>
       </c>
       <c r="F42" s="3">
-        <v>551200</v>
+        <v>578000</v>
       </c>
       <c r="G42" s="3">
-        <v>342300</v>
+        <v>529100</v>
       </c>
       <c r="H42" s="3">
-        <v>547400</v>
+        <v>328600</v>
       </c>
       <c r="I42" s="3">
-        <v>417300</v>
+        <v>525500</v>
       </c>
       <c r="J42" s="3">
+        <v>400600</v>
+      </c>
+      <c r="K42" s="3">
         <v>672700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>431200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>560000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>517100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>467300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>102400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>156800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>506700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>839200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>999800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>247600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>459900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>662000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>906600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1349100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1383500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>11108100</v>
+        <v>7987900</v>
       </c>
       <c r="E43" s="3">
-        <v>10566800</v>
+        <v>10663800</v>
       </c>
       <c r="F43" s="3">
-        <v>11632200</v>
+        <v>10144200</v>
       </c>
       <c r="G43" s="3">
-        <v>13002800</v>
+        <v>11166900</v>
       </c>
       <c r="H43" s="3">
-        <v>13938700</v>
+        <v>12482700</v>
       </c>
       <c r="I43" s="3">
-        <v>11720500</v>
+        <v>13381200</v>
       </c>
       <c r="J43" s="3">
+        <v>11251700</v>
+      </c>
+      <c r="K43" s="3">
         <v>9999900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9332300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7984900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6087200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5301400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3306500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2555100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1960700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2097900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2059500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1806900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2131500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2049800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2634900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2725700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2538700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>2703400</v>
+        <v>2728400</v>
       </c>
       <c r="E44" s="3">
-        <v>2550600</v>
+        <v>2595200</v>
       </c>
       <c r="F44" s="3">
-        <v>2839100</v>
+        <v>2448600</v>
       </c>
       <c r="G44" s="3">
-        <v>2573900</v>
+        <v>2725600</v>
       </c>
       <c r="H44" s="3">
-        <v>2780800</v>
+        <v>2470900</v>
       </c>
       <c r="I44" s="3">
-        <v>2970000</v>
+        <v>2669500</v>
       </c>
       <c r="J44" s="3">
+        <v>2851200</v>
+      </c>
+      <c r="K44" s="3">
         <v>2695900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3165900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2852700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2015600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1997200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1507200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1345600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1061300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1322500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1208400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1511100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1471100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1594800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1580600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1479100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1326100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>350900</v>
+        <v>363000</v>
       </c>
       <c r="E45" s="3">
-        <v>350200</v>
+        <v>336900</v>
       </c>
       <c r="F45" s="3">
-        <v>443400</v>
+        <v>336200</v>
       </c>
       <c r="G45" s="3">
-        <v>409200</v>
+        <v>425700</v>
       </c>
       <c r="H45" s="3">
-        <v>443400</v>
+        <v>392800</v>
       </c>
       <c r="I45" s="3">
-        <v>361100</v>
+        <v>425700</v>
       </c>
       <c r="J45" s="3">
+        <v>346700</v>
+      </c>
+      <c r="K45" s="3">
         <v>405200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>306400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>341400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>295100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>358600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>175900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>224100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>199200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>282900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>216900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>304500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>172500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>196300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>144400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>146700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>138600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>131000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>125000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>131300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>125800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>180600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>191400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>169900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>140500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>18527800</v>
+        <v>14903600</v>
       </c>
       <c r="E46" s="3">
-        <v>17153800</v>
+        <v>17786600</v>
       </c>
       <c r="F46" s="3">
-        <v>18483600</v>
+        <v>16467600</v>
       </c>
       <c r="G46" s="3">
-        <v>19159400</v>
+        <v>17744200</v>
       </c>
       <c r="H46" s="3">
-        <v>21584700</v>
+        <v>18393000</v>
       </c>
       <c r="I46" s="3">
-        <v>19319200</v>
+        <v>20721300</v>
       </c>
       <c r="J46" s="3">
+        <v>18546400</v>
+      </c>
+      <c r="K46" s="3">
         <v>17003100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15862700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15378800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12407000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10343600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6146600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5686000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4795200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6421200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6704100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6157500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6074800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6949500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6758000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8113900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7028000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>9582400</v>
+        <v>9481500</v>
       </c>
       <c r="E47" s="3">
-        <v>9642900</v>
+        <v>9199100</v>
       </c>
       <c r="F47" s="3">
-        <v>9783200</v>
+        <v>9257200</v>
       </c>
       <c r="G47" s="3">
-        <v>10454500</v>
+        <v>9391800</v>
       </c>
       <c r="H47" s="3">
-        <v>10709500</v>
+        <v>10036300</v>
       </c>
       <c r="I47" s="3">
-        <v>10803900</v>
+        <v>10281200</v>
       </c>
       <c r="J47" s="3">
+        <v>10371700</v>
+      </c>
+      <c r="K47" s="3">
         <v>9597600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9415100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9386800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8117900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7244100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1100900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1015100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>992900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1208900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1451100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1642600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1920700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1956400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1743300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1335500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1410900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>35477300</v>
+        <v>35194300</v>
       </c>
       <c r="E48" s="3">
-        <v>35307300</v>
+        <v>34058300</v>
       </c>
       <c r="F48" s="3">
-        <v>35003100</v>
+        <v>33895000</v>
       </c>
       <c r="G48" s="3">
-        <v>34990500</v>
+        <v>33603000</v>
       </c>
       <c r="H48" s="3">
-        <v>35953100</v>
+        <v>33590900</v>
       </c>
       <c r="I48" s="3">
-        <v>35987200</v>
+        <v>34514900</v>
       </c>
       <c r="J48" s="3">
+        <v>34547700</v>
+      </c>
+      <c r="K48" s="3">
         <v>34531700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33960900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32323000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30365200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25704900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21623400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21324800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20752300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24092400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23977800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26598600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24369500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24227100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23212000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>23085100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22319900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>4836200</v>
+        <v>4900900</v>
       </c>
       <c r="E49" s="3">
-        <v>4830300</v>
+        <v>4642800</v>
       </c>
       <c r="F49" s="3">
-        <v>5071100</v>
+        <v>4637000</v>
       </c>
       <c r="G49" s="3">
-        <v>5229600</v>
+        <v>4868300</v>
       </c>
       <c r="H49" s="3">
-        <v>5642200</v>
+        <v>5020500</v>
       </c>
       <c r="I49" s="3">
-        <v>5814100</v>
+        <v>5416500</v>
       </c>
       <c r="J49" s="3">
+        <v>5581500</v>
+      </c>
+      <c r="K49" s="3">
         <v>5565400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5331700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4982500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4626800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6636400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>402700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>400900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>460900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>357200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>397400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>364700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>355300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>354900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>361500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>345800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>354300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>383600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>384100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>415900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>404900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>375200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>380300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>393200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4495,8 +4608,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4593,106 +4709,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>3747400</v>
+        <v>4233500</v>
       </c>
       <c r="E52" s="3">
-        <v>3636000</v>
+        <v>3597500</v>
       </c>
       <c r="F52" s="3">
-        <v>2966000</v>
+        <v>3490500</v>
       </c>
       <c r="G52" s="3">
-        <v>3427300</v>
+        <v>2847400</v>
       </c>
       <c r="H52" s="3">
-        <v>4200900</v>
+        <v>3290200</v>
       </c>
       <c r="I52" s="3">
-        <v>4668000</v>
+        <v>4032900</v>
       </c>
       <c r="J52" s="3">
+        <v>4481300</v>
+      </c>
+      <c r="K52" s="3">
         <v>4085100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3777700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3144900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3103100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3142400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2484600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2427200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2336300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2923900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2825800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3302800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2486900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1880600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1713700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1711100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1717900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4789,106 +4911,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>72171100</v>
+        <v>68713800</v>
       </c>
       <c r="E54" s="3">
-        <v>70570100</v>
+        <v>69284300</v>
       </c>
       <c r="F54" s="3">
-        <v>71307000</v>
+        <v>67747300</v>
       </c>
       <c r="G54" s="3">
-        <v>73261300</v>
+        <v>68454700</v>
       </c>
       <c r="H54" s="3">
-        <v>78090400</v>
+        <v>70330900</v>
       </c>
       <c r="I54" s="3">
-        <v>76592400</v>
+        <v>74966800</v>
       </c>
       <c r="J54" s="3">
+        <v>73528700</v>
+      </c>
+      <c r="K54" s="3">
         <v>70783000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68348000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65215900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58620000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>53071400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31763400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30855800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29277600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35107300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35316000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38098900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35216500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35368900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33781800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34607100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32822600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4923,8 +5051,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4959,596 +5088,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2925200</v>
+        <v>3559300</v>
       </c>
       <c r="E57" s="3">
-        <v>3426200</v>
+        <v>2808200</v>
       </c>
       <c r="F57" s="3">
-        <v>3007500</v>
+        <v>3289200</v>
       </c>
       <c r="G57" s="3">
-        <v>2889000</v>
+        <v>2887200</v>
       </c>
       <c r="H57" s="3">
-        <v>3231900</v>
+        <v>2773400</v>
       </c>
       <c r="I57" s="3">
-        <v>3758700</v>
+        <v>3102600</v>
       </c>
       <c r="J57" s="3">
+        <v>3608300</v>
+      </c>
+      <c r="K57" s="3">
         <v>2945100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3181400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2864600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2512900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1848600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1513700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1410300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1363300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1292100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1131100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1753800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2109900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1923100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1823000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1658600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1788400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>3838300</v>
+        <v>3849400</v>
       </c>
       <c r="E58" s="3">
-        <v>3887500</v>
+        <v>3684800</v>
       </c>
       <c r="F58" s="3">
-        <v>4404100</v>
+        <v>3732000</v>
       </c>
       <c r="G58" s="3">
-        <v>4275300</v>
+        <v>4228000</v>
       </c>
       <c r="H58" s="3">
-        <v>4064300</v>
+        <v>4104300</v>
       </c>
       <c r="I58" s="3">
-        <v>5549600</v>
+        <v>3901800</v>
       </c>
       <c r="J58" s="3">
+        <v>5327700</v>
+      </c>
+      <c r="K58" s="3">
         <v>5653600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2538400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2272100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2209500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1903900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1117900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1093400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1033900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1497800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2281900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1593000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1303200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1221700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1103800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1091500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1045200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>7389400</v>
+        <v>2637600</v>
       </c>
       <c r="E59" s="3">
-        <v>3577100</v>
+        <v>7093800</v>
       </c>
       <c r="F59" s="3">
-        <v>5518800</v>
+        <v>3434100</v>
       </c>
       <c r="G59" s="3">
-        <v>8628000</v>
+        <v>5298000</v>
       </c>
       <c r="H59" s="3">
-        <v>11582900</v>
+        <v>8282900</v>
       </c>
       <c r="I59" s="3">
-        <v>4887300</v>
+        <v>11119600</v>
       </c>
       <c r="J59" s="3">
+        <v>4691800</v>
+      </c>
+      <c r="K59" s="3">
         <v>4248500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5135800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5984500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2537300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2381300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1427600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1688500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1442100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2328000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2975500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4170100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2239900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1948300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2444200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4481500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1800800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>14152900</v>
+        <v>10046400</v>
       </c>
       <c r="E60" s="3">
-        <v>10890800</v>
+        <v>13586800</v>
       </c>
       <c r="F60" s="3">
-        <v>12930400</v>
+        <v>10455200</v>
       </c>
       <c r="G60" s="3">
-        <v>15792300</v>
+        <v>12413200</v>
       </c>
       <c r="H60" s="3">
-        <v>18879200</v>
+        <v>15160600</v>
       </c>
       <c r="I60" s="3">
-        <v>14195600</v>
+        <v>18124000</v>
       </c>
       <c r="J60" s="3">
+        <v>13627800</v>
+      </c>
+      <c r="K60" s="3">
         <v>12847200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10855500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11121200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7259700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6133800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4059200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4192300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3839300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5117900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6388500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7517000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5653000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5093100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5371000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7231700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4634400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>23340400</v>
+        <v>23755300</v>
       </c>
       <c r="E61" s="3">
-        <v>22566400</v>
+        <v>22406800</v>
       </c>
       <c r="F61" s="3">
-        <v>23028000</v>
+        <v>21663700</v>
       </c>
       <c r="G61" s="3">
-        <v>22739800</v>
+        <v>22106900</v>
       </c>
       <c r="H61" s="3">
-        <v>25026200</v>
+        <v>21830200</v>
       </c>
       <c r="I61" s="3">
-        <v>23234100</v>
+        <v>24025200</v>
       </c>
       <c r="J61" s="3">
+        <v>22304700</v>
+      </c>
+      <c r="K61" s="3">
         <v>21281400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23135700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21548700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20605100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18309500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9394800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9384300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8779800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11336200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10598900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10485200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8639000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9688200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9012400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9095000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8851100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>11385100</v>
+        <v>11176100</v>
       </c>
       <c r="E62" s="3">
-        <v>11338200</v>
+        <v>10929700</v>
       </c>
       <c r="F62" s="3">
-        <v>9345800</v>
+        <v>10884700</v>
       </c>
       <c r="G62" s="3">
-        <v>9356000</v>
+        <v>8972000</v>
       </c>
       <c r="H62" s="3">
-        <v>9266000</v>
+        <v>8981800</v>
       </c>
       <c r="I62" s="3">
-        <v>9391000</v>
+        <v>8895400</v>
       </c>
       <c r="J62" s="3">
+        <v>9015300</v>
+      </c>
+      <c r="K62" s="3">
         <v>9694700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9740800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9368600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8254700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7994800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5164400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5067400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4936500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4931700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4975800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5437900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5235000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4019500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4026100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4060300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3917900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5645,8 +5793,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5743,8 +5894,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5841,106 +5995,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>54861400</v>
+        <v>51017000</v>
       </c>
       <c r="E66" s="3">
-        <v>50972100</v>
+        <v>52666900</v>
       </c>
       <c r="F66" s="3">
-        <v>51777000</v>
+        <v>48933200</v>
       </c>
       <c r="G66" s="3">
-        <v>54553300</v>
+        <v>49705900</v>
       </c>
       <c r="H66" s="3">
-        <v>59938300</v>
+        <v>52371200</v>
       </c>
       <c r="I66" s="3">
-        <v>53833700</v>
+        <v>57540800</v>
       </c>
       <c r="J66" s="3">
+        <v>51680400</v>
+      </c>
+      <c r="K66" s="3">
         <v>50316600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49990000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47937600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41404100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39212600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19406800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19405700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18337600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22287100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22919800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>24429400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20549300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19382000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19002400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20923200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17947000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5975,8 +6135,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6073,8 +6234,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6171,8 +6335,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6269,8 +6436,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6367,106 +6537,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>7425700</v>
+        <v>7938900</v>
       </c>
       <c r="E72" s="3">
-        <v>9630000</v>
+        <v>7128700</v>
       </c>
       <c r="F72" s="3">
-        <v>8572900</v>
+        <v>9244800</v>
       </c>
       <c r="G72" s="3">
-        <v>7301400</v>
+        <v>8229900</v>
       </c>
       <c r="H72" s="3">
-        <v>6279500</v>
+        <v>7009400</v>
       </c>
       <c r="I72" s="3">
-        <v>10960000</v>
+        <v>6028400</v>
       </c>
       <c r="J72" s="3">
+        <v>10521600</v>
+      </c>
+      <c r="K72" s="3">
         <v>9247300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7143800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6217600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6914900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4951900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3927300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3144800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2643400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2859000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2653800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2868400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4758100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4799200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3986200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3044700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4623800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6563,8 +6739,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6661,8 +6840,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6759,106 +6941,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>17309800</v>
+        <v>17696800</v>
       </c>
       <c r="E76" s="3">
-        <v>19598000</v>
+        <v>16617400</v>
       </c>
       <c r="F76" s="3">
-        <v>19529900</v>
+        <v>18814100</v>
       </c>
       <c r="G76" s="3">
-        <v>18708000</v>
+        <v>18748700</v>
       </c>
       <c r="H76" s="3">
-        <v>18152100</v>
+        <v>17959700</v>
       </c>
       <c r="I76" s="3">
-        <v>22758700</v>
+        <v>17426000</v>
       </c>
       <c r="J76" s="3">
+        <v>21848300</v>
+      </c>
+      <c r="K76" s="3">
         <v>20466300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18358000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17278400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17215900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13858900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12356600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11450100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10940000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12820300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12396200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13669400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14667200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15986900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14779400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13683900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14875500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6955,209 +7143,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1002900</v>
+        <v>810200</v>
       </c>
       <c r="E81" s="3">
-        <v>1057100</v>
+        <v>962800</v>
       </c>
       <c r="F81" s="3">
-        <v>1271500</v>
+        <v>1014800</v>
       </c>
       <c r="G81" s="3">
-        <v>1021900</v>
+        <v>1220600</v>
       </c>
       <c r="H81" s="3">
-        <v>1415100</v>
+        <v>981000</v>
       </c>
       <c r="I81" s="3">
-        <v>1712700</v>
+        <v>1358500</v>
       </c>
       <c r="J81" s="3">
+        <v>1644200</v>
+      </c>
+      <c r="K81" s="3">
         <v>2378200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2722200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1708900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1458500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>837600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>782100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>648000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>141800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>34600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1042300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>813000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>941500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>741000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>688300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>749200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>784400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>321100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>417500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>283500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>61400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7192,106 +7389,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>893200</v>
+        <v>891300</v>
       </c>
       <c r="E83" s="3">
-        <v>937300</v>
+        <v>857500</v>
       </c>
       <c r="F83" s="3">
-        <v>884700</v>
+        <v>899800</v>
       </c>
       <c r="G83" s="3">
-        <v>840400</v>
+        <v>849300</v>
       </c>
       <c r="H83" s="3">
-        <v>790700</v>
+        <v>806800</v>
       </c>
       <c r="I83" s="3">
-        <v>844900</v>
+        <v>759100</v>
       </c>
       <c r="J83" s="3">
+        <v>811100</v>
+      </c>
+      <c r="K83" s="3">
         <v>796000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>742600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>704500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>666200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>591000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>503100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>483400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>523300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>551700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>549500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>579700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>592200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>595600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>565200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>537500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>497000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>559000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>537300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>588000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>713800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>683300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>660300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>634300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7388,8 +7589,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7486,8 +7690,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7584,8 +7791,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7682,8 +7892,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7780,106 +7993,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1503600</v>
+        <v>4096600</v>
       </c>
       <c r="E89" s="3">
-        <v>2600400</v>
+        <v>1443500</v>
       </c>
       <c r="F89" s="3">
-        <v>1047500</v>
+        <v>2496400</v>
       </c>
       <c r="G89" s="3">
-        <v>784500</v>
+        <v>1005600</v>
       </c>
       <c r="H89" s="3">
-        <v>517800</v>
+        <v>753100</v>
       </c>
       <c r="I89" s="3">
-        <v>2839800</v>
+        <v>497000</v>
       </c>
       <c r="J89" s="3">
+        <v>2726200</v>
+      </c>
+      <c r="K89" s="3">
         <v>3733800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1600000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>984400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2642300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1161500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>695900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>616000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1120400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>846400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-539500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>668800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1966900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2513500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1620900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1305300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1176500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>478900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7914,106 +8133,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-4627406000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4273868000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7224436000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6158165000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5554360000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5153955000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-295700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-178500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-359700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-320800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-278300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-214000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-385700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-324300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-196700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-161900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-358000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8110,8 +8333,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8208,106 +8434,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-1002400</v>
+        <v>-1085900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1640500</v>
+        <v>-962300</v>
       </c>
       <c r="F94" s="3">
-        <v>-1303800</v>
+        <v>-1574900</v>
       </c>
       <c r="G94" s="3">
-        <v>-1126200</v>
+        <v>-1251700</v>
       </c>
       <c r="H94" s="3">
-        <v>-934400</v>
+        <v>-1081100</v>
       </c>
       <c r="I94" s="3">
-        <v>-1759700</v>
+        <v>-897000</v>
       </c>
       <c r="J94" s="3">
+        <v>-1689300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-722400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-916800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-552000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-145300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-462600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-224600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-712600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-475200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-293400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>130100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8342,106 +8574,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-67700</v>
+        <v>-2861200</v>
       </c>
       <c r="E96" s="3">
-        <v>-427800</v>
+        <v>-65000</v>
       </c>
       <c r="F96" s="3">
-        <v>-324800</v>
+        <v>-410700</v>
       </c>
       <c r="G96" s="3">
-        <v>-583400</v>
+        <v>-311800</v>
       </c>
       <c r="H96" s="3">
-        <v>-56700</v>
+        <v>-560100</v>
       </c>
       <c r="I96" s="3">
-        <v>-542500</v>
+        <v>-54500</v>
       </c>
       <c r="J96" s="3">
+        <v>-520800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-71100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-323200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-60300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-206300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-732400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-698500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-458600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-110700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-990600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-832000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-89800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-36500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8538,8 +8774,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8636,8 +8875,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8734,298 +8976,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>151200</v>
+        <v>-3534400</v>
       </c>
       <c r="E100" s="3">
-        <v>-507000</v>
+        <v>145100</v>
       </c>
       <c r="F100" s="3">
-        <v>506200</v>
+        <v>-486700</v>
       </c>
       <c r="G100" s="3">
-        <v>-559600</v>
+        <v>486000</v>
       </c>
       <c r="H100" s="3">
-        <v>471700</v>
+        <v>-537200</v>
       </c>
       <c r="I100" s="3">
-        <v>-653900</v>
+        <v>452800</v>
       </c>
       <c r="J100" s="3">
+        <v>-627800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-402100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-734000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2906600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-507400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-163600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2061800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-266700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-954100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-274300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>55200</v>
+        <v>60500</v>
       </c>
       <c r="E101" s="3">
-        <v>-386600</v>
+        <v>53000</v>
       </c>
       <c r="F101" s="3">
-        <v>-63400</v>
+        <v>-371100</v>
       </c>
       <c r="G101" s="3">
-        <v>-141800</v>
+        <v>-60900</v>
       </c>
       <c r="H101" s="3">
-        <v>-31000</v>
+        <v>-136200</v>
       </c>
       <c r="I101" s="3">
-        <v>194600</v>
+        <v>-29700</v>
       </c>
       <c r="J101" s="3">
+        <v>186800</v>
+      </c>
+      <c r="K101" s="3">
         <v>16500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>211600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>79700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-10700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>30000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-99000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-144100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>270100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-38800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>108200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>30500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>107900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>51800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>9800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>69600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>51000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>707700</v>
+        <v>-463200</v>
       </c>
       <c r="E102" s="3">
-        <v>66300</v>
+        <v>679400</v>
       </c>
       <c r="F102" s="3">
-        <v>186500</v>
+        <v>63700</v>
       </c>
       <c r="G102" s="3">
-        <v>-1043100</v>
+        <v>179000</v>
       </c>
       <c r="H102" s="3">
-        <v>24100</v>
+        <v>-1001400</v>
       </c>
       <c r="I102" s="3">
-        <v>620800</v>
+        <v>23100</v>
       </c>
       <c r="J102" s="3">
+        <v>596000</v>
+      </c>
+      <c r="K102" s="3">
         <v>703500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-143200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1071100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1114400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-349900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>337100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-576700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-340600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>108200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>447600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-516200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>955000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-921700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>709100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-210300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>211400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>30000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>513900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>230300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>EC</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,446 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7830500</v>
+        <v>8300800</v>
       </c>
       <c r="E8" s="3">
-        <v>7512400</v>
+        <v>7888400</v>
       </c>
       <c r="F8" s="3">
-        <v>8350700</v>
+        <v>8112400</v>
       </c>
       <c r="G8" s="3">
-        <v>8431300</v>
+        <v>8981500</v>
       </c>
       <c r="H8" s="3">
-        <v>8232000</v>
+        <v>8683800</v>
       </c>
       <c r="I8" s="3">
-        <v>9324900</v>
+        <v>8219600</v>
       </c>
       <c r="J8" s="3">
+        <v>8393000</v>
+      </c>
+      <c r="K8" s="3">
         <v>9522700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10859600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11410100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8442900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7622700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5133200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4083300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3613300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2979900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2957500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2026000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3918700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4831100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4863900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4943300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4304500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4939400</v>
+        <v>5386000</v>
       </c>
       <c r="E9" s="3">
-        <v>4575100</v>
+        <v>4909200</v>
       </c>
       <c r="F9" s="3">
-        <v>5593700</v>
+        <v>4857400</v>
       </c>
       <c r="G9" s="3">
-        <v>4945400</v>
+        <v>5945400</v>
       </c>
       <c r="H9" s="3">
-        <v>5156900</v>
+        <v>5003200</v>
       </c>
       <c r="I9" s="3">
-        <v>5466800</v>
+        <v>5069300</v>
       </c>
       <c r="J9" s="3">
+        <v>4846100</v>
+      </c>
+      <c r="K9" s="3">
         <v>5761800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6108800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6000200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4663800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4591800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3191300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2400600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2207500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2164400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2002500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1827700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2934600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3190200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3034900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3027600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2763200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2891200</v>
+        <v>2914900</v>
       </c>
       <c r="E10" s="3">
-        <v>2937300</v>
+        <v>2979200</v>
       </c>
       <c r="F10" s="3">
-        <v>2757000</v>
+        <v>3255000</v>
       </c>
       <c r="G10" s="3">
-        <v>3485900</v>
+        <v>3036100</v>
       </c>
       <c r="H10" s="3">
-        <v>3075100</v>
+        <v>3680700</v>
       </c>
       <c r="I10" s="3">
-        <v>3858100</v>
+        <v>3150200</v>
       </c>
       <c r="J10" s="3">
+        <v>3546900</v>
+      </c>
+      <c r="K10" s="3">
         <v>3760900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4750800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5409900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3779100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3030900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1941900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1682700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1405700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>815500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>955000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>198300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>984100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1641000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1829000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1915700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1541300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1128,109 +1149,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>112300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>85700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>188500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>193100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>59900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>59800</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="3">
         <v>209900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>115700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>101600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>66200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>35300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>86600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>33600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>103000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>15700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>66900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>16600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>50300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>271600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>56400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>21200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>292200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>103900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>24700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>96800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1330,210 +1355,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>4900</v>
+        <v>8100</v>
       </c>
       <c r="E14" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G14" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K14" s="3">
+        <v>81100</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N14" s="3">
         <v>6800</v>
       </c>
-      <c r="F14" s="3">
-        <v>509700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>8800</v>
-      </c>
-      <c r="I14" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J14" s="3">
-        <v>81100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M14" s="3">
-        <v>6800</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-116500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-328800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>314200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>187600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>10400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>149000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>244000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>28700</v>
+        <v>1023400</v>
       </c>
       <c r="E15" s="3">
-        <v>29100</v>
+        <v>961300</v>
       </c>
       <c r="F15" s="3">
-        <v>50200</v>
+        <v>975200</v>
       </c>
       <c r="G15" s="3">
-        <v>29200</v>
+        <v>555900</v>
       </c>
       <c r="H15" s="3">
-        <v>29500</v>
+        <v>1050500</v>
       </c>
       <c r="I15" s="3">
-        <v>36800</v>
+        <v>833800</v>
       </c>
       <c r="J15" s="3">
+        <v>715100</v>
+      </c>
+      <c r="K15" s="3">
         <v>79300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>31900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>33800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>89200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>40200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>20000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>46000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>11200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>11500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>6100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>15000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>10900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>13300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>16400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1566,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5542200</v>
+        <v>6060500</v>
       </c>
       <c r="E17" s="3">
-        <v>5159800</v>
+        <v>5578700</v>
       </c>
       <c r="F17" s="3">
-        <v>7003600</v>
+        <v>5560400</v>
       </c>
       <c r="G17" s="3">
-        <v>5595500</v>
+        <v>7522300</v>
       </c>
       <c r="H17" s="3">
-        <v>5712400</v>
+        <v>5831500</v>
       </c>
       <c r="I17" s="3">
-        <v>6031900</v>
+        <v>5691800</v>
       </c>
       <c r="J17" s="3">
+        <v>5426800</v>
+      </c>
+      <c r="K17" s="3">
         <v>6706600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6554200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6572100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5185200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5129400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3570700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2706400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2455500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2553800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2319800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1827300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3529200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3845900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3321700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3334800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2966200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2288300</v>
+        <v>2240300</v>
       </c>
       <c r="E18" s="3">
-        <v>2352600</v>
+        <v>2309700</v>
       </c>
       <c r="F18" s="3">
-        <v>1347100</v>
+        <v>2552000</v>
       </c>
       <c r="G18" s="3">
-        <v>2835900</v>
+        <v>1459200</v>
       </c>
       <c r="H18" s="3">
-        <v>2519600</v>
+        <v>2852300</v>
       </c>
       <c r="I18" s="3">
-        <v>3293000</v>
+        <v>2527800</v>
       </c>
       <c r="J18" s="3">
+        <v>2966100</v>
+      </c>
+      <c r="K18" s="3">
         <v>2816100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4305400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4838000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3257700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2493200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1562500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1376900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1157800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>426100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>637700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>198700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>389600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>985200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1542100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1608600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1338300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>538900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1805,513 +1846,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-29300</v>
+        <v>128700</v>
       </c>
       <c r="E20" s="3">
-        <v>-20900</v>
+        <v>126300</v>
       </c>
       <c r="F20" s="3">
-        <v>116600</v>
+        <v>121800</v>
       </c>
       <c r="G20" s="3">
-        <v>288500</v>
+        <v>433200</v>
       </c>
       <c r="H20" s="3">
-        <v>-47700</v>
+        <v>-206800</v>
       </c>
       <c r="I20" s="3">
-        <v>137900</v>
+        <v>157700</v>
       </c>
       <c r="J20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K20" s="3">
         <v>65800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-44700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-109400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-58100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>70200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-70500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>31500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-47000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>80100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-31700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>43400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>61300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>83200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>45700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>26900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>18100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>117200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>291700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3150300</v>
+        <v>3135000</v>
       </c>
       <c r="E21" s="3">
-        <v>3189200</v>
+        <v>3144700</v>
       </c>
       <c r="F21" s="3">
-        <v>2363500</v>
+        <v>3405400</v>
       </c>
       <c r="G21" s="3">
-        <v>3973700</v>
+        <v>1581900</v>
       </c>
       <c r="H21" s="3">
-        <v>3278700</v>
+        <v>4109600</v>
       </c>
       <c r="I21" s="3">
-        <v>4190000</v>
+        <v>3203800</v>
       </c>
       <c r="J21" s="3">
+        <v>3685700</v>
+      </c>
+      <c r="K21" s="3">
         <v>3693000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5056700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5471100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3904100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3137800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2179000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1845800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1632900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1019600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1118900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>779700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>922300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1657500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2106000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2217200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1937100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>426800</v>
+        <v>439000</v>
       </c>
       <c r="E22" s="3">
-        <v>412400</v>
+        <v>430000</v>
       </c>
       <c r="F22" s="3">
-        <v>425500</v>
+        <v>445300</v>
       </c>
       <c r="G22" s="3">
-        <v>413500</v>
+        <v>29700</v>
       </c>
       <c r="H22" s="3">
-        <v>405500</v>
+        <v>425800</v>
       </c>
       <c r="I22" s="3">
-        <v>417200</v>
+        <v>404900</v>
       </c>
       <c r="J22" s="3">
+        <v>375500</v>
+      </c>
+      <c r="K22" s="3">
         <v>391500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>363900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>346400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>285600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>294600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>154300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>127500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>117300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>125700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>155400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>156700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>126200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>127000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>128100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>129500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>122000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>183100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>144600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>347900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>171800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>206800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>198200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>153300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>205200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>226800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1832200</v>
+        <v>1768100</v>
       </c>
       <c r="E23" s="3">
-        <v>1919300</v>
+        <v>1845700</v>
       </c>
       <c r="F23" s="3">
-        <v>1038200</v>
+        <v>2072600</v>
       </c>
       <c r="G23" s="3">
-        <v>2710900</v>
+        <v>1116600</v>
       </c>
       <c r="H23" s="3">
-        <v>2066400</v>
+        <v>2792100</v>
       </c>
       <c r="I23" s="3">
-        <v>3013700</v>
+        <v>2063300</v>
       </c>
       <c r="J23" s="3">
+        <v>2712500</v>
+      </c>
+      <c r="K23" s="3">
         <v>2490400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3896800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4382200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2914000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2177000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1433600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1215200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1032100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>370700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>411700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>73500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>216300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>938200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1382300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1522500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1277600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>806300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>739400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>603800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>776100</v>
+        <v>543000</v>
       </c>
       <c r="E24" s="3">
-        <v>701000</v>
+        <v>781800</v>
       </c>
       <c r="F24" s="3">
-        <v>-180700</v>
+        <v>757000</v>
       </c>
       <c r="G24" s="3">
-        <v>1273700</v>
+        <v>-194300</v>
       </c>
       <c r="H24" s="3">
-        <v>800600</v>
+        <v>1311900</v>
       </c>
       <c r="I24" s="3">
-        <v>1342300</v>
+        <v>799400</v>
       </c>
       <c r="J24" s="3">
+        <v>1208200</v>
+      </c>
+      <c r="K24" s="3">
         <v>643600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1278900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1380500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1009800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>495300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>482700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>371200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>322700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>178300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>137100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>91500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-186900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>477900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>505400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>451800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>303400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>589000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>564000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>457200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>414600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>535100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>396300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>485600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2411,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1056100</v>
+        <v>1225100</v>
       </c>
       <c r="E26" s="3">
-        <v>1218300</v>
+        <v>1063900</v>
       </c>
       <c r="F26" s="3">
-        <v>1218900</v>
+        <v>1315600</v>
       </c>
       <c r="G26" s="3">
-        <v>1437100</v>
+        <v>1311000</v>
       </c>
       <c r="H26" s="3">
-        <v>1265800</v>
+        <v>1480200</v>
       </c>
       <c r="I26" s="3">
-        <v>1671400</v>
+        <v>1263900</v>
       </c>
       <c r="J26" s="3">
+        <v>1504300</v>
+      </c>
+      <c r="K26" s="3">
         <v>1846800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2617900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3001700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1904200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1681700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>951000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>844000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>709400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>192400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>274600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>72400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>124800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1125100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>904500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1017100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>825800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>765200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>811900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>845100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>391700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>474500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>343200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>118200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>810200</v>
+        <v>875300</v>
       </c>
       <c r="E27" s="3">
-        <v>962800</v>
+        <v>816200</v>
       </c>
       <c r="F27" s="3">
-        <v>1014800</v>
+        <v>1039700</v>
       </c>
       <c r="G27" s="3">
-        <v>1220600</v>
+        <v>1091500</v>
       </c>
       <c r="H27" s="3">
-        <v>981000</v>
+        <v>1257200</v>
       </c>
       <c r="I27" s="3">
-        <v>1358500</v>
+        <v>979500</v>
       </c>
       <c r="J27" s="3">
+        <v>1222700</v>
+      </c>
+      <c r="K27" s="3">
         <v>1644200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2378200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2722200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1708900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1458500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>837600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>782100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>648000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>141800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>205200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>34600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1042300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>813000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>941500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>741000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>688300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>749200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>784400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>321100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>417500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>283500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>61400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2714,8 +2780,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2815,8 +2884,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2916,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3017,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>29300</v>
+        <v>-128700</v>
       </c>
       <c r="E32" s="3">
-        <v>20900</v>
+        <v>-126300</v>
       </c>
       <c r="F32" s="3">
-        <v>-116600</v>
+        <v>-121800</v>
       </c>
       <c r="G32" s="3">
-        <v>-288500</v>
+        <v>-433200</v>
       </c>
       <c r="H32" s="3">
-        <v>47700</v>
+        <v>206800</v>
       </c>
       <c r="I32" s="3">
-        <v>-137900</v>
+        <v>-157700</v>
       </c>
       <c r="J32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-65800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>44700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>109400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>58100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>34100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-70200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>70500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-31500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>47000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-80100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>31700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-43400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-61300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>58800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>111000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>810200</v>
+        <v>875300</v>
       </c>
       <c r="E33" s="3">
-        <v>962800</v>
+        <v>816200</v>
       </c>
       <c r="F33" s="3">
-        <v>1014800</v>
+        <v>1039700</v>
       </c>
       <c r="G33" s="3">
-        <v>1220600</v>
+        <v>1091500</v>
       </c>
       <c r="H33" s="3">
-        <v>981000</v>
+        <v>1257200</v>
       </c>
       <c r="I33" s="3">
-        <v>1358500</v>
+        <v>979500</v>
       </c>
       <c r="J33" s="3">
+        <v>1222700</v>
+      </c>
+      <c r="K33" s="3">
         <v>1644200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2378200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2722200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1708900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1458500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>837600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>782100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>648000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>141800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>205200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>34600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1042300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>813000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>941500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>741000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>688300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>749200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>784400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>321100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>417500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>283500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>61400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3320,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>810200</v>
+        <v>875300</v>
       </c>
       <c r="E35" s="3">
-        <v>962800</v>
+        <v>816200</v>
       </c>
       <c r="F35" s="3">
-        <v>1014800</v>
+        <v>1039700</v>
       </c>
       <c r="G35" s="3">
-        <v>1220600</v>
+        <v>1091500</v>
       </c>
       <c r="H35" s="3">
-        <v>981000</v>
+        <v>1257200</v>
       </c>
       <c r="I35" s="3">
-        <v>1358500</v>
+        <v>979500</v>
       </c>
       <c r="J35" s="3">
+        <v>1222700</v>
+      </c>
+      <c r="K35" s="3">
         <v>1644200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2378200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2722200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1708900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1458500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>837600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>782100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>648000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>141800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>205200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>34600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1042300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>813000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>941500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>741000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>688300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>749200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>784400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>321100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>417500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>283500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>61400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3564,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3601,917 +3695,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3176900</v>
+        <v>3381700</v>
       </c>
       <c r="E41" s="3">
-        <v>3640100</v>
+        <v>3200300</v>
       </c>
       <c r="F41" s="3">
-        <v>2960700</v>
+        <v>3930800</v>
       </c>
       <c r="G41" s="3">
-        <v>2897000</v>
+        <v>3184300</v>
       </c>
       <c r="H41" s="3">
-        <v>2718000</v>
+        <v>2983700</v>
       </c>
       <c r="I41" s="3">
-        <v>3719400</v>
+        <v>2713800</v>
       </c>
       <c r="J41" s="3">
+        <v>3347700</v>
+      </c>
+      <c r="K41" s="3">
         <v>3696300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3229400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2626900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3639800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3492000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2219100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1054500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1404400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1067300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1878900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2219500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2287300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1839700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2446500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1491500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2413200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>647400</v>
+        <v>537100</v>
       </c>
       <c r="E42" s="3">
-        <v>550700</v>
+        <v>510800</v>
       </c>
       <c r="F42" s="3">
-        <v>578000</v>
+        <v>441500</v>
       </c>
       <c r="G42" s="3">
-        <v>529100</v>
+        <v>480400</v>
       </c>
       <c r="H42" s="3">
-        <v>328600</v>
+        <v>433100</v>
       </c>
       <c r="I42" s="3">
-        <v>525500</v>
+        <v>218400</v>
       </c>
       <c r="J42" s="3">
+        <v>363800</v>
+      </c>
+      <c r="K42" s="3">
         <v>400600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>672700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>431200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>560000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>517100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>467300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>102400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>156800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>506700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>839200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>999800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>247600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>459900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>662000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>906600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1349100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>7987900</v>
+        <v>7387300</v>
       </c>
       <c r="E43" s="3">
-        <v>10663800</v>
+        <v>7745000</v>
       </c>
       <c r="F43" s="3">
-        <v>10144200</v>
+        <v>11217900</v>
       </c>
       <c r="G43" s="3">
-        <v>11166900</v>
+        <v>10692300</v>
       </c>
       <c r="H43" s="3">
-        <v>12482700</v>
+        <v>11260800</v>
       </c>
       <c r="I43" s="3">
-        <v>13381200</v>
+        <v>12220100</v>
       </c>
       <c r="J43" s="3">
+        <v>11822500</v>
+      </c>
+      <c r="K43" s="3">
         <v>11251700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9999900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9332300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7984900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6087200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5301400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3306500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2555100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1960700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2097900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2059500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1806900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2131500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2049800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2634900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2725700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>2728400</v>
+        <v>2616200</v>
       </c>
       <c r="E44" s="3">
-        <v>2595200</v>
+        <v>2748600</v>
       </c>
       <c r="F44" s="3">
-        <v>2448600</v>
+        <v>2802500</v>
       </c>
       <c r="G44" s="3">
-        <v>2725600</v>
+        <v>2633600</v>
       </c>
       <c r="H44" s="3">
-        <v>2470900</v>
+        <v>2807200</v>
       </c>
       <c r="I44" s="3">
-        <v>2669500</v>
+        <v>2467200</v>
       </c>
       <c r="J44" s="3">
+        <v>2402800</v>
+      </c>
+      <c r="K44" s="3">
         <v>2851200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2695900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3165900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2852700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2015600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1997200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1507200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1345600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1061300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1322500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1208400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1511100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1471100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1594800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1580600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1479100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>363000</v>
+        <v>574100</v>
       </c>
       <c r="E45" s="3">
-        <v>336900</v>
+        <v>638200</v>
       </c>
       <c r="F45" s="3">
-        <v>336200</v>
+        <v>632900</v>
       </c>
       <c r="G45" s="3">
-        <v>425700</v>
+        <v>517500</v>
       </c>
       <c r="H45" s="3">
-        <v>392800</v>
+        <v>556300</v>
       </c>
       <c r="I45" s="3">
-        <v>425700</v>
+        <v>598700</v>
       </c>
       <c r="J45" s="3">
+        <v>556400</v>
+      </c>
+      <c r="K45" s="3">
         <v>346700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>405200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>306400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>341400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>295100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>358600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>175900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>224100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>199200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>282900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>216900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>304500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>172500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>196300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>144400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>146700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>138600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>131000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>125000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>131300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>125800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>180600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>191400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>169900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>140500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>14903600</v>
+        <v>14835800</v>
       </c>
       <c r="E46" s="3">
-        <v>17786600</v>
+        <v>15013700</v>
       </c>
       <c r="F46" s="3">
-        <v>16467600</v>
+        <v>19207200</v>
       </c>
       <c r="G46" s="3">
-        <v>17744200</v>
+        <v>17711700</v>
       </c>
       <c r="H46" s="3">
-        <v>18393000</v>
+        <v>18275700</v>
       </c>
       <c r="I46" s="3">
-        <v>20721300</v>
+        <v>18365100</v>
       </c>
       <c r="J46" s="3">
+        <v>18650500</v>
+      </c>
+      <c r="K46" s="3">
         <v>18546400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17003100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15862700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15378800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12407000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10343600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6146600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5686000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4795200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6421200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6704100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6157500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6074800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6949500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6758000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8113900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>9481500</v>
+        <v>3061800</v>
       </c>
       <c r="E47" s="3">
-        <v>9199100</v>
+        <v>2228400</v>
       </c>
       <c r="F47" s="3">
-        <v>9257200</v>
+        <v>2335200</v>
       </c>
       <c r="G47" s="3">
-        <v>9391800</v>
+        <v>2269100</v>
       </c>
       <c r="H47" s="3">
-        <v>10036300</v>
+        <v>2243600</v>
       </c>
       <c r="I47" s="3">
-        <v>10281200</v>
+        <v>2379700</v>
       </c>
       <c r="J47" s="3">
+        <v>2169700</v>
+      </c>
+      <c r="K47" s="3">
         <v>10371700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9597600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9415100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9386800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8117900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7244100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1100900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1015100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>992900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1208900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1451100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1642600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1920700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1956400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1743300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1335500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>35194300</v>
+        <v>35360500</v>
       </c>
       <c r="E48" s="3">
-        <v>34058300</v>
+        <v>35454400</v>
       </c>
       <c r="F48" s="3">
-        <v>33895000</v>
+        <v>36778400</v>
       </c>
       <c r="G48" s="3">
-        <v>33603000</v>
+        <v>36455600</v>
       </c>
       <c r="H48" s="3">
-        <v>33590900</v>
+        <v>34609400</v>
       </c>
       <c r="I48" s="3">
-        <v>34514900</v>
+        <v>33539900</v>
       </c>
       <c r="J48" s="3">
+        <v>31065700</v>
+      </c>
+      <c r="K48" s="3">
         <v>34547700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34531700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33960900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32323000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30365200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25704900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21623400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21324800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20752300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24092400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23977800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26598600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24369500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24227100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>23212000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23085100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>4900900</v>
+        <v>4918100</v>
       </c>
       <c r="E49" s="3">
-        <v>4642800</v>
+        <v>4937100</v>
       </c>
       <c r="F49" s="3">
-        <v>4637000</v>
+        <v>5013600</v>
       </c>
       <c r="G49" s="3">
-        <v>4868300</v>
+        <v>4987400</v>
       </c>
       <c r="H49" s="3">
-        <v>5020500</v>
+        <v>5014100</v>
       </c>
       <c r="I49" s="3">
-        <v>5416500</v>
+        <v>5012800</v>
       </c>
       <c r="J49" s="3">
+        <v>4875200</v>
+      </c>
+      <c r="K49" s="3">
         <v>5581500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5565400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5331700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4982500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4626800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6636400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>407900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>402700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>400900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>460900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>357200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>397400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>364700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>355300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>354900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>361500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>345800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>354300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>383600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>384100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>415900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>404900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>375200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>380300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>393200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4611,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4712,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>4233500</v>
+        <v>5152300</v>
       </c>
       <c r="E52" s="3">
-        <v>3597500</v>
+        <v>5187700</v>
       </c>
       <c r="F52" s="3">
-        <v>3490500</v>
+        <v>4681600</v>
       </c>
       <c r="G52" s="3">
-        <v>2847400</v>
+        <v>1221000</v>
       </c>
       <c r="H52" s="3">
-        <v>3290200</v>
+        <v>3707800</v>
       </c>
       <c r="I52" s="3">
-        <v>4032900</v>
+        <v>4043600</v>
       </c>
       <c r="J52" s="3">
+        <v>4335700</v>
+      </c>
+      <c r="K52" s="3">
         <v>4481300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4085100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3777700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3144900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3103100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3142400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2484600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2427200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2336300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2923900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2825800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3302800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2486900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1880600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1713700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1711100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4914,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>68713800</v>
+        <v>70209700</v>
       </c>
       <c r="E54" s="3">
-        <v>69284300</v>
+        <v>69221700</v>
       </c>
       <c r="F54" s="3">
-        <v>67747300</v>
+        <v>74817800</v>
       </c>
       <c r="G54" s="3">
-        <v>68454700</v>
+        <v>72865400</v>
       </c>
       <c r="H54" s="3">
-        <v>70330900</v>
+        <v>70505000</v>
       </c>
       <c r="I54" s="3">
-        <v>74966800</v>
+        <v>70224100</v>
       </c>
       <c r="J54" s="3">
+        <v>67474900</v>
+      </c>
+      <c r="K54" s="3">
         <v>73528700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70783000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68348000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65215900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58620000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>53071400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31763400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30855800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29277600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35107300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35316000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38098900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35216500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35368900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33781800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34607100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5052,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5089,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>3559300</v>
+        <v>2979200</v>
       </c>
       <c r="E57" s="3">
-        <v>2808200</v>
+        <v>2852300</v>
       </c>
       <c r="F57" s="3">
-        <v>3289200</v>
+        <v>3047300</v>
       </c>
       <c r="G57" s="3">
-        <v>2887200</v>
+        <v>3554400</v>
       </c>
       <c r="H57" s="3">
-        <v>2773400</v>
+        <v>2988400</v>
       </c>
       <c r="I57" s="3">
-        <v>3102600</v>
+        <v>2769200</v>
       </c>
       <c r="J57" s="3">
+        <v>2806000</v>
+      </c>
+      <c r="K57" s="3">
         <v>3608300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2945100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3181400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2864600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2512900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1848600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1513700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1410300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1363300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1292100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1131100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1753800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2109900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1923100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1823000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1658600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>3849400</v>
+        <v>2837800</v>
       </c>
       <c r="E58" s="3">
-        <v>3684800</v>
+        <v>3877900</v>
       </c>
       <c r="F58" s="3">
-        <v>3732000</v>
+        <v>3979100</v>
       </c>
       <c r="G58" s="3">
-        <v>4228000</v>
+        <v>4013900</v>
       </c>
       <c r="H58" s="3">
-        <v>4104300</v>
+        <v>4354600</v>
       </c>
       <c r="I58" s="3">
-        <v>3901800</v>
+        <v>4098000</v>
       </c>
       <c r="J58" s="3">
+        <v>3511800</v>
+      </c>
+      <c r="K58" s="3">
         <v>5327700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5653600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2538400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2272100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2209500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1903900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1117900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1093400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1033900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1497800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2281900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1593000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1303200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1221700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1103800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1091500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2637600</v>
+        <v>2172900</v>
       </c>
       <c r="E59" s="3">
-        <v>7093800</v>
+        <v>2643500</v>
       </c>
       <c r="F59" s="3">
-        <v>3434100</v>
+        <v>6770500</v>
       </c>
       <c r="G59" s="3">
-        <v>5298000</v>
+        <v>2816200</v>
       </c>
       <c r="H59" s="3">
-        <v>8282900</v>
+        <v>4629600</v>
       </c>
       <c r="I59" s="3">
-        <v>11119600</v>
+        <v>7606000</v>
       </c>
       <c r="J59" s="3">
+        <v>9319000</v>
+      </c>
+      <c r="K59" s="3">
         <v>4691800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4248500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5135800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5984500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2537300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2381300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1427600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1688500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1442100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2328000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2975500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4170100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2239900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1948300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2444200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4481500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>10046400</v>
+        <v>8855900</v>
       </c>
       <c r="E60" s="3">
-        <v>13586800</v>
+        <v>10120600</v>
       </c>
       <c r="F60" s="3">
-        <v>10455200</v>
+        <v>14671900</v>
       </c>
       <c r="G60" s="3">
-        <v>12413200</v>
+        <v>11245100</v>
       </c>
       <c r="H60" s="3">
-        <v>15160600</v>
+        <v>12785000</v>
       </c>
       <c r="I60" s="3">
-        <v>18124000</v>
+        <v>15137600</v>
       </c>
       <c r="J60" s="3">
+        <v>16312800</v>
+      </c>
+      <c r="K60" s="3">
         <v>13627800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12847200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10855500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11121200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7259700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6133800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4059200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4192300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3839300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5117900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6388500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7517000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5653000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5093100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5371000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7231700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>23755300</v>
+        <v>25079000</v>
       </c>
       <c r="E61" s="3">
-        <v>22406800</v>
+        <v>23930800</v>
       </c>
       <c r="F61" s="3">
-        <v>21663700</v>
+        <v>24196400</v>
       </c>
       <c r="G61" s="3">
-        <v>22106900</v>
+        <v>23300300</v>
       </c>
       <c r="H61" s="3">
-        <v>21830200</v>
+        <v>22769000</v>
       </c>
       <c r="I61" s="3">
-        <v>24025200</v>
+        <v>21797100</v>
       </c>
       <c r="J61" s="3">
+        <v>21624200</v>
+      </c>
+      <c r="K61" s="3">
         <v>22304700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21281400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23135700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21548700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20605100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18309500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9394800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9384300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8779800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11336200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10598900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10485200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8639000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9688200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9012400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9095000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>11176100</v>
+        <v>7550400</v>
       </c>
       <c r="E62" s="3">
-        <v>10929700</v>
+        <v>7462400</v>
       </c>
       <c r="F62" s="3">
-        <v>10884700</v>
+        <v>7807500</v>
       </c>
       <c r="G62" s="3">
-        <v>8972000</v>
+        <v>4909800</v>
       </c>
       <c r="H62" s="3">
-        <v>8981800</v>
+        <v>6892800</v>
       </c>
       <c r="I62" s="3">
-        <v>8895400</v>
+        <v>6780000</v>
       </c>
       <c r="J62" s="3">
+        <v>5967400</v>
+      </c>
+      <c r="K62" s="3">
         <v>9015300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9694700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9740800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9368600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8254700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7994800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5164400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5067400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4936500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4931700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4975800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5437900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5235000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4019500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4026100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4060300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5796,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5897,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5998,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>51017000</v>
+        <v>45043200</v>
       </c>
       <c r="E66" s="3">
-        <v>52666900</v>
+        <v>45310200</v>
       </c>
       <c r="F66" s="3">
-        <v>48933200</v>
+        <v>50670800</v>
       </c>
       <c r="G66" s="3">
-        <v>49705900</v>
+        <v>46252400</v>
       </c>
       <c r="H66" s="3">
-        <v>52371200</v>
+        <v>44794700</v>
       </c>
       <c r="I66" s="3">
-        <v>57540800</v>
+        <v>45902800</v>
       </c>
       <c r="J66" s="3">
+        <v>45943300</v>
+      </c>
+      <c r="K66" s="3">
         <v>51680400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50316600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49990000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47937600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41404100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39212600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19406800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19405700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18337600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22287100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22919800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24429400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20549300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19382000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19002400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20923200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6136,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6237,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6338,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6439,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6540,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>7938900</v>
+        <v>8785000</v>
       </c>
       <c r="E72" s="3">
-        <v>7128700</v>
+        <v>7997600</v>
       </c>
       <c r="F72" s="3">
-        <v>9244800</v>
+        <v>7698100</v>
       </c>
       <c r="G72" s="3">
-        <v>8229900</v>
+        <v>9943200</v>
       </c>
       <c r="H72" s="3">
-        <v>7009400</v>
+        <v>8476400</v>
       </c>
       <c r="I72" s="3">
-        <v>6028400</v>
+        <v>6998700</v>
       </c>
       <c r="J72" s="3">
+        <v>5425900</v>
+      </c>
+      <c r="K72" s="3">
         <v>10521600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9247300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7143800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6217600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6914900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4951900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3927300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3144800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2643400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2859000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2653800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2868400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4758100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4799200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3986200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3044700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6742,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6843,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6944,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>17696800</v>
+        <v>18774900</v>
       </c>
       <c r="E76" s="3">
-        <v>16617400</v>
+        <v>17827600</v>
       </c>
       <c r="F76" s="3">
-        <v>18814100</v>
+        <v>17944600</v>
       </c>
       <c r="G76" s="3">
-        <v>18748700</v>
+        <v>20235400</v>
       </c>
       <c r="H76" s="3">
-        <v>17959700</v>
+        <v>19310300</v>
       </c>
       <c r="I76" s="3">
-        <v>17426000</v>
+        <v>17932400</v>
       </c>
       <c r="J76" s="3">
+        <v>15684500</v>
+      </c>
+      <c r="K76" s="3">
         <v>21848300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20466300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18358000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17278400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17215900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13858900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12356600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11450100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10940000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12820300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12396200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13669400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14667200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15986900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14779400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13683900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7146,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>810200</v>
+        <v>875300</v>
       </c>
       <c r="E81" s="3">
-        <v>962800</v>
+        <v>816200</v>
       </c>
       <c r="F81" s="3">
-        <v>1014800</v>
+        <v>1039700</v>
       </c>
       <c r="G81" s="3">
-        <v>1220600</v>
+        <v>1091500</v>
       </c>
       <c r="H81" s="3">
-        <v>981000</v>
+        <v>1257200</v>
       </c>
       <c r="I81" s="3">
-        <v>1358500</v>
+        <v>979500</v>
       </c>
       <c r="J81" s="3">
+        <v>1222700</v>
+      </c>
+      <c r="K81" s="3">
         <v>1644200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2378200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2722200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1708900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1458500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>837600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>782100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>648000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>141800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>205200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>34600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1042300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>813000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>941500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>741000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>688300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>749200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>784400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>321100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>417500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>283500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>61400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7390,109 +7596,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>891300</v>
+        <v>874800</v>
       </c>
       <c r="E83" s="3">
-        <v>857500</v>
+        <v>805500</v>
       </c>
       <c r="F83" s="3">
-        <v>899800</v>
+        <v>683200</v>
       </c>
       <c r="G83" s="3">
-        <v>849300</v>
+        <v>525300</v>
       </c>
       <c r="H83" s="3">
-        <v>806800</v>
+        <v>691800</v>
       </c>
       <c r="I83" s="3">
-        <v>759100</v>
+        <v>684600</v>
       </c>
       <c r="J83" s="3">
+        <v>722000</v>
+      </c>
+      <c r="K83" s="3">
         <v>811100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>796000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>742600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>704500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>666200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>591000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>503100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>483400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>523300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>551700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>549500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>579700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>592200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>595600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>565200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>537500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>497000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>559000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>537300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>588000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>713800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>683300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>660300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>634300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7592,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7693,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7794,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7895,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7996,109 +8218,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>4096600</v>
+        <v>2989800</v>
       </c>
       <c r="E89" s="3">
-        <v>1443500</v>
+        <v>4126900</v>
       </c>
       <c r="F89" s="3">
-        <v>2496400</v>
+        <v>1558800</v>
       </c>
       <c r="G89" s="3">
-        <v>1005600</v>
+        <v>2685000</v>
       </c>
       <c r="H89" s="3">
-        <v>753100</v>
+        <v>1035700</v>
       </c>
       <c r="I89" s="3">
-        <v>497000</v>
+        <v>752000</v>
       </c>
       <c r="J89" s="3">
+        <v>447400</v>
+      </c>
+      <c r="K89" s="3">
         <v>2726200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3733800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1600000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>984400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2642300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1161500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>695900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>616000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1120400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>846400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-539500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>668800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1966900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2513500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1620900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1305300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>478900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8134,109 +8362,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-4627406000</v>
+        <v>-1182000</v>
       </c>
       <c r="E91" s="3">
-        <v>-4273868000</v>
+        <v>-1076300</v>
       </c>
       <c r="F91" s="3">
-        <v>-7224436000</v>
+        <v>-1052300</v>
       </c>
       <c r="G91" s="3">
-        <v>-6158165000</v>
+        <v>-1784200</v>
       </c>
       <c r="H91" s="3">
-        <v>-5554360000</v>
+        <v>-1508300</v>
       </c>
       <c r="I91" s="3">
-        <v>-5153955000</v>
+        <v>-1279700</v>
       </c>
       <c r="J91" s="3">
+        <v>-1068800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-295700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-178500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-359700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-320800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-278300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-214000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-385700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-324300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-196700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-161900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8336,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8437,109 +8672,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-1085900</v>
+        <v>-1744500</v>
       </c>
       <c r="E94" s="3">
-        <v>-962300</v>
+        <v>-1094000</v>
       </c>
       <c r="F94" s="3">
-        <v>-1574900</v>
+        <v>-1039100</v>
       </c>
       <c r="G94" s="3">
-        <v>-1251700</v>
+        <v>-1693900</v>
       </c>
       <c r="H94" s="3">
-        <v>-1081100</v>
+        <v>-1289200</v>
       </c>
       <c r="I94" s="3">
-        <v>-897000</v>
+        <v>-1079500</v>
       </c>
       <c r="J94" s="3">
+        <v>-807400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-722400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-916800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-552000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-145300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-462600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-40800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-224600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-712600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-475200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-293400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>130100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8575,109 +8816,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-2861200</v>
+        <v>146800</v>
       </c>
       <c r="E96" s="3">
-        <v>-65000</v>
+        <v>2882300</v>
       </c>
       <c r="F96" s="3">
-        <v>-410700</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-311800</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-560100</v>
+        <v>70100</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I96" s="3">
-        <v>-54500</v>
+        <v>559200</v>
       </c>
       <c r="J96" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-520800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-71100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-323200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-60300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-206300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-35300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-732400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-698500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-458600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-110700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-990600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-832000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-89800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8777,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8878,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8979,307 +9230,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-3534400</v>
+        <v>-1174600</v>
       </c>
       <c r="E100" s="3">
-        <v>145100</v>
+        <v>-3560500</v>
       </c>
       <c r="F100" s="3">
-        <v>-486700</v>
+        <v>156700</v>
       </c>
       <c r="G100" s="3">
-        <v>486000</v>
+        <v>-523500</v>
       </c>
       <c r="H100" s="3">
-        <v>-537200</v>
+        <v>500600</v>
       </c>
       <c r="I100" s="3">
-        <v>452800</v>
+        <v>-536400</v>
       </c>
       <c r="J100" s="3">
+        <v>407500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-627800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-402100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-734000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2906600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-507400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-163600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2061800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-266700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-954100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-274300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>60500</v>
+        <v>-62700</v>
       </c>
       <c r="E101" s="3">
-        <v>53000</v>
+        <v>-136000</v>
       </c>
       <c r="F101" s="3">
-        <v>-371100</v>
+        <v>-26700</v>
       </c>
       <c r="G101" s="3">
-        <v>-60900</v>
+        <v>160600</v>
       </c>
       <c r="H101" s="3">
-        <v>-136200</v>
+        <v>14300</v>
       </c>
       <c r="I101" s="3">
-        <v>-29700</v>
+        <v>195100</v>
       </c>
       <c r="J101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K101" s="3">
         <v>186800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>16500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>211600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>79700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>30000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-99000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-144100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>270100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-38800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>108200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>30500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>107900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>51800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>9800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>69600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>51000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-463200</v>
+        <v>206700</v>
       </c>
       <c r="E102" s="3">
-        <v>679400</v>
+        <v>-466600</v>
       </c>
       <c r="F102" s="3">
-        <v>63700</v>
+        <v>733700</v>
       </c>
       <c r="G102" s="3">
-        <v>179000</v>
+        <v>68500</v>
       </c>
       <c r="H102" s="3">
-        <v>-1001400</v>
+        <v>184400</v>
       </c>
       <c r="I102" s="3">
-        <v>23100</v>
+        <v>-999900</v>
       </c>
       <c r="J102" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K102" s="3">
         <v>596000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>703500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-143200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1071100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1114400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-349900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>337100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-576700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-340600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>108200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>447600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-516200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>955000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-921700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>709100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>211400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>30000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>513900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>230300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>EC</t>
   </si>
@@ -656,464 +656,476 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7890100</v>
+      </c>
+      <c r="E8" s="3">
         <v>8300800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7888400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8112400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8981500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8683800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8219600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8393000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9522700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10859600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11410100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8442900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7622700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5133200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4083300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3613300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2979900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2957500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2026000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3918700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4831100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4863900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4943300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4304500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5423000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5386000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4909200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4857400</v>
       </c>
-      <c r="G9" s="3">
-        <v>5945400</v>
-      </c>
       <c r="H9" s="3">
+        <v>5915000</v>
+      </c>
+      <c r="I9" s="3">
         <v>5003200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5069300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4846100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5761800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6108800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6000200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4663800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4591800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3191300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2400600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2207500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2164400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2002500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1827700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2934600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3190200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3034900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3027600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2763200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2467000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2914900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2979200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3255000</v>
       </c>
-      <c r="G10" s="3">
-        <v>3036100</v>
-      </c>
       <c r="H10" s="3">
+        <v>3066500</v>
+      </c>
+      <c r="I10" s="3">
         <v>3680700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3150200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3546900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3760900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4750800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5409900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3779100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3030900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1941900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1682700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1405700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>815500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>955000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>198300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>984100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1641000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1829000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1915700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1541300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1162,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1176,86 +1189,89 @@
       <c r="J12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="3">
         <v>209900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>115700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>101600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>66200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>35300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>86600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>33600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>103000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>15700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>66900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>50300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>271600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>56400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>21200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>292200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>103900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>24700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>8600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>96800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1358,216 +1374,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-260500</v>
+      </c>
+      <c r="E14" s="3">
         <v>8100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-68500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>81100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-116500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-328800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>314200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>187600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>149000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>244000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1023400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>961300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>975200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>555900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1050500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>833800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>715100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>79300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>31900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>33800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>89200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>40200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>20000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>46000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>11200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>11500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>6100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>8700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>15000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>10900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>13300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>16400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,216 +1626,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5924200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6060500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5578700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5560400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7522300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5831500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5691800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5426800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6706600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6554200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6572100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5185200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5129400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3570700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2706400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2455500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2553800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2319800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1827300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3529200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3845900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3321700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3334800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2966200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1965800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2240300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2309700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2552000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1459200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2852300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2527800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2966100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2816100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4305400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4838000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3257700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2493200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1562500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1376900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1157800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>426100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>637700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>198700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>389600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>985200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1542100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1608600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1338300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>538900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1847,528 +1879,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E20" s="3">
         <v>128700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>126300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>121800</v>
       </c>
-      <c r="G20" s="3">
-        <v>433200</v>
-      </c>
       <c r="H20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-206800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>157700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>65800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-44700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-109400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-58100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-34100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>70200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-70500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>31500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-47000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>80100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>43400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>61300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>83200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>19300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>45700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>26900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>18100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>117200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>291700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1933200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3135000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3144700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3405400</v>
       </c>
-      <c r="G21" s="3">
-        <v>1581900</v>
-      </c>
       <c r="H21" s="3">
+        <v>2009900</v>
+      </c>
+      <c r="I21" s="3">
         <v>4109600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3203800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3685700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3693000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5056700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5471100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3904100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3137800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2179000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1845800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1632900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1019600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1118900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>779700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>922300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1657500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2106000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2217200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1937100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E22" s="3">
         <v>439000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>430000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>445300</v>
       </c>
-      <c r="G22" s="3">
-        <v>29700</v>
-      </c>
       <c r="H22" s="3">
+        <v>457600</v>
+      </c>
+      <c r="I22" s="3">
         <v>425800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>404900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>375500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>391500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>363900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>346400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>285600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>294600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>154300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>127500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>117300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>125700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>155400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>156700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>126200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>127000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>128100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>129500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>122000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>183100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>144600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>347900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>171800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>206800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>198200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>153300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>205200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>226800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1746800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1768100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1845700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2072600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1116600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2792100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2063300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2712500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2490400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3896800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4382200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2914000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2177000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1433600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1215200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1032100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>370700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>411700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>73500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>216300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>938200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1382300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1522500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>806300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>739400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>603800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E24" s="3">
         <v>543000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>781800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>757000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-194300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1311900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>799400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1208200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>643600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1278900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1380500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1009800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>495300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>482700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>371200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>322700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>178300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>137100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>91500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-186900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>477900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>505400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>451800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>303400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>589000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>564000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>457200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>414600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>535100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>396300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>485600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2471,216 +2519,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1140700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1225100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1063900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1315600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1311000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1480200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1263900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1504300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1846800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2617900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3001700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1904200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1681700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>951000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>844000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>709400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>192400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>274600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>72400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>124800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1125100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>904500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1017100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>825800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>765200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>811900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>845100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>391700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>474500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>343200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>118200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E27" s="3">
         <v>875300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>816200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1039700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1091500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1257200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>979500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1222700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1644200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2378200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2722200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1708900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1458500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>837600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>782100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>648000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>141800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>205200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1042300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>813000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>941500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>741000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>688300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>749200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>784400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>321100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>417500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>283500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>61400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2783,8 +2840,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2887,8 +2947,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3095,216 +3161,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-108200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-128700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-126300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-121800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-433200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I32" s="3">
         <v>206800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-157700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-65800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>44700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>109400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>58100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>34100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-70200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>70500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-31500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>47000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-80100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>31700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-43400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-61300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>58800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>111000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E33" s="3">
         <v>875300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>816200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1039700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1091500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1257200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>979500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1222700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1644200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2378200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2722200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1708900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1458500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>837600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>782100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>648000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>141800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>205200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>34600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1042300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>813000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>941500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>741000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>688300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>749200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>784400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>321100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>417500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>283500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>61400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3407,221 +3482,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E35" s="3">
         <v>875300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>816200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1039700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1091500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1257200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>979500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1222700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1644200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2378200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2722200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1708900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1458500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>837600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>782100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>648000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>141800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>205200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>34600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1042300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>813000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>941500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>741000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>688300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>749200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>784400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>321100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>417500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>283500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>61400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3696,944 +3781,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3187200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3381700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3200300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3930800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3184300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2983700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2713800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3347700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3696300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3229400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2626900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3639800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3492000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2219100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1054500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1404400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1067300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1878900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2219500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2287300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1839700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2446500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1491500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2413200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>193100</v>
+      </c>
+      <c r="E42" s="3">
         <v>537100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>510800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>441500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>480400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>433100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>218400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>363800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>400600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>672700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>431200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>560000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>517100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>467300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>102400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>156800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>506700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>839200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>999800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>247600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>459900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>662000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>906600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1349100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>7226000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7387300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7745000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11217900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10692300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11260800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12220100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11822500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11251700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9999900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9332300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7984900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6087200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5301400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3306500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2555100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1960700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2097900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2059500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1806900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2131500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2049800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2634900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2725700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2274100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2616200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2748600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2802500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2633600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2807200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2467200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2402800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2851200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2695900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3165900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2852700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2015600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1997200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1507200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1345600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1061300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1322500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1208400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1511100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1471100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1594800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1580600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1479100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>510100</v>
+      </c>
+      <c r="E45" s="3">
         <v>574100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>638200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>632900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>517500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>556300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>598700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>556400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>346700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>405200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>306400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>341400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>295100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>358600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>175900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>224100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>199200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>282900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>216900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>304500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>172500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>196300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>144400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>146700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>138600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>131000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>125000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>131300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>125800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>180600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>191400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>169900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>140500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>13752300</v>
+      </c>
+      <c r="E46" s="3">
         <v>14835800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15013700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19207200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17711700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18275700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18365100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18650500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18546400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17003100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15862700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15378800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12407000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10343600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6146600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5686000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4795200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6421200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6704100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6157500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6074800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6949500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6758000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8113900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2957400</v>
+      </c>
+      <c r="E47" s="3">
         <v>3061800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2228400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2335200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2269100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2243600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2379700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2169700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10371700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9597600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9415100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9386800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8117900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7244100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1100900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1015100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>992900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1208900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1451100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1642600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1920700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1956400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1743300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1335500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>35400200</v>
+      </c>
+      <c r="E48" s="3">
         <v>35360500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35454400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36778400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36455600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34609400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33539900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31065700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34547700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34531700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33960900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32323000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30365200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25704900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21623400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21324800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20752300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24092400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23977800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26598600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24369500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24227100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23212000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23085100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>4834600</v>
+      </c>
+      <c r="E49" s="3">
         <v>4918100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4937100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5013600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4987400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5014100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5012800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4875200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5581500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5565400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5331700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4982500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4626800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6636400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>407900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>402700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>400900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>460900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>357200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>397400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>364700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>355300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>354900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>361500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>345800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>354300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>383600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>384100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>415900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>404900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>375200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>380300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>393200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4840,112 +4956,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1308400</v>
+      </c>
+      <c r="E52" s="3">
         <v>5152300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5187700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4681600</v>
       </c>
-      <c r="G52" s="3">
-        <v>1221000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1390700</v>
+      </c>
+      <c r="I52" s="3">
         <v>3707800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4043600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4335700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4481300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4085100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3777700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3144900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3103100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3142400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2484600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2427200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2336300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2923900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2825800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3302800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2486900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1880600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1713700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1711100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>68338400</v>
+      </c>
+      <c r="E54" s="3">
         <v>70209700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69221700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>74817800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72865400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70505000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70224100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67474900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73528700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70783000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68348000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>65215900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58620000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>53071400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31763400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30855800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29277600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35107300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35316000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38098900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35216500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35368900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33781800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34607100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3432900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2979200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2852300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3047300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3554400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2988400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2769200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2806000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3608300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2945100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3181400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2864600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2512900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1848600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1513700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1410300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1363300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1292100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1131100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1753800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2109900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1923100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1823000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1658600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>2559900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2837800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3877900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3979100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4013900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4354600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4098000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3511800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5327700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5653600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2538400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2272100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2209500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1903900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1117900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1093400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1033900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1497800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2281900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1593000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1303200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1221700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1103800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1091500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2168300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2172900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2643500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6770500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2816200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4629600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7606000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9319000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4691800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4248500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5135800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5984500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2537300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2381300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1427600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1688500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1442100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2328000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2975500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4170100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2239900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1948300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2444200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4481500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>8988500</v>
+      </c>
+      <c r="E60" s="3">
         <v>8855900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10120600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14671900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11245100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12785000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15137600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16312800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13627800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12847200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10855500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11121200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7259700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6133800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4059200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4192300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3839300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5117900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6388500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7517000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5653000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5093100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5371000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7231700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>24645600</v>
+      </c>
+      <c r="E61" s="3">
         <v>25079000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23930800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24196400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23300300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22769000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21797100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>21624200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22304700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21281400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23135700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21548700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20605100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18309500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9394800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9384300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8779800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11336200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10598900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10485200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8639000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9688200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9012400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9095000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>3867100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7550400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7462400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7807500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4909800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6892800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6780000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5967400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9015300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9694700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9740800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9368600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8254700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7994800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5164400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5067400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4936500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4931700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4975800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5437900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5235000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4019500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4026100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4060300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>43398300</v>
+      </c>
+      <c r="E66" s="3">
         <v>45043200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45310200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50670800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46252400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44794700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45902800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45943300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51680400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50316600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>49990000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47937600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41404100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39212600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19406800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19405700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18337600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22287100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22919800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24429400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20549300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19382000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19002400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20923200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>9190200</v>
+      </c>
+      <c r="E72" s="3">
         <v>8785000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7997600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7698100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9943200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8476400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6998700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5425900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10521600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9247300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7143800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6217600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6914900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4951900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3927300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3144800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2643400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2859000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2653800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2868400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4758100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4799200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3986200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3044700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>18980600</v>
+      </c>
+      <c r="E76" s="3">
         <v>18774900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17827600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17944600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20235400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19310300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17932400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15684500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21848300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20466300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18358000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17278400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17215900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13858900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12356600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11450100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10940000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12820300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12396200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13669400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14667200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15986900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14779400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13683900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7346,221 +7534,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E81" s="3">
         <v>875300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>816200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1039700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1091500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1257200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>979500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1222700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1644200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2378200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2722200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1708900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1458500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>837600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>782100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>648000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>141800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>205200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>34600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1042300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>813000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>941500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>741000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>688300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>749200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>784400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>321100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>417500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>283500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>61400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7597,112 +7794,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>737500</v>
+      </c>
+      <c r="E83" s="3">
         <v>874800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>805500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>683200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>525300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>691800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>684600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>722000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>811100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>796000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>742600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>704500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>666200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>591000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>503100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>483400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>523300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>551700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>549500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>579700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>592200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>595600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>565200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>537500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>497000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>559000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>537300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>588000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>713800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>683300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>660300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>634300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8221,112 +8434,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2172300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2989800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4126900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1558800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2685000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1035700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>752000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>447400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2726200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3733800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1600000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>984400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2642300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1161500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>695900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>616000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1120400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>846400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-539500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>668800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1966900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2513500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1620900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1305300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>478900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8363,112 +8582,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1499000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1182000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1076300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1052300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1784200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-1783400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1508300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1279700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1068800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-295700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-178500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-359700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-320800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-278300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-214000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-385700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-324300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-196700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8675,112 +8901,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1412100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1744500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1039100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1693900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1289200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1079500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-807400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-722400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-916800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-552000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-145300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-462600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-40800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-224600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-712600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-475200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-293400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>130100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8817,112 +9049,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="3">
         <v>146800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2882300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>70100</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3">
+        <v>236800</v>
+      </c>
+      <c r="I96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>559200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>49000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-520800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-71100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-323200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-60300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-206300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-35300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-732400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-698500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-458600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-110700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-990600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-832000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9233,316 +9475,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-831900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1174600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3560500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>156700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-523500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-536400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>407500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-627800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-402100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-734000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2906600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-507400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-163600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2061800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-266700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-954100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-274300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-399200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-62700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-136000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-26700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>160600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>14300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>195100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>186800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>16500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>211600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>79700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>30000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-99000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-144100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>270100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-38800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>108200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>30500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>107900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>51800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>9800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>69600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E102" s="3">
         <v>206700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-466600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>733700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>68500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>184400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-999900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>596000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>703500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-143200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1071100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1114400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-349900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>337100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-576700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-340600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>108200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>447600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-516200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>955000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-921700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>709100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>211400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>30000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>513900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>230300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>EC</t>
   </si>
@@ -656,476 +656,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7478500</v>
+      </c>
+      <c r="E8" s="3">
         <v>7890100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8300800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7888400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8112400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8981500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8683800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8219600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8393000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9522700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10859600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11410100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8442900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7622700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5133200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4083300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3613300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2979900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2957500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2026000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3918700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4831100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4863900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4943300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4304500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4045500</v>
+      </c>
+      <c r="E9" s="3">
         <v>5423000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5386000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4909200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4857400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5915000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5003200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5069300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4846100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5761800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6108800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6000200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4663800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4591800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3191300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2400600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2207500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2164400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2002500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1827700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2934600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3190200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3034900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3027600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2763200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3433000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2467000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2914900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2979200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3255000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3066500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3680700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3150200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3546900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3760900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4750800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5409900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3779100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3030900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1941900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1682700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1405700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>815500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>955000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>198300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>984100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1641000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1829000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1915700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1541300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,86 +1206,89 @@
       <c r="K12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" s="3">
         <v>209900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>115700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>101600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>66200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>35300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>86600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>33600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>103000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>15700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>66900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>16600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>50300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>271600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>56400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>21200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>292200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>103900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>24700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>96800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1377,222 +1394,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>-260500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-68500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>81100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-116500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-328800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>314200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>187600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>149000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>244000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>891300</v>
+      </c>
+      <c r="E15" s="3">
         <v>75500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1023400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>961300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>975200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>555900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1050500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>833800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>715100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>79300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>31900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>33800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>89200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>13600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>40200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>20000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>46000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>11200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>11500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>6100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>15000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>10900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>16400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,222 +1653,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5480400</v>
+      </c>
+      <c r="E17" s="3">
         <v>5924200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6060500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5578700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5560400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7522300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5831500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5691800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5426800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6706600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6554200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6572100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5185200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5129400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3570700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2706400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2455500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2553800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2319800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1827300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3529200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3845900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3321700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3334800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2966200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1998100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1965800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2240300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2309700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2552000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1459200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2852300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2527800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2966100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2816100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4305400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4838000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3257700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2493200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1562500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1376900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1157800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>426100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>637700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>198700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>389600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>985200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1542100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1608600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1338300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>538900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1880,543 +1913,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="E20" s="3">
         <v>108200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>128700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>126300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>121800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-206800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>157700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>65800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-44700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-109400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-58100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>25500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-34100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>70200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-70500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>31500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-47000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>80100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>43400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>61300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>83200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>19300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>45700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>26900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>18100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>117200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>291700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2939200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1933200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3135000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3144700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3405400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2009900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4109600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3203800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3685700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3693000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5056700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5471100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3904100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3137800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2179000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1845800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1632900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1019600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1118900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>779700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>922300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1657500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2106000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2217200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1937100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>576500</v>
+      </c>
+      <c r="E22" s="3">
         <v>465000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>439000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>430000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>445300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>457600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>425800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>404900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>375500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>391500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>363900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>346400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>285600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>294600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>154300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>127500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>117300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>125700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>155400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>156700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>126200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>127000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>128100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>129500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>122000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>183100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>144600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>347900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>171800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>206800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>198200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>153300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>205200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>226800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1471400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1746800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1768100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1845700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2072600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1116600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2792100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2063300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2712500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2490400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3896800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4382200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2914000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2177000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1433600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1215200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1032100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>370700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>411700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>73500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>216300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>938200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1382300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1522500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>806300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>739400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>603800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>462300</v>
+      </c>
+      <c r="E24" s="3">
         <v>606000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>543000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>781800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>757000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-194300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1311900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>799400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1208200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>643600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1278900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1380500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1009800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>495300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>482700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>371200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>322700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>178300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>137100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>91500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-186900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>477900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>505400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>451800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>303400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>589000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>564000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>457200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>414600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>535100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>396300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>485600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2522,222 +2571,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1009100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1140700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1225100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1063900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1315600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1311000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1480200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1263900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1504300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1846800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2617900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3001700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1904200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1681700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>951000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>844000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>709400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>192400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>274600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>72400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>124800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1125100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>904500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1017100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>825800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>765200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>811900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>845100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>391700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>474500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>343200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>118200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>745600</v>
+      </c>
+      <c r="E27" s="3">
         <v>884000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>875300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>816200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1039700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1091500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1257200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>979500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1222700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1644200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2378200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2722200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1708900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1458500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>837600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>782100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>648000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>141800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>205200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>34600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1042300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>813000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>941500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>741000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>688300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>749200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>784400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>321100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>417500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>283500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>61400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2950,8 +3011,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3164,222 +3231,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-108200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-128700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-126300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-121800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>206800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-157700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-65800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>44700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>109400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>58100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>21600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-25500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>34100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-70200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>70500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-31500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>47000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-80100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>31700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-61300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>58800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>111000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>745600</v>
+      </c>
+      <c r="E33" s="3">
         <v>884000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>875300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>816200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1039700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1091500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1257200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>979500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1222700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1644200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2378200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2722200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1708900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1458500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>837600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>782100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>648000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>141800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>205200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>34600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1042300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>813000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>941500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>741000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>688300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>749200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>784400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>321100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>417500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>283500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>61400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3485,227 +3561,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>745600</v>
+      </c>
+      <c r="E35" s="3">
         <v>884000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>875300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>816200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1039700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1091500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1257200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>979500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1222700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1644200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2378200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2722200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1708900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1458500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>837600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>782100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>648000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>141800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>205200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>34600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1042300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>813000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>941500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>741000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>688300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>749200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>784400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>321100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>417500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>283500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>61400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3782,971 +3868,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" s="3">
         <v>3187200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3381700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3200300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3930800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3184300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2983700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2713800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3347700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3696300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3229400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2626900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3639800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3492000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2219100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1054500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1404400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1067300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1878900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2219500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2287300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1839700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2446500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1491500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2413200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>193100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>537100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>510800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>441500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>480400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>433100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>218400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>363800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>400600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>672700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>431200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>560000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>517100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>467300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>102400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>156800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>506700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>839200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>999800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>247600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>459900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>662000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>906600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1349100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="3">
         <v>7226000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7387300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7745000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11217900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10692300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11260800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12220100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11822500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11251700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9999900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9332300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7984900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6087200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5301400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3306500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2555100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1960700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2097900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2059500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1806900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2131500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2049800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2634900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2725700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="3">
         <v>2274100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2616200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2748600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2802500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2633600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2807200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2467200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2402800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2851200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2695900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3165900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2852700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2015600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1997200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1507200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1345600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1061300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1322500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1208400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1511100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1471100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1594800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1580600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1479100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="3">
         <v>510100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>574100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>638200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>632900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>517500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>556300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>598700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>556400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>346700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>405200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>306400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>341400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>295100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>358600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>175900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>224100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>199200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>282900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>216900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>304500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>172500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>196300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>144400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>146700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>138600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>131000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>125000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>131300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>125800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>180600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>191400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>169900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>140500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E46" s="3">
         <v>13752300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14835800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15013700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19207200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17711700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18275700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18365100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18650500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18546400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17003100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15862700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15378800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12407000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10343600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6146600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5686000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4795200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6421200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6704100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6157500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6074800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6949500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6758000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8113900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="3">
         <v>2957400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3061800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2228400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2335200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2269100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2243600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2379700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2169700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10371700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9597600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9415100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9386800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8117900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7244100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1100900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1015100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>992900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1208900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1451100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1642600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1920700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1956400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1743300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1335500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="3">
         <v>35400200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35360500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35454400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36778400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36455600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34609400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33539900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31065700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34547700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34531700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33960900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32323000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30365200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25704900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21623400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21324800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20752300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24092400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23977800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26598600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24369500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24227100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23212000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23085100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>4834600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4918100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4937100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5013600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4987400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5014100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5012800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4875200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5581500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5565400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5331700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4982500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4626800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6636400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>407900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>402700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>400900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>460900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>357200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>397400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>364700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>355300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>354900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>361500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>345800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>354300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>383600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>384100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>415900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>404900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>375200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>380300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>393200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4959,115 +5076,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="3">
         <v>1308400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5152300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5187700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4681600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1390700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3707800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4043600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4335700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4481300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4085100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3777700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3144900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3103100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3142400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2484600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2427200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2336300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2923900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2825800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3302800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2486900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1880600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1713700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1711100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" s="3">
         <v>68338400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70209700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69221700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74817800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>72865400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70505000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70224100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>67474900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>73528700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70783000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>68348000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65215900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58620000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>53071400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31763400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30855800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29277600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35107300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35316000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38098900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35216500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35368900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33781800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34607100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="3">
         <v>3432900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2979200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2852300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3047300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3554400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2988400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2769200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2806000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3608300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2945100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3181400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2864600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2512900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1848600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1513700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1410300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1363300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1292100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1131100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1753800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2109900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1923100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1823000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1658600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>2559900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2837800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3877900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3979100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4013900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4354600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4098000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3511800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5327700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5653600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2538400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2272100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2209500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1903900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1117900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1093400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1033900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1497800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2281900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1593000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1303200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1221700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1103800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1091500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" s="3">
         <v>2168300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2172900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2643500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6770500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2816200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4629600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7606000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9319000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4691800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4248500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5135800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5984500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2537300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2381300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1427600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1688500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1442100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2328000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2975500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4170100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2239900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1948300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2444200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4481500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E60" s="3">
         <v>8988500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8855900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10120600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14671900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11245100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12785000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15137600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16312800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13627800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12847200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10855500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11121200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7259700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6133800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4059200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4192300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3839300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5117900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6388500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7517000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5653000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5093100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5371000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7231700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>24645600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25079000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23930800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24196400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23300300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22769000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>21797100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21624200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22304700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21281400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23135700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21548700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20605100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18309500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9394800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9384300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8779800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11336200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10598900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10485200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8639000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9688200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9012400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9095000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62" s="3">
         <v>3867100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7550400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7462400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7807500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4909800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6892800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6780000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5967400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9015300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9694700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9740800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9368600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8254700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7994800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5164400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5067400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4936500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4931700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4975800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5437900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5235000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4019500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4026100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4060300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E66" s="3">
         <v>43398300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45043200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45310200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50670800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46252400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44794700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45902800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45943300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51680400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50316600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>49990000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47937600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>41404100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39212600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19406800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19405700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18337600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22287100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22919800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24429400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20549300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19382000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19002400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20923200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" s="3">
         <v>9190200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8785000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7997600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7698100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9943200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8476400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6998700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5425900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10521600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9247300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7143800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6217600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6914900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4951900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3927300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3144800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2643400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2859000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2653800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2868400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4758100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4799200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3986200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3044700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>19956300</v>
+      </c>
+      <c r="E76" s="3">
         <v>18980600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18774900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17827600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17944600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20235400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19310300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17932400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15684500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21848300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20466300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18358000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17278400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17215900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13858900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12356600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11450100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10940000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12820300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12396200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13669400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14667200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15986900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14779400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13683900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7537,227 +7726,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>745600</v>
+      </c>
+      <c r="E81" s="3">
         <v>884000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>875300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>816200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1039700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1091500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1257200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>979500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1222700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1644200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2378200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2722200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1708900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1458500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>837600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>782100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>648000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>141800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>205200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>34600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1042300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>813000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>941500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>741000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>688300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>749200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>784400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>321100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>417500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>283500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>61400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E83" s="3">
         <v>737500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>874800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>805500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>683200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>525300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>691800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>684600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>722000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>811100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>796000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>742600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>704500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>666200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>591000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>503100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>483400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>523300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>551700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>549500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>579700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>592200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>595600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>565200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>537500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>497000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>559000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>537300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>588000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>713800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>683300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>660300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>634300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8437,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E89" s="3">
         <v>2172300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2989800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4126900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1558800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2685000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1035700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>752000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>447400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2726200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3733800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1600000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>984400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2642300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1161500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>695900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>616000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1120400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>846400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-539500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>668800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1966900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2513500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1620900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1305300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>478900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8583,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1499000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1182000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1076300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1052300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1783400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1508300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1279700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1068800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-295700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-178500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-359700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-320800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-278300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-214000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-385700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-324300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-196700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8904,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1412100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1744500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1039100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1693900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1289200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1079500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-807400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-900300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-722400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-916800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-552000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-145300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-462600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-40800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-224600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-712600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-475200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-293400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>130100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9050,115 +9283,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="3">
         <v>146800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2882300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>70100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>236800</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>559200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>49000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-520800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-71100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-323200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-60300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-206300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-35300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-732400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-698500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-458600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-110700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-990600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-832000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9478,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E100" s="3">
         <v>-831900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1174600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3560500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>156700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-523500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-536400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>407500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-627800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-402100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-734000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2906600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-507400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-163600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2061800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-266700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-954100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-274300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-399200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-62700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-136000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-26700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>160600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>195100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>186800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>16500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>211600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>79700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-10700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>13700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>30000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-99000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-144100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>270100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-38800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>108200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>30500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>107900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>51800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>9800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>69600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>51000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>206700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-466600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>733700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>68500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>184400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-999900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>596000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>703500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-143200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1071100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1114400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-349900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>337100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-576700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-340600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>108200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>447600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-516200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>955000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-921700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>709100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>211400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>30000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>513900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>230300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>EC</t>
   </si>
@@ -656,489 +656,502 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7478500</v>
+        <v>7265700</v>
       </c>
       <c r="E8" s="3">
+        <v>7478600</v>
+      </c>
+      <c r="F8" s="3">
         <v>7890100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8300800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7888400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8112400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8981500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8683800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8219600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8393000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9522700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10859600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11410100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8442900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7622700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5133200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4083300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3613300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2979900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2957500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2026000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3918700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4831100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4863900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4943300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4304500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4045500</v>
+        <v>5087200</v>
       </c>
       <c r="E9" s="3">
+        <v>4844400</v>
+      </c>
+      <c r="F9" s="3">
         <v>5423000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5386000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4909200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4857400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5915000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5003200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5069300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4846100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5761800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6108800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6000200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4663800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4591800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3191300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2400600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2207500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2164400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2002500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1827700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2934600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3190200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3034900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3027600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2763200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3433000</v>
+        <v>2178500</v>
       </c>
       <c r="E10" s="3">
+        <v>2634200</v>
+      </c>
+      <c r="F10" s="3">
         <v>2467000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2914900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2979200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3255000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3066500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3680700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3150200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3546900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3760900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4750800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5409900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3779100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3030900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1941900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1682700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1405700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>815500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>955000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>198300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>984100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1641000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1829000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1915700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1541300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,86 +1223,89 @@
       <c r="L12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="3">
         <v>209900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>115700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>101600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>66200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>35300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>86600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>23800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>33600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>103000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>15700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>66900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>16600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>50300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>271600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>56400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>21200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>292200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>103900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>8600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>96800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,228 +1414,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>91</v>
+      <c r="D14" s="3">
+        <v>6600</v>
       </c>
       <c r="E14" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F14" s="3">
         <v>-260500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-68500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>81100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>24000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-116500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-328800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>314200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>187600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>149000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>244000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>891300</v>
+        <v>1141900</v>
       </c>
       <c r="E15" s="3">
+        <v>912400</v>
+      </c>
+      <c r="F15" s="3">
         <v>75500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1023400</v>
       </c>
-      <c r="G15" s="3">
-        <v>961300</v>
-      </c>
       <c r="H15" s="3">
-        <v>975200</v>
+        <v>979600</v>
       </c>
       <c r="I15" s="3">
+        <v>995100</v>
+      </c>
+      <c r="J15" s="3">
         <v>555900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1050500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>833800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>715100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>79300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>31900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>34000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>33800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>89200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>14100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>40200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>12900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>20000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>46000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>10700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>7800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>11500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>6100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>15000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>13300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>16400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,228 +1680,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5480400</v>
+        <v>5878700</v>
       </c>
       <c r="E17" s="3">
+        <v>5476600</v>
+      </c>
+      <c r="F17" s="3">
         <v>5924200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6060500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5578700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5560400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7522300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5831500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5691800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5426800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6706600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6554200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6572100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5185200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5129400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3570700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2706400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2455500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2553800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2319800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1827300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3529200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3845900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3321700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3334800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2966200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1998100</v>
+        <v>1387000</v>
       </c>
       <c r="E18" s="3">
+        <v>2002000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1965800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2240300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2309700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2552000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1459200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2852300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2527800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2966100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2816100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4305400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4838000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3257700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2493200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1562500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1376900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1157800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>426100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>637700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>198700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>389600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>985200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1542100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1608600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1338300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>538900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1914,558 +1947,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-49800</v>
+        <v>78700</v>
       </c>
       <c r="E20" s="3">
+        <v>157100</v>
+      </c>
+      <c r="F20" s="3">
         <v>108200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>128700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>126300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>121800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-206800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>157700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>65800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-44700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-109400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-21600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-34100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>70200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-70500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>31500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>80100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>43400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>61300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>83200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>19300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>45700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>26900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>18100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>117200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>291700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2939200</v>
+        <v>2450200</v>
       </c>
       <c r="E21" s="3">
+        <v>2757300</v>
+      </c>
+      <c r="F21" s="3">
         <v>1933200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3135000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3144700</v>
-      </c>
       <c r="H21" s="3">
-        <v>3405400</v>
+        <v>3163000</v>
       </c>
       <c r="I21" s="3">
+        <v>3425300</v>
+      </c>
+      <c r="J21" s="3">
         <v>2009900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4109600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3203800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3685700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3693000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5056700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5471100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3904100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3137800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2179000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1845800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1632900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1019600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1118900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>779700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>922300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1657500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2106000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2217200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1937100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>576500</v>
+        <v>470600</v>
       </c>
       <c r="E22" s="3">
+        <v>442100</v>
+      </c>
+      <c r="F22" s="3">
         <v>465000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>439000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>430000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>445300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>457600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>425800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>404900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>375500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>391500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>363900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>346400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>285600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>294600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>154300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>127500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>117300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>125700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>155400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>156700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>126200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>127000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>128100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>129500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>122000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>183100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>144600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>347900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>171800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>206800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>198200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>153300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>205200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>226800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1471400</v>
+        <v>916100</v>
       </c>
       <c r="E23" s="3">
+        <v>1471500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1746800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1768100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1845700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2072600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1116600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2792100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2063300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2712500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2490400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3896800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4382200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2914000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2177000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1433600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1215200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1032100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>370700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>411700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>73500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>216300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>938200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1382300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1522500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>806300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>739400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>603800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>462300</v>
+        <v>314600</v>
       </c>
       <c r="E24" s="3">
+        <v>462400</v>
+      </c>
+      <c r="F24" s="3">
         <v>606000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>543000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>781800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>757000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-194300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1311900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>799400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1208200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>643600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1278900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1380500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1009800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>495300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>482700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>371200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>322700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>178300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>137100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>91500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-186900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>477900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>505400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>451800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>303400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>589000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>564000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>457200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>414600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>535100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>396300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>485600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2574,228 +2623,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1009100</v>
+        <v>601500</v>
       </c>
       <c r="E26" s="3">
+        <v>1009000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1140700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1225100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1063900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1315600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1311000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1480200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1263900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1504300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1846800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2617900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3001700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1904200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1681700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>951000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>844000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>709400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>192400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>274600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>72400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>124800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1125100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>904500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1017100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>825800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>765200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>811900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>845100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>391700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>474500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>343200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>118200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E27" s="3">
         <v>745600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>884000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>875300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>816200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1039700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1091500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1257200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>979500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1222700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1644200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2378200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2722200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1708900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1458500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>837600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>782100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>648000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>141800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>205200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>34600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1042300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>813000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>941500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>741000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>688300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>749200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>784400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>321100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>417500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>283500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>61400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2904,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3014,8 +3075,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,228 +3301,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>49800</v>
+        <v>-78700</v>
       </c>
       <c r="E32" s="3">
+        <v>-157100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-108200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-128700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-126300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-121800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>206800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-157700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-65800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>44700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>109400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>58100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>21600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>34100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-70200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>70500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-31500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>47000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-80100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>31700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-61300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>58800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>111000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E33" s="3">
         <v>745600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>884000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>875300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>816200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1039700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1091500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1257200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>979500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1222700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1644200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2378200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2722200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1708900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1458500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>837600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>782100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>648000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>141800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>205200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>34600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1042300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>813000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>941500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>741000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>688300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>749200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>784400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>321100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>417500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>283500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>61400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3564,233 +3640,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E35" s="3">
         <v>745600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>884000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>875300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>816200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1039700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1091500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1257200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>979500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1222700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1644200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2378200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2722200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1708900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1458500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>837600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>782100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>648000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>141800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>205200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>34600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1042300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>813000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>941500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>741000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>688300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>749200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>784400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>321100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>417500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>283500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>61400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3869,998 +3955,1026 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>91</v>
+      <c r="D41" s="3">
+        <v>2477800</v>
       </c>
       <c r="E41" s="3">
+        <v>3362500</v>
+      </c>
+      <c r="F41" s="3">
         <v>3187200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3381700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3200300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3930800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3184300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2983700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2713800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3347700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3696300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3229400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2626900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3639800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3492000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2219100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1054500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1404400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1067300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1878900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2219500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2287300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1839700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2446500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1491500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2413200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1034000</v>
       </c>
       <c r="E42" s="3">
+        <v>602700</v>
+      </c>
+      <c r="F42" s="3">
         <v>193100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>537100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>510800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>441500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>480400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>433100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>218400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>363800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>400600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>672700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>431200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>560000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>517100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>467300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>102400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>156800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>506700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>839200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>999800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>247600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>459900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>662000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>906600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1349100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>91</v>
+      <c r="D43" s="3">
+        <v>7523900</v>
       </c>
       <c r="E43" s="3">
+        <v>7771100</v>
+      </c>
+      <c r="F43" s="3">
         <v>7226000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7387300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7745000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11217900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10692300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11260800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12220100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11822500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11251700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9999900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9332300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7984900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6087200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5301400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3306500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2555100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1960700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2097900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2059500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1806900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2131500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2049800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2634900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2725700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>91</v>
+      <c r="D44" s="3">
+        <v>2546300</v>
       </c>
       <c r="E44" s="3">
+        <v>2630500</v>
+      </c>
+      <c r="F44" s="3">
         <v>2274100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2616200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2748600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2802500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2633600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2807200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2467200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2402800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2851200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2695900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3165900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2852700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2015600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1997200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1507200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1345600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1061300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1322500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1208400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1511100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1471100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1594800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1580600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1479100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>91</v>
+      <c r="D45" s="3">
+        <v>588100</v>
       </c>
       <c r="E45" s="3">
+        <v>546500</v>
+      </c>
+      <c r="F45" s="3">
         <v>510100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>574100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>638200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>632900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>517500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>556300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>598700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>556400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>346700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>405200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>306400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>341400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>295100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>358600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>175900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>224100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>199200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>282900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>216900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>304500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>172500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>196300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>144400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>146700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>138600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>131000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>125000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>131300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>125800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>180600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>191400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>169900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>140500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>91</v>
+      <c r="D46" s="3">
+        <v>14490000</v>
       </c>
       <c r="E46" s="3">
+        <v>15258700</v>
+      </c>
+      <c r="F46" s="3">
         <v>13752300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14835800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15013700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19207200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17711700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18275700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18365100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18650500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18546400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17003100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15862700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15378800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12407000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10343600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6146600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5686000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4795200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6421200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6704100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6157500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6074800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6949500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6758000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8113900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>91</v>
+      <c r="D47" s="3">
+        <v>3088700</v>
       </c>
       <c r="E47" s="3">
+        <v>2927800</v>
+      </c>
+      <c r="F47" s="3">
         <v>2957400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3061800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2228400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2335200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2269100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2243600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2379700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2169700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10371700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9597600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9415100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9386800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8117900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7244100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1100900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1015100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>992900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1208900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1451100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1642600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1920700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1956400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1743300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1335500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>91</v>
+      <c r="D48" s="3">
+        <v>37415500</v>
       </c>
       <c r="E48" s="3">
+        <v>36640300</v>
+      </c>
+      <c r="F48" s="3">
         <v>35400200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35360500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35454400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36778400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36455600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34609400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33539900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31065700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34547700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34531700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33960900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32323000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30365200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25704900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21623400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21324800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20752300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24092400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23977800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>26598600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24369500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24227100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23212000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>23085100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>4868400</v>
       </c>
       <c r="E49" s="3">
+        <v>4853100</v>
+      </c>
+      <c r="F49" s="3">
         <v>4834600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4918100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4937100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5013600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4987400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5014100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5012800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4875200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5581500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5565400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5331700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4982500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4626800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6636400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>407900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>402700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>400900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>460900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>357200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>397400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>364700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>355300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>354900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>361500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>345800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>354300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>383600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>384100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>415900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>404900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>375200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>380300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>393200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5079,118 +5196,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>91</v>
+      <c r="D52" s="3">
+        <v>4816500</v>
       </c>
       <c r="E52" s="3">
+        <v>4884000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1308400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5152300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5187700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4681600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1390700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3707800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4043600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4335700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4481300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4085100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3777700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3144900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3103100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3142400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2484600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2427200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2336300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2923900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2825800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3302800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2486900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1880600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1713700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1711100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5299,118 +5422,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>91</v>
+      <c r="D54" s="3">
+        <v>72146400</v>
       </c>
       <c r="E54" s="3">
+        <v>71607200</v>
+      </c>
+      <c r="F54" s="3">
         <v>68338400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70209700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>69221700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74817800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72865400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70505000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70224100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>67474900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73528700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70783000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>68348000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>65215900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58620000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>53071400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31763400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>30855800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29277600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35107300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35316000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>38098900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35216500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35368900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33781800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34607100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5489,668 +5619,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>91</v>
+      <c r="D57" s="3">
+        <v>2794000</v>
       </c>
       <c r="E57" s="3">
+        <v>2866300</v>
+      </c>
+      <c r="F57" s="3">
         <v>3432900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2979200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2852300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3047300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3554400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2988400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2769200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2806000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3608300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2945100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3181400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2864600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2512900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1848600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1513700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1410300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1363300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1292100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1131100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1753800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2109900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1923100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1823000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1658600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3830000</v>
       </c>
       <c r="E58" s="3">
+        <v>3109400</v>
+      </c>
+      <c r="F58" s="3">
         <v>2559900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2837800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3877900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3979100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4013900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4354600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4098000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3511800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5327700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5653600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2538400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2272100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2209500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1903900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1117900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1093400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1033900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1497800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2281900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1593000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1303200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1221700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1103800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1091500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>91</v>
+      <c r="D59" s="3">
+        <v>2580100</v>
       </c>
       <c r="E59" s="3">
+        <v>4732500</v>
+      </c>
+      <c r="F59" s="3">
         <v>2168300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2172900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2643500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6770500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2816200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4629600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7606000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9319000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4691800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4248500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5135800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5984500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2537300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2381300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1427600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1688500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1442100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2328000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2975500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4170100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2239900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1948300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2444200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4481500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>91</v>
+      <c r="D60" s="3">
+        <v>9964300</v>
       </c>
       <c r="E60" s="3">
+        <v>11477700</v>
+      </c>
+      <c r="F60" s="3">
         <v>8988500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8855900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10120600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14671900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11245100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12785000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15137600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16312800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13627800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12847200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10855500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11121200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7259700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6133800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4059200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4192300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3839300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5117900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6388500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7517000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5653000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5093100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5371000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7231700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>25620000</v>
       </c>
       <c r="E61" s="3">
+        <v>25183600</v>
+      </c>
+      <c r="F61" s="3">
         <v>24645600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25079000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23930800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24196400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23300300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22769000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21797100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21624200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22304700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21281400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23135700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21548700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20605100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18309500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9394800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9384300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8779800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11336200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10598900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10485200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8639000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9688200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9012400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9095000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>91</v>
+      <c r="D62" s="3">
+        <v>4244400</v>
       </c>
       <c r="E62" s="3">
+        <v>6979900</v>
+      </c>
+      <c r="F62" s="3">
         <v>3867100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7550400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7462400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7807500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4909800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6892800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6780000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5967400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9015300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9694700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9740800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9368600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8254700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7994800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5164400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5067400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4936500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4931700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4975800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5437900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5235000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4019500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4026100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4060300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6479,118 +6634,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>91</v>
+      <c r="D66" s="3">
+        <v>46291000</v>
       </c>
       <c r="E66" s="3">
+        <v>46977300</v>
+      </c>
+      <c r="F66" s="3">
         <v>43398300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45043200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45310200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50670800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46252400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44794700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45902800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45943300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51680400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>50316600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>49990000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47937600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41404100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39212600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19406800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19405700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18337600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22287100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22919800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24429400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20549300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19382000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19002400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>20923200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7069,118 +7240,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>91</v>
+      <c r="D72" s="3">
+        <v>8978700</v>
       </c>
       <c r="E72" s="3">
+        <v>8310200</v>
+      </c>
+      <c r="F72" s="3">
         <v>9190200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8785000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7997600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7698100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9943200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8476400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6998700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5425900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10521600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9247300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7143800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6217600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6914900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4951900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3927300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3144800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2643400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2859000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2653800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2868400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4758100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4799200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3986200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3044700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7509,118 +7692,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>19956300</v>
+        <v>19401200</v>
       </c>
       <c r="E76" s="3">
+        <v>18475300</v>
+      </c>
+      <c r="F76" s="3">
         <v>18980600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18774900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17827600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17944600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20235400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19310300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17932400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15684500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21848300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20466300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18358000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17278400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17215900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13858900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12356600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11450100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10940000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12820300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12396200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13669400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14667200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15986900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14779400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13683900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7729,233 +7918,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E81" s="3">
         <v>745600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>884000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>875300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>816200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1039700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1091500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1257200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>979500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1222700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1644200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2378200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2722200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1708900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1458500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>837600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>782100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>648000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>141800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>205200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>34600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1042300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>813000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>941500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>741000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>688300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>749200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>784400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>321100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>417500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>283500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>61400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7994,118 +8192,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>867000</v>
+        <v>897900</v>
       </c>
       <c r="E83" s="3">
+        <v>926000</v>
+      </c>
+      <c r="F83" s="3">
         <v>737500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>874800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>805500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>683200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>525300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>691800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>684600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>722000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>811100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>796000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>742600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>704500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>666200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>591000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>503100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>483400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>523300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>551700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>549500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>579700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>592200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>595600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>565200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>537500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>497000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>559000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>537300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>588000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>713800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>683300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>660300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>634300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8654,118 +8868,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>91</v>
+      <c r="D89" s="3">
+        <v>2460100</v>
       </c>
       <c r="E89" s="3">
+        <v>1459800</v>
+      </c>
+      <c r="F89" s="3">
         <v>2172300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2989800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4126900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1558800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2685000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1035700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>752000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>447400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2726200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3733800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1600000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>984400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2642300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1161500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>695900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>616000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1120400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>846400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-539500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>668800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1966900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2513500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1620900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1305300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>478900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8804,118 +9024,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>91</v>
+      <c r="D91" s="3">
+        <v>-1196500</v>
       </c>
       <c r="E91" s="3">
+        <v>-1191500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1499000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1182000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1076300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1052300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1783400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1508300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1279700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1068800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-295700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-178500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-359700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-320800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-278300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-214000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-385700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-324300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-196700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9134,118 +9361,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>91</v>
+      <c r="D94" s="3">
+        <v>-1490000</v>
       </c>
       <c r="E94" s="3">
+        <v>-1303700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1412100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1744500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1039100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1693900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1289200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1079500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-807400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-722400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-916800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-552000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-145300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-462600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-40800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-224600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-712600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-475200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-293400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>130100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9284,118 +9517,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>91</v>
+      <c r="D96" s="3">
+        <v>2151000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G96" s="3">
         <v>146800</v>
       </c>
-      <c r="G96" s="3">
-        <v>2882300</v>
-      </c>
       <c r="H96" s="3">
-        <v>70100</v>
-      </c>
-      <c r="I96" s="3">
+        <v>2555500</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" s="3">
         <v>236800</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>559200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>49000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-520800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-71100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-323200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-60300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-206300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-35300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-732400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-698500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-458600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-110700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-990600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-832000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9724,334 +9967,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>91</v>
+      <c r="D100" s="3">
+        <v>-1883600</v>
       </c>
       <c r="E100" s="3">
+        <v>-136500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-831900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1174600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3560500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>156700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-523500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-536400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>407500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-627800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-402100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-734000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2906600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-507400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-163600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2061800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-266700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-954100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-274300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E101" s="3">
         <v>57300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-399200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-62700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-136000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-26700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>160600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>14300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>195100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>186800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>16500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>211600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>79700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-10700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>30000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-99000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-144100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>270100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-38800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>108200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>30500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>107900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>51800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>9800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>51000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-975600</v>
       </c>
       <c r="E102" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-10000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>206700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-466600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>733700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>68500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>184400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-999900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>596000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>703500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-143200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1071100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1114400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-349900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>337100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-576700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-340600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>108200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>447600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-516200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>955000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-921700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>709100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>211400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>30000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>513900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>230300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7642900</v>
+      </c>
+      <c r="E8" s="3">
         <v>7594400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7265800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7478600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7890100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8300800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7888400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8112400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8981500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8683800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8219600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8393000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9522700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10859600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11410100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8442900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7622700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5133200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4083300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3613300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2979900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2957500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2026000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3918700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4831100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4863900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4943300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4304500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5273300</v>
+      </c>
+      <c r="E9" s="3">
         <v>4964900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5087200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4844400</v>
       </c>
-      <c r="G9" s="3">
-        <v>5423000</v>
-      </c>
       <c r="H9" s="3">
+        <v>5415500</v>
+      </c>
+      <c r="I9" s="3">
         <v>5242600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5061700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4857400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5915000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5003200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5069300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4846100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5761800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6108800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6000200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4663800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4591800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3191300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2400600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2207500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2164400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2002500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1827700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2934600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3190200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3034900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3027600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2763200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2369600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2629500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2178500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2634200</v>
       </c>
-      <c r="G10" s="3">
-        <v>2467000</v>
-      </c>
       <c r="H10" s="3">
+        <v>2474600</v>
+      </c>
+      <c r="I10" s="3">
         <v>3058200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2826700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3255000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3066500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3680700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3150200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3546900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3760900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4750800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5409900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3779100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3030900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1941900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1682700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1405700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>815500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>955000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>198300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>984100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1641000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1829000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1915700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1541300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1205,8 +1217,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1243,86 +1256,89 @@
       <c r="N12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="3">
         <v>209900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>115700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>101600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>66200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>35300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>86600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>23800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>33600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>103000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>15700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>66900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>16600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>50300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>271600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>56400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>21200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>292200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>103900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>24700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>8600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>96800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1437,240 +1453,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-137100</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>53300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3900</v>
       </c>
-      <c r="G14" s="3">
-        <v>-260500</v>
-      </c>
       <c r="H14" s="3">
+        <v>-295700</v>
+      </c>
+      <c r="I14" s="3">
         <v>35700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-68500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>81100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>24000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-116500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-328800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>314200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>187600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>149000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>7900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>244000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1047600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1141900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>912400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>75500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1042600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>979600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>995100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>555900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1050500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>833800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>715100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>79300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>31900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>33800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>89200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>14100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>13600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>40200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>12900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>20000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>46000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>11200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>7800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>11500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>6100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>15000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>10900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>13300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>16400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1708,240 +1733,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6367300</v>
+      </c>
+      <c r="E17" s="3">
         <v>5699600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5832100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5476600</v>
       </c>
-      <c r="G17" s="3">
-        <v>5924200</v>
-      </c>
       <c r="H17" s="3">
+        <v>5959500</v>
+      </c>
+      <c r="I17" s="3">
         <v>6033000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5569000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5560400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7522300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5831500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5691800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5426800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6706600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6554200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6572100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5185200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5129400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3570700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2706400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2455500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2553800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2319800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1827300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3529200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3845900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3321700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3334800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2966200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1275600</v>
+      </c>
+      <c r="E18" s="3">
         <v>1894800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1433700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2002000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1965800</v>
-      </c>
       <c r="H18" s="3">
+        <v>1930600</v>
+      </c>
+      <c r="I18" s="3">
         <v>2267900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2319400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2552000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1459200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2852300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2527800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2966100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2816100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4305400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4838000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3257700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2493200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1562500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1376900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1157800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>426100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>637700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>198700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>389600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>985200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1542100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1608600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1338300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>538900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1982,588 +2014,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E20" s="3">
         <v>46100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>78800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>157100</v>
       </c>
-      <c r="G20" s="3">
-        <v>108200</v>
-      </c>
       <c r="H20" s="3">
+        <v>107900</v>
+      </c>
+      <c r="I20" s="3">
         <v>128800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>126300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>121800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-206800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>157700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>65800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-44700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-109400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-58100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-21600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>25500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-34100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>70200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-70500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>31500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>80100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-31700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>43400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>61300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>83200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>19300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>45700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>26900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>117200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>291700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1268500</v>
+      </c>
+      <c r="E21" s="3">
         <v>2896400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2496800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2757300</v>
       </c>
-      <c r="G21" s="3">
-        <v>1933200</v>
-      </c>
       <c r="H21" s="3">
+        <v>1898100</v>
+      </c>
+      <c r="I21" s="3">
         <v>3181600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3172700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3425300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2009900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4109600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3203800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3685700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3693000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5056700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5471100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3904100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3137800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2179000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1845800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1632900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1019600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1118900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>779700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>922300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1657500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2106000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2217200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1937100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>492500</v>
+      </c>
+      <c r="E22" s="3">
         <v>501600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>470600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>442100</v>
       </c>
-      <c r="G22" s="3">
-        <v>465000</v>
-      </c>
       <c r="H22" s="3">
+        <v>464900</v>
+      </c>
+      <c r="I22" s="3">
         <v>438900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>430100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>445300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>457600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>425800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>404900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>375500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>391500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>363900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>346400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>285600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>294600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>154300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>127500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>117300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>125700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>155400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>156700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>126200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>127000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>128100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>129500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>122000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>183100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>144600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>347900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>171800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>206800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>198200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>153300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>205200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>226800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>921000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1393700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>916100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1471500</v>
       </c>
-      <c r="G23" s="3">
-        <v>1746800</v>
-      </c>
       <c r="H23" s="3">
+        <v>1746900</v>
+      </c>
+      <c r="I23" s="3">
         <v>1768000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1845700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2072600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1116600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2792100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2063300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2712500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2490400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3896800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4382200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2914000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2177000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1433600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1215200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1032100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>370700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>411700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>73500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>216300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>938200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1382300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1522500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>806300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>739400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>603800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>263600</v>
+      </c>
+      <c r="E24" s="3">
         <v>435200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>314300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>462400</v>
       </c>
-      <c r="G24" s="3">
-        <v>606000</v>
-      </c>
       <c r="H24" s="3">
+        <v>606200</v>
+      </c>
+      <c r="I24" s="3">
         <v>543000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>781700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>757000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-194300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1311900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>799400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1208200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>643600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1278900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1380500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1009800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>495300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>482700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>371200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>322700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>178300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>137100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>91500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-186900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>477900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>505400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>451800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>303400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>589000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>564000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>457200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>414600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>535100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>396300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>485600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2678,240 +2726,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>657400</v>
+      </c>
+      <c r="E26" s="3">
         <v>958500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>601700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1009000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1140700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1225000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1063900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1315600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1311000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1480200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1263900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1504300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1846800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2617900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3001700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1904200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1681700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>951000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>844000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>709400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>192400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>274600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>72400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>124800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1125100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>904500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1017100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>825800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>765200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>811900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>845100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>391700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>474500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>343200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>118200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E27" s="3">
         <v>652300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>443800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>745600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>884000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>875200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>816300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1039700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1091500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1257200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>979500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1222700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1644200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2378200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2722200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1708900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1458500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>837600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>782100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>648000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>141800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>205200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1042300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>813000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>941500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>741000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>688300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>749200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>784400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>321100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>417500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>283500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>61400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3026,8 +3083,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3142,8 +3202,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3258,8 +3321,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3374,240 +3440,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-46100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-78800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-157100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-108200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-107900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-128800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-126300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-121800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>206800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-157700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-65800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>44700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>109400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>58100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>21600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-25500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>34100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-70200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>70500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-31500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>47000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-80100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>31700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-61300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>58800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>111000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E33" s="3">
         <v>652300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>443800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>745600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>884000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>875200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>816300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1039700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1091500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1257200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>979500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1222700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1644200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2378200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2722200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1708900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1458500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>837600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>782100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>648000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>141800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>205200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>34600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1042300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>813000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>941500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>741000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>688300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>749200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>784400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>321100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>417500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>283500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>61400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3722,245 +3797,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E35" s="3">
         <v>652300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>443800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>745600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>884000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>875200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>816300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1039700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1091500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1257200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>979500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1222700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1644200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2378200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2722200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1708900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1458500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>837600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>782100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>648000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>141800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>205200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>34600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1042300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>813000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>941500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>741000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>688300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>749200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>784400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>321100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>417500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>283500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>61400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4001,8 +4085,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4043,1052 +4128,1080 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2836100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2637700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2477800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3362500</v>
       </c>
-      <c r="G41" s="3">
-        <v>3187200</v>
-      </c>
       <c r="H41" s="3">
+        <v>3187100</v>
+      </c>
+      <c r="I41" s="3">
         <v>3381700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3200300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3930800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3184300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2983700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2713800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3347700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3696300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3229400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2626900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3639800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3492000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2219100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1054500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1404400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1067300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1878900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2219500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2287300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1839700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2446500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1491500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2413200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>487400</v>
+      </c>
+      <c r="E42" s="3">
         <v>857700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1034000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>602700</v>
       </c>
-      <c r="G42" s="3">
-        <v>193100</v>
-      </c>
       <c r="H42" s="3">
+        <v>193000</v>
+      </c>
+      <c r="I42" s="3">
         <v>537100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>510800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>441500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>480400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>433100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>218400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>363800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>400600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>672700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>431200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>560000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>517100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>467300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>102400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>156800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>506700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>839200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>999800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>247600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>459900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>662000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>906600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1349100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>7795400</v>
+      </c>
+      <c r="E43" s="3">
         <v>8009500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7523900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7771100</v>
       </c>
-      <c r="G43" s="3">
-        <v>7226000</v>
-      </c>
       <c r="H43" s="3">
+        <v>7226100</v>
+      </c>
+      <c r="I43" s="3">
         <v>7387300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7745000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11217900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10692300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11260800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12220100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11822500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11251700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9999900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9332300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7984900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6087200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5301400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3306500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2555100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1960700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2097900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2059500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1806900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2131500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2049800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2634900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2725700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2283100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2682200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2546300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2630500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2274100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2616200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2748600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2802500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2633600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2807200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2467200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2402800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2851200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2695900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3165900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2852700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2015600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1997200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1507200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1345600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1061300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1322500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1208400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1511100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1471100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1594800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1580600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1479100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>485600</v>
+      </c>
+      <c r="E45" s="3">
         <v>584900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>588100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>546500</v>
       </c>
-      <c r="G45" s="3">
-        <v>510100</v>
-      </c>
       <c r="H45" s="3">
+        <v>510300</v>
+      </c>
+      <c r="I45" s="3">
         <v>574100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>638200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>632900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>517500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>556300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>598700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>556400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>346700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>405200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>306400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>341400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>295100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>358600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>175900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>224100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>199200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>282900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>216900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>304500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>172500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>196300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>144400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>146700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>138600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>131000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>125000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>131300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>125800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>180600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>191400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>169900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>140500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>14173800</v>
+      </c>
+      <c r="E46" s="3">
         <v>15211700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14490000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15258700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13752300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14835800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15013700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19207200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17711700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18275700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18365100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18650500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18546400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17003100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15862700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15378800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12407000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10343600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6146600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5686000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4795200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6421200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6704100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6157500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6074800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6949500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6758000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8113900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2521000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2990700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3088700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2927800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2957400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3061800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2228400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2335200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2269100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2243600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2379700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2169700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10371700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9597600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9415100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9386800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8117900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7244100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1100900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1015100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>992900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1208900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1451100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1642600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1920700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1956400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1743300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1335500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>41240400</v>
+      </c>
+      <c r="E48" s="3">
         <v>38724200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37415500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36640300</v>
       </c>
-      <c r="G48" s="3">
-        <v>35400200</v>
-      </c>
       <c r="H48" s="3">
+        <v>35400300</v>
+      </c>
+      <c r="I48" s="3">
         <v>35360500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35454400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36778400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36455600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34609400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33539900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31065700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34547700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34531700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33960900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32323000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30365200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25704900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21623400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21324800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20752300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24092400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23977800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26598600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>24369500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>24227100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>23212000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>23085100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>4941300</v>
+      </c>
+      <c r="E49" s="3">
         <v>4874300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4868400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4853100</v>
       </c>
-      <c r="G49" s="3">
-        <v>4834600</v>
-      </c>
       <c r="H49" s="3">
+        <v>4834500</v>
+      </c>
+      <c r="I49" s="3">
         <v>4918100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4937100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5013600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4987400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5014100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5012800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4875200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5581500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5565400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5331700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4982500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4626800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6636400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>407900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>402700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>400900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>460900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>357200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>397400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>364700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>355300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>354900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>361500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>345800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>354300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>383600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>384100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>415900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>404900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>375200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>380300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>393200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5203,8 +5316,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5319,124 +5435,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1522300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1483300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4816500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4884000</v>
       </c>
-      <c r="G52" s="3">
-        <v>1308400</v>
-      </c>
       <c r="H52" s="3">
+        <v>1308300</v>
+      </c>
+      <c r="I52" s="3">
         <v>5152300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5187700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4681600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1390700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3707800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4043600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4335700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4481300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4085100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3777700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3144900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3103100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3142400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2484600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2427200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2336300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2923900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2825800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3302800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2486900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1880600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1713700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1711100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5551,124 +5673,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>75353900</v>
+      </c>
+      <c r="E54" s="3">
         <v>74282800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>72146400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71607200</v>
       </c>
-      <c r="G54" s="3">
-        <v>68338400</v>
-      </c>
       <c r="H54" s="3">
+        <v>68338200</v>
+      </c>
+      <c r="I54" s="3">
         <v>70209700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69221700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74817800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>72865400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70505000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70224100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67474900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>73528700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70783000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68348000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>65215900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58620000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>53071400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31763400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30855800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29277600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35107300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35316000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>38098900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35216500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35368900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33781800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34607100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5709,8 +5837,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5751,704 +5880,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3085900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2939500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2794000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2866300</v>
       </c>
-      <c r="G57" s="3">
-        <v>3432900</v>
-      </c>
       <c r="H57" s="3">
+        <v>3432700</v>
+      </c>
+      <c r="I57" s="3">
         <v>2979200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2852300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3047300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3554400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2988400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2769200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2806000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3608300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2945100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3181400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2864600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2512900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1848600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1513700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1410300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1363300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1292100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1131100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1753800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2109900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1923100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1823000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1658600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>2673200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3169900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3830000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3109400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2559900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2837800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3877900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3979100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4013900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4354600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4098000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3511800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5327700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5653600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2538400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2272100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2209500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1903900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1117900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1093400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1033900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1497800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2281900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1593000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1303200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1221700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1103800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1091500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2363500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2916100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2580100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4732500</v>
       </c>
-      <c r="G59" s="3">
-        <v>2168300</v>
-      </c>
       <c r="H59" s="3">
+        <v>2168000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2172900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2643500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6397400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2816200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4629600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7606000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9319000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4691800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4248500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5135800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5984500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2537300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2381300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1427600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1688500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1442100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2328000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2975500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4170100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2239900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1948300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2444200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4481500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>9153200</v>
+      </c>
+      <c r="E60" s="3">
         <v>9953700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9964300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11477700</v>
       </c>
-      <c r="G60" s="3">
-        <v>8988500</v>
-      </c>
       <c r="H60" s="3">
+        <v>8988100</v>
+      </c>
+      <c r="I60" s="3">
         <v>8855900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10120600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14671900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11245100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12785000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15137600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16312800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13627800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12847200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10855500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11121200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7259700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6133800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4059200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4192300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3839300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5117900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6388500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7517000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5653000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5093100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5371000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7231700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>26286900</v>
+      </c>
+      <c r="E61" s="3">
         <v>25912400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25620000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25183600</v>
       </c>
-      <c r="G61" s="3">
-        <v>24645600</v>
-      </c>
       <c r="H61" s="3">
+        <v>24645500</v>
+      </c>
+      <c r="I61" s="3">
         <v>25079000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23930800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24196400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23300300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22769000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21797100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21624200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22304700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21281400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23135700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21548700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20605100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18309500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9394800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9384300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8779800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11336200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10598900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10485200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8639000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9688200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9012400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9095000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>5005700</v>
+      </c>
+      <c r="E62" s="3">
         <v>4501200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4244400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6979900</v>
       </c>
-      <c r="G62" s="3">
-        <v>3867100</v>
-      </c>
       <c r="H62" s="3">
+        <v>3867200</v>
+      </c>
+      <c r="I62" s="3">
         <v>7550400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7462400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7807500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4909800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6892800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6780000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5967400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9015300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9694700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9740800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9368600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8254700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7994800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5164400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5067400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4936500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4931700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4975800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5437900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5235000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4019500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4026100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4060300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6563,8 +6711,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6679,8 +6830,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6795,124 +6949,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>46381600</v>
+      </c>
+      <c r="E66" s="3">
         <v>47048300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>46291000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46977300</v>
       </c>
-      <c r="G66" s="3">
-        <v>43398300</v>
-      </c>
       <c r="H66" s="3">
+        <v>43398000</v>
+      </c>
+      <c r="I66" s="3">
         <v>45043200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45310200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>50670800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46252400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>44794700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45902800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45943300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51680400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>50316600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>49990000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47937600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>41404100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>39212600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19406800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19405700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18337600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22287100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22919800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24429400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20549300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19382000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19002400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20923200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6953,8 +7113,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7069,8 +7230,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7185,8 +7349,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7301,8 +7468,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7417,124 +7587,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>10808300</v>
+      </c>
+      <c r="E72" s="3">
         <v>9983700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8978700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8310200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9190200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8785000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7997600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7698100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9943200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8476400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6998700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5425900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10521600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9247300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7143800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6217600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6914900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4951900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3927300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3144800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2643400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2859000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2653800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2868400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4758100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4799200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3986200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3044700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7649,8 +7825,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7765,8 +7944,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7881,124 +8063,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>22213400</v>
+      </c>
+      <c r="E76" s="3">
         <v>20542100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19401200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18475300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18980600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18774900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17827600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17944600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20235400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19310300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17932400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15684500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21848300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20466300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18358000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17278400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17215900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13858900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12356600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11450100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10940000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12820300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12396200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13669400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14667200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15986900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14779400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13683900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8113,245 +8301,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E81" s="3">
         <v>652300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>443800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>745600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>884000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>875200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>816300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1039700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1091500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1257200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>979500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1222700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1644200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2378200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2722200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1708900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1458500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>837600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>782100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>648000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>141800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>205200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>34600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1042300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>813000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>941500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>741000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>688300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>749200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>784400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>321100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>417500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>283500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>61400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8392,124 +8589,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>692400</v>
+      </c>
+      <c r="E83" s="3">
         <v>960500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>897900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>926000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>737500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>874800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>805500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>683200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>525300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>691800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>684600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>722000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>811100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>796000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>742600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>704500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>666200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>591000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>503100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>483400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>523300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>551700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>549500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>579700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>592200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>595600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>565200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>537500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>497000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>559000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>537300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>588000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>713800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>683300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>660300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>634300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8624,8 +8825,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8740,8 +8944,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8856,8 +9063,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8972,8 +9182,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9088,124 +9301,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2199900</v>
+      </c>
+      <c r="E89" s="3">
         <v>2259700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2460100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1459800</v>
       </c>
-      <c r="G89" s="3">
-        <v>2172300</v>
-      </c>
       <c r="H89" s="3">
+        <v>2172100</v>
+      </c>
+      <c r="I89" s="3">
         <v>2989900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4126900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1558800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2685000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1035700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>752000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>447400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2726200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3733800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1600000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>984400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2642300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1161500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>695900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>616000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1120400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>846400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-539500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>668800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1966900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2513500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1620900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1305300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>478900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9246,124 +9465,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1748000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1260700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1195200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1191500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1499000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-1698300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1182300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1076300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1052300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1783400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1508300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1279700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1068800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-295700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-178500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-359700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-320800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-278300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-214000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-385700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-324300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-196700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9478,8 +9701,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9594,124 +9820,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-857400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-795800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1490000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1303700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1412100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1744400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1039100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1693900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1289200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1079500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-807400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-900300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-722400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-916800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-552000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-145300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-462600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-224600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-712600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-475200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-293400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>130100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9752,124 +9984,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2151000</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>535900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2555500</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>236800</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>559200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>49000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-520800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-71100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-323200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-60300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-206300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-35300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-732400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-698500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-458600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-110700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-990600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-832000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9984,8 +10220,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10100,8 +10339,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10216,352 +10458,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1038000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1320100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1883600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-136500</v>
       </c>
-      <c r="G100" s="3">
-        <v>-831900</v>
-      </c>
       <c r="H100" s="3">
+        <v>-831800</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1174600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3560500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>156700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-523500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-536400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>407500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-627800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-402100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-734000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2906600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-507400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-163600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2061800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-266700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-954100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-274300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E101" s="3">
         <v>136000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>61000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>57300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-399200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-62700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-136000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-26700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>160600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>14300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>195100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>186800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>16500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>211600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>79700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-10700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>13700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>30000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-99000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-144100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>270100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-38800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>108200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>30500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>107900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>51800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>69600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>51000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E102" s="3">
         <v>62700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-975600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11400</v>
       </c>
-      <c r="G102" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I102" s="3">
         <v>206800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-466600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>733700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>68500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>184400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-999900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>596000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>703500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-143200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1071100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1114400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-349900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>337100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-576700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-340600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>108200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>447600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-516200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>955000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-921700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>709100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>211400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>513900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>230300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-67900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>EC</t>
   </si>
@@ -656,527 +656,540 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7819800</v>
+      </c>
+      <c r="E8" s="3">
         <v>7642900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7594400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7265800</v>
       </c>
-      <c r="G8" s="3">
-        <v>7478600</v>
-      </c>
       <c r="H8" s="3">
+        <v>7478500</v>
+      </c>
+      <c r="I8" s="3">
         <v>7890100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8300800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7888400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8112400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8981500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8683800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8219600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8393000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9522700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10859600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11410100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8442900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7622700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5133200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4083300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3613300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2979900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2957500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2026000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3918700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4831100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4863900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4943300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4304500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4683700</v>
+      </c>
+      <c r="E9" s="3">
         <v>5273300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4964900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5087200</v>
       </c>
-      <c r="G9" s="3">
-        <v>4844400</v>
-      </c>
       <c r="H9" s="3">
+        <v>4844500</v>
+      </c>
+      <c r="I9" s="3">
         <v>5415500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5242600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5061700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4857400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5915000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5003200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5069300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4846100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5761800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6108800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6000200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4663800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4591800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3191300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2400600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2207500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2164400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2002500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1827700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2934600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3190200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3034900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3027600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2763200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3136100</v>
+      </c>
+      <c r="E10" s="3">
         <v>2369600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2629500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2178500</v>
       </c>
-      <c r="G10" s="3">
-        <v>2634200</v>
-      </c>
       <c r="H10" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2474600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3058200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2826700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3255000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3066500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3680700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3150200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3546900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3760900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4750800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5409900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3779100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3030900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1941900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1682700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1405700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>815500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>955000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>198300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>984100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1641000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1829000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1915700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1541300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1218,8 +1231,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1259,86 +1273,89 @@
       <c r="O12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="3">
         <v>209900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>115700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>101600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>66200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>14100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>35300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>86600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>23800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>33600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>103000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>15700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>66900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>16600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>50300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>271600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>56400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>292200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>103900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>24700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>8600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>96800</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1456,246 +1473,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-137100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>53300</v>
       </c>
-      <c r="G14" s="3">
-        <v>3900</v>
-      </c>
       <c r="H14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I14" s="3">
         <v>-295700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>35700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-68500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>81100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>24000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-116500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-328800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>314200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>187600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>149000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>7900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>800</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>244000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1006900</v>
+      </c>
+      <c r="E15" s="3">
         <v>71900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1047600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1141900</v>
       </c>
-      <c r="G15" s="3">
-        <v>912400</v>
-      </c>
       <c r="H15" s="3">
+        <v>931300</v>
+      </c>
+      <c r="I15" s="3">
         <v>75500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1042600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>979600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>995100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>555900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1050500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>833800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>715100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>79300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>31900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>33800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>89200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>14100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>13600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>40200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>12900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>20000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>46000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>11200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>11500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>8700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>15000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>10900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>13300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>16400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1734,246 +1760,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5479700</v>
+      </c>
+      <c r="E17" s="3">
         <v>6367300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5699600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5832100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5476600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5959500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6033000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5569000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5560400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7522300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5831500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5691800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5426800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6706600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6554200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6572100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5185200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5129400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3570700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2706400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2455500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2553800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2319800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1827300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3529200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3845900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3321700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3334800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2966200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2340100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1275600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1894800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1433700</v>
       </c>
-      <c r="G18" s="3">
-        <v>2002000</v>
-      </c>
       <c r="H18" s="3">
+        <v>2001900</v>
+      </c>
+      <c r="I18" s="3">
         <v>1930600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2267900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2319400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2552000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1459200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2852300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2527800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2966100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2816100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4305400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4838000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3257700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2493200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1562500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1376900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1157800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>426100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>637700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>198700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>389600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>985200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1542100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1608600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1338300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>538900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2015,603 +2048,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>262300</v>
+      </c>
+      <c r="E20" s="3">
         <v>79000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>46100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>78800</v>
       </c>
-      <c r="G20" s="3">
-        <v>157100</v>
-      </c>
       <c r="H20" s="3">
+        <v>157400</v>
+      </c>
+      <c r="I20" s="3">
         <v>107900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>128800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>126300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>121800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-206800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>157700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>65800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-44700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-109400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-58100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-21600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>25500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-34100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>70200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-70500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>31500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>80100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-31700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>43400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>61300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>83200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>19300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>45700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>26900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>18100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>117200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>291700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3084700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1268500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2896400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2496800</v>
       </c>
-      <c r="G21" s="3">
-        <v>2757300</v>
-      </c>
       <c r="H21" s="3">
+        <v>2775900</v>
+      </c>
+      <c r="I21" s="3">
         <v>1898100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3181600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3172700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3425300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2009900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4109600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3203800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3685700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3693000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5056700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5471100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3904100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3137800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2179000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1845800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1632900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1019600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1118900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>779700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>922300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1657500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2106000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2217200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1937100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>484100</v>
+      </c>
+      <c r="E22" s="3">
         <v>492500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>501600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>470600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>442100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>464900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>438900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>430100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>445300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>457600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>425800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>404900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>375500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>391500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>363900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>346400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>285600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>294600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>154300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>127500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>117300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>125700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>155400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>156700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>126200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>127000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>128100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>129500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>122000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>183100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>144600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>347900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>171800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>206800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>198200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>153300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>205200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>226800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1660400</v>
+      </c>
+      <c r="E23" s="3">
         <v>921000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1393700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>916100</v>
       </c>
-      <c r="G23" s="3">
-        <v>1471500</v>
-      </c>
       <c r="H23" s="3">
+        <v>1471400</v>
+      </c>
+      <c r="I23" s="3">
         <v>1746900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1768000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1845700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2072600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1116600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2792100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2063300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2712500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2490400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3896800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4382200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2914000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2177000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1433600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1215200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1032100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>370700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>411700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>73500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>216300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>938200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1382300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1522500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>806300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>739400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>603800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>616300</v>
+      </c>
+      <c r="E24" s="3">
         <v>263600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>435200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>314300</v>
       </c>
-      <c r="G24" s="3">
-        <v>462400</v>
-      </c>
       <c r="H24" s="3">
+        <v>462300</v>
+      </c>
+      <c r="I24" s="3">
         <v>606200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>543000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>781700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>757000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-194300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1311900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>799400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1208200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>643600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1278900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1380500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1009800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>495300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>482700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>371200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>322700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>178300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>137100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>91500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-186900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>477900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>505400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>451800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>303400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>589000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>564000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>457200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>414600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>535100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>396300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>485600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2729,246 +2778,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1044100</v>
+      </c>
+      <c r="E26" s="3">
         <v>657400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>958500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>601700</v>
       </c>
-      <c r="G26" s="3">
-        <v>1009000</v>
-      </c>
       <c r="H26" s="3">
+        <v>1009100</v>
+      </c>
+      <c r="I26" s="3">
         <v>1140700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1225000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1063900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1315600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1311000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1480200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1263900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1504300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1846800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2617900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3001700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1904200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1681700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>951000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>844000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>709400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>192400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>274600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>72400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>124800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1125100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>904500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1017100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>825800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>765200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>811900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>845100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>391700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>474500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>343200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>118200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>788700</v>
+      </c>
+      <c r="E27" s="3">
         <v>405000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>652300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>443800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>745600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>884000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>875200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>816300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1039700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1091500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1257200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>979500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1222700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1644200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2378200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2722200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1708900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1458500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>837600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>782100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>648000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>141800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>205200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>34600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1042300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>813000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>941500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>741000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>688300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>749200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>784400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>321100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>417500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>283500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>61400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3086,8 +3144,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3205,8 +3266,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3324,8 +3388,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3443,246 +3510,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-262300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-79000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-46100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-78800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-157100</v>
-      </c>
       <c r="H32" s="3">
+        <v>-157400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-107900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-128800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-126300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-121800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>206800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-157700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-65800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>44700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>109400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>58100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>21600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-25500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>34100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-70200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>70500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-31500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>47000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-80100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>31700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-61300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>58800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>111000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>788700</v>
+      </c>
+      <c r="E33" s="3">
         <v>405000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>652300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>443800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>745600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>884000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>875200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>816300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1039700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1091500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1257200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>979500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1222700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1644200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2378200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2722200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1708900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1458500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>837600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>782100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>648000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>141800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>34600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1042300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>813000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>941500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>741000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>688300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>749200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>784400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>321100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>417500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>283500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>61400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3800,251 +3876,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>788700</v>
+      </c>
+      <c r="E35" s="3">
         <v>405000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>652300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>443800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>745600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>884000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>875200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>816300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1039700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1091500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1257200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>979500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1222700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1644200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2378200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2722200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1708900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1458500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>837600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>782100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>648000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>141800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>34600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1042300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>813000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>941500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>741000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>688300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>749200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>784400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>321100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>417500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>283500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>61400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4086,8 +4171,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4129,1079 +4215,1107 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3518500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2836100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2637700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2477800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3362500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3187100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3381700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3200300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3930800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3184300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2983700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2713800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3347700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3696300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3229400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2626900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3639800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3492000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2219100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1054500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1404400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1067300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1878900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2219500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2287300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1839700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2446500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1491500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2413200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>249100</v>
+      </c>
+      <c r="E42" s="3">
         <v>487400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>857700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1034000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>602700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>193000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>537100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>510800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>441500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>480400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>433100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>218400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>363800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>400600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>672700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>431200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>560000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>517100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>467300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>102400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>156800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>506700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>839200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>999800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>247600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>459900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>662000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>906600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1349100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>8065600</v>
+      </c>
+      <c r="E43" s="3">
         <v>7795400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8009500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7523900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7771100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7226100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7387300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7745000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11217900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10692300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11260800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12220100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11822500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11251700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9999900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9332300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7984900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6087200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5301400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3306500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2555100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1960700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2097900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2059500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1806900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2131500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2049800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2634900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2725700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2838300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2283100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2682200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2546300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2630500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2274100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2616200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2748600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2802500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2633600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2807200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2467200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2402800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2851200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2695900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3165900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2852700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2015600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1997200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1507200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1345600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1061300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1322500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1208400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1511100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1471100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1594800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1580600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1479100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>485700</v>
+      </c>
+      <c r="E45" s="3">
         <v>485600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>584900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>588100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>546500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>510300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>574100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>638200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>632900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>517500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>556300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>598700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>556400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>346700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>405200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>306400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>341400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>295100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>358600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>175900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>224100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>199200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>282900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>216900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>304500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>172500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>196300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>144400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>146700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>138600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>131000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>125000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>131300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>125800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>180600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>191400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>169900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>140500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>15534100</v>
+      </c>
+      <c r="E46" s="3">
         <v>14173800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15211700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14490000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15258700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13752300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14835800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15013700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19207200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17711700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18275700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18365100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18650500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18546400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17003100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15862700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15378800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12407000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10343600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6146600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5686000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4795200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6421200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6704100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6157500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6074800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6949500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6758000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8113900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2635400</v>
+      </c>
+      <c r="E47" s="3">
         <v>2521000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2990700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3088700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2927800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2957400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3061800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2228400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2335200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2269100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2243600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2379700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2169700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10371700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9597600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9415100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9386800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8117900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7244100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1100900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1015100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>992900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1208900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1451100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1642600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1920700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1956400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1743300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1335500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>42395200</v>
+      </c>
+      <c r="E48" s="3">
         <v>41240400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38724200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37415500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36640300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35400300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35360500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35454400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36778400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36455600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34609400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33539900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31065700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34547700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34531700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33960900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>32323000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30365200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25704900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21623400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21324800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20752300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24092400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23977800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26598600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>24369500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24227100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>23212000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>23085100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>4977900</v>
+      </c>
+      <c r="E49" s="3">
         <v>4941300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4874300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4868400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4853100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4834500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4918100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4937100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5013600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4987400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5014100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5012800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4875200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5581500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5565400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5331700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4982500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4626800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6636400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>407900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>402700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>400900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>460900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>357200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>397400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>364700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>355300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>354900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>361500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>345800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>354300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>383600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>384100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>415900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>404900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>375200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>380300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>393200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5319,8 +5433,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5438,127 +5555,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1587200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1522300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1483300</v>
       </c>
-      <c r="F52" s="3">
-        <v>4816500</v>
-      </c>
       <c r="G52" s="3">
+        <v>1437700</v>
+      </c>
+      <c r="H52" s="3">
         <v>4884000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1308300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5152300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5187700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4681600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1390700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3707800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4043600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4335700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4481300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4085100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3777700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3144900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3103100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3142400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2484600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2427200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2336300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2923900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2825800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3302800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2486900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1880600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1713700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1711100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5676,127 +5799,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>78567400</v>
+      </c>
+      <c r="E54" s="3">
         <v>75353900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>74282800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72146400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71607200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>68338200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70209700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69221700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74817800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>72865400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70505000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70224100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67474900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>73528700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70783000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68348000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>65215900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58620000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>53071400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31763400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30855800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29277600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35107300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35316000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>38098900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35216500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35368900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33781800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34607100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5838,8 +5967,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5881,722 +6011,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3284200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3085900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2939500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2794000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2866300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3432700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2979200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2852300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3047300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3554400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2988400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2769200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2806000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3608300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2945100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3181400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2864600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2512900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1848600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1513700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1410300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1363300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1292100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1131100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1753800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2109900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1923100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1823000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1658600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>3334700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2673200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3169900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3830000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3109400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2559900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2837800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3877900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3979100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4013900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4354600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4098000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3511800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5327700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5653600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2538400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2272100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2209500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1903900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1117900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1093400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1033900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1497800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2281900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1593000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1303200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1221700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1103800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1091500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>4776300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2363500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2916100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2580100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4732500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2168000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2172900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2643500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6397400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2816200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4629600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7606000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9319000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4691800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4248500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5135800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5984500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2537300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2381300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1427600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1688500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1442100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2328000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2975500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4170100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2239900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1948300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2444200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4481500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>12342000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9153200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9953700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9964300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11477700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8988100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8855900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10120600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14671900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11245100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12785000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15137600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16312800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13627800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12847200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10855500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11121200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7259700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6133800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4059200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4192300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3839300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5117900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6388500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7517000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5653000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5093100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5371000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7231700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>26202500</v>
+      </c>
+      <c r="E61" s="3">
         <v>26286900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25912400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25620000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25183600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24645500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25079000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23930800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24196400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23300300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22769000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21797100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21624200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22304700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21281400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23135700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21548700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20605100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18309500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9394800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9384300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8779800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11336200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10598900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10485200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8639000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9688200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9012400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9095000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>5180600</v>
+      </c>
+      <c r="E62" s="3">
         <v>5005700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4501200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4244400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6979900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3867200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7550400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7462400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7807500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4909800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6892800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6780000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5967400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9015300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9694700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9740800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9368600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8254700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7994800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5164400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5067400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4936500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4931700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4975800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5437900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5235000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4019500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4026100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4060300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6714,8 +6863,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6833,8 +6985,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6952,127 +7107,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>49938500</v>
+      </c>
+      <c r="E66" s="3">
         <v>46381600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47048300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46291000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46977300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43398000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45043200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45310200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50670800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46252400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>44794700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45902800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45943300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51680400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50316600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>49990000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47937600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>41404100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>39212600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19406800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19405700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18337600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22287100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22919800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24429400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>20549300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19382000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19002400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20923200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7114,8 +7275,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7233,8 +7395,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7352,8 +7517,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7471,8 +7639,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7590,127 +7761,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>10563000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10808300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9983700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8978700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8310200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9190200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8785000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7997600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7698100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9943200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8476400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6998700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5425900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10521600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9247300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7143800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6217600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6914900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4951900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3927300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3144800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2643400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2859000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2653800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2868400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4758100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4799200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3986200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3044700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7828,8 +8005,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7947,8 +8127,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8066,127 +8249,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>21785000</v>
+      </c>
+      <c r="E76" s="3">
         <v>22213400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20542100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19401200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18475300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18980600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18774900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17827600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17944600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20235400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19310300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17932400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15684500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21848300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20466300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18358000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17278400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17215900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13858900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12356600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11450100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10940000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12820300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12396200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13669400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14667200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15986900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14779400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13683900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8304,251 +8493,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>788700</v>
+      </c>
+      <c r="E81" s="3">
         <v>405000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>652300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>443800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>745600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>884000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>875200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>816300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1039700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1091500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1257200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>979500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1222700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1644200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2378200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2722200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1708900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1458500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>837600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>782100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>648000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>141800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>34600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1042300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>813000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>941500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>741000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>688300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>749200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>784400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>321100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>417500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>283500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>61400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8590,127 +8788,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>927500</v>
+      </c>
+      <c r="E83" s="3">
         <v>692400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>960500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>897900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>926000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>737500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>874800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>805500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>683200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>525300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>691800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>684600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>722000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>811100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>796000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>742600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>704500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>666200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>591000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>503100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>483400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>523300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>551700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>549500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>579700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>592200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>595600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>565200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>537500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>497000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>559000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>537300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>588000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>713800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>683300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>660300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>634300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8828,8 +9030,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8947,8 +9152,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9066,8 +9274,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9185,8 +9396,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9304,127 +9518,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1960900</v>
+      </c>
+      <c r="E89" s="3">
         <v>2199900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2259700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2460100</v>
       </c>
-      <c r="G89" s="3">
-        <v>1459800</v>
-      </c>
       <c r="H89" s="3">
+        <v>1459700</v>
+      </c>
+      <c r="I89" s="3">
         <v>2172100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2989900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4126900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1558800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2685000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1035700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>752000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>447400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2726200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3733800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1600000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>984400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2642300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1161500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>695900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>616000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1120400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>846400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-539500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>668800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1966900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2513500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1620900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1305300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>478900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9466,127 +9686,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1124100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1748000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1260700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1195200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1191500</v>
-      </c>
       <c r="H91" s="3">
+        <v>-927000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1698300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1182300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1076300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1052300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1783400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1508300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1279700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1068800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-295700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-178500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-359700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-320800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-278300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-214000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-385700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-324300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-196700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9704,8 +9928,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9823,127 +10050,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-819500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-857400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-795800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1490000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1303700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1303800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1412100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1744400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1039100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1693900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1289200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1079500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-807400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-900300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-722400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-916800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-552000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-145300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-462600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-224600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-712600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-475200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-293400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>130100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9985,127 +10218,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2151000</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3">
+        <v>166200</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>535900</v>
+      </c>
+      <c r="K96" s="3">
+        <v>2555500</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>535900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>2555500</v>
-      </c>
-      <c r="K96" s="3" t="s">
+      <c r="M96" s="3">
+        <v>236800</v>
+      </c>
+      <c r="N96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L96" s="3">
-        <v>236800</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>559200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>49000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-520800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-71100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-323200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-60300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-206300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-35300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-732400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-698500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-458600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-110700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-990600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-832000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10223,8 +10460,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10342,8 +10582,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10461,361 +10704,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-532400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1038000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1320100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1883600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-136500</v>
-      </c>
       <c r="H100" s="3">
+        <v>-136400</v>
+      </c>
+      <c r="I100" s="3">
         <v>-831800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1174600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3560500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>156700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-523500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-536400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>407500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-627800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-402100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-734000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2906600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-507400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-163600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2061800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-266700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-954100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-274300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E101" s="3">
         <v>61700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>136000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>61000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>57300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-399200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-62700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-136000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-26700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>160600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>195100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>186800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>16500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>211600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>79700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-10700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>13700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>30000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-99000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-144100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>270100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-38800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>108200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>30500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>107900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>51800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>69600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>51000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>597200</v>
+      </c>
+      <c r="E102" s="3">
         <v>87500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>62700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-975600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>206800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-466600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>733700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>68500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>184400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-999900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>596000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>703500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-143200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1071100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1114400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-349900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>337100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-576700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-340600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>108200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>447600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-516200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>955000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-921700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>709100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>211400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>30000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>513900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>230300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-67900</v>
       </c>
     </row>
